--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -21,8 +21,8 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.########"/>
     <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00 &quot;€&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -110,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -194,11 +194,27 @@
         <color rgb="00000000"/>
       </top>
     </border>
+    <border>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,7 +271,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -280,7 +296,7 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -290,6 +306,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -951,23 +971,23 @@
       <c r="F2" s="19" t="n">
         <v>46224</v>
       </c>
-      <c r="G2" s="20" t="n">
+      <c r="G2" s="33" t="n">
         <v>126.56</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>16.14269911</v>
       </c>
-      <c r="I2" s="20" t="n">
+      <c r="I2" s="33" t="n">
         <v>131.03</v>
       </c>
-      <c r="J2" s="20" t="n">
+      <c r="J2" s="33" t="n">
         <v>2115.18</v>
       </c>
       <c r="K2" s="22" t="n">
         <v>3.53</v>
       </c>
       <c r="L2" s="22" t="n">
-        <v>-0.62</v>
+        <v>-0.48</v>
       </c>
       <c r="M2" s="22" t="n">
         <v>1.76</v>
@@ -976,10 +996,10 @@
         <v>2.32</v>
       </c>
       <c r="O2" s="22" t="n">
-        <v>2.53</v>
+        <v>3.22</v>
       </c>
       <c r="P2" s="22" t="n">
-        <v>1</v>
+        <v>0.31</v>
       </c>
       <c r="Q2" s="22" t="n"/>
       <c r="R2" s="22" t="n"/>
@@ -1015,23 +1035,23 @@
       <c r="F3" s="19" t="n">
         <v>46261</v>
       </c>
-      <c r="G3" s="20" t="n">
+      <c r="G3" s="33" t="n">
         <v>40.46</v>
       </c>
       <c r="H3" s="21" t="n">
         <v>47</v>
       </c>
-      <c r="I3" s="20" t="n">
+      <c r="I3" s="33" t="n">
         <v>38.58</v>
       </c>
-      <c r="J3" s="20" t="n">
+      <c r="J3" s="33" t="n">
         <v>1813.47</v>
       </c>
       <c r="K3" s="22" t="n">
         <v>-4.63</v>
       </c>
       <c r="L3" s="22" t="n">
-        <v>-5.89</v>
+        <v>-6.23</v>
       </c>
       <c r="M3" s="22" t="n">
         <v>-4.63</v>
@@ -1040,10 +1060,10 @@
         <v>1.99</v>
       </c>
       <c r="O3" s="22" t="n">
-        <v>1.59</v>
+        <v>2.28</v>
       </c>
       <c r="P3" s="22" t="n">
-        <v>-6.22</v>
+        <v>-6.91</v>
       </c>
       <c r="Q3" s="22" t="n">
         <v>5.35</v>
@@ -1087,23 +1107,23 @@
       <c r="F4" s="19" t="n">
         <v>45629</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="33" t="n">
         <v>78.91</v>
       </c>
       <c r="H4" s="21" t="n">
         <v>4.808569</v>
       </c>
-      <c r="I4" s="20" t="n">
+      <c r="I4" s="33" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="J4" s="20" t="n">
+      <c r="J4" s="33" t="n">
         <v>309.66</v>
       </c>
       <c r="K4" s="22" t="n">
         <v>-18.39</v>
       </c>
       <c r="L4" s="22" t="n">
-        <v>-9.720000000000001</v>
+        <v>-10.18</v>
       </c>
       <c r="M4" s="22" t="n">
         <v>-0.88</v>
@@ -1112,10 +1132,10 @@
         <v>0.34</v>
       </c>
       <c r="O4" s="22" t="n">
-        <v>18.97</v>
+        <v>19.78</v>
       </c>
       <c r="P4" s="22" t="n">
-        <v>-37.36</v>
+        <v>-38.17</v>
       </c>
       <c r="Q4" s="22" t="n">
         <v>5.79</v>
@@ -1151,23 +1171,23 @@
       <c r="F5" s="19" t="n">
         <v>45621</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="33" t="n">
         <v>81.17</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>17.014908</v>
       </c>
-      <c r="I5" s="20" t="n">
+      <c r="I5" s="33" t="n">
         <v>72.89</v>
       </c>
-      <c r="J5" s="20" t="n">
+      <c r="J5" s="33" t="n">
         <v>1240.22</v>
       </c>
       <c r="K5" s="22" t="n">
         <v>-10.2</v>
       </c>
       <c r="L5" s="22" t="n">
-        <v>-5.29</v>
+        <v>-4.32</v>
       </c>
       <c r="M5" s="22" t="n">
         <v>-0.46</v>
@@ -1176,10 +1196,10 @@
         <v>1.36</v>
       </c>
       <c r="O5" s="22" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="P5" s="22" t="n">
-        <v>-30</v>
+        <v>-30.8</v>
       </c>
       <c r="Q5" s="22" t="n"/>
       <c r="R5" s="22" t="n"/>
@@ -1207,23 +1227,23 @@
       <c r="F6" s="19" t="n">
         <v>45621</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="33" t="n">
         <v>596.48</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>0.828825</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="33" t="n">
         <v>730.4400000000001</v>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="33" t="n">
         <v>605.41</v>
       </c>
       <c r="K6" s="22" t="n">
         <v>22.46</v>
       </c>
       <c r="L6" s="22" t="n">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="22" t="n">
         <v>1.02</v>
@@ -1232,10 +1252,10 @@
         <v>0.66</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" s="22" t="n"/>
       <c r="R6" s="22" t="n"/>
@@ -1271,23 +1291,23 @@
       <c r="F7" s="19" t="n">
         <v>46170</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="33" t="n">
         <v>206.93</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>5.95313343</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="33" t="n">
         <v>206.87</v>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="33" t="n">
         <v>1231.52</v>
       </c>
       <c r="K7" s="22" t="n">
         <v>-0.03</v>
       </c>
       <c r="L7" s="22" t="n">
-        <v>-18.56</v>
+        <v>-19.23</v>
       </c>
       <c r="M7" s="22" t="n">
         <v>-0.01</v>
@@ -1296,10 +1316,10 @@
         <v>1.35</v>
       </c>
       <c r="O7" s="22" t="n">
-        <v>3.72</v>
+        <v>4.42</v>
       </c>
       <c r="P7" s="22" t="n">
-        <v>-3.75</v>
+        <v>-4.45</v>
       </c>
       <c r="Q7" s="22" t="n">
         <v>10.53</v>
@@ -1343,23 +1363,23 @@
       <c r="F8" s="19" t="n">
         <v>45621</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="33" t="n">
         <v>5.61</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>40.45804</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="33" t="n">
         <v>7.8</v>
       </c>
-      <c r="J8" s="20" t="n">
+      <c r="J8" s="33" t="n">
         <v>315.69</v>
       </c>
       <c r="K8" s="22" t="n">
         <v>39.06</v>
       </c>
       <c r="L8" s="22" t="n">
-        <v>-6.22</v>
+        <v>-6.32</v>
       </c>
       <c r="M8" s="22" t="n">
         <v>1.78</v>
@@ -1368,10 +1388,10 @@
         <v>0.35</v>
       </c>
       <c r="O8" s="22" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="P8" s="22" t="n">
-        <v>19.26</v>
+        <v>18.46</v>
       </c>
       <c r="Q8" s="22" t="n">
         <v>25.34</v>
@@ -1405,35 +1425,35 @@
       <c r="F9" s="19" t="n">
         <v>45623</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="33" t="n">
         <v>11.36</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>11.498102</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="33" t="n">
         <v>12.63</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="33" t="n">
         <v>145.22</v>
       </c>
       <c r="K9" s="22" t="n">
         <v>11.14</v>
       </c>
       <c r="L9" s="22" t="n">
-        <v>-5.9</v>
+        <v>-4.19</v>
       </c>
       <c r="M9" s="22" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="N9" s="22" t="n">
         <v>0.16</v>
       </c>
       <c r="O9" s="22" t="n">
-        <v>19.74</v>
+        <v>20.54</v>
       </c>
       <c r="P9" s="22" t="n">
-        <v>-8.6</v>
+        <v>-9.4</v>
       </c>
       <c r="Q9" s="22" t="n"/>
       <c r="R9" s="22" t="n"/>
@@ -1469,23 +1489,23 @@
       <c r="F10" s="19" t="n">
         <v>46260</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="33" t="n">
         <v>76.27</v>
       </c>
       <c r="H10" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="33" t="n">
         <v>69.23999999999999</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="J10" s="33" t="n">
         <v>1592.59</v>
       </c>
       <c r="K10" s="22" t="n">
         <v>-9.220000000000001</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>-8.869999999999999</v>
+        <v>-10.36</v>
       </c>
       <c r="M10" s="22" t="n">
         <v>-9.220000000000001</v>
@@ -1494,10 +1514,10 @@
         <v>1.75</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>-11.67</v>
+        <v>-12.37</v>
       </c>
       <c r="Q10" s="22" t="n">
         <v>10.24</v>
@@ -1541,23 +1561,23 @@
       <c r="F11" s="19" t="n">
         <v>45922</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="33" t="n">
         <v>6.26</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="33" t="n">
         <v>6.39</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="33" t="n">
         <v>958.47</v>
       </c>
       <c r="K11" s="22" t="n">
         <v>2.02</v>
       </c>
       <c r="L11" s="22" t="n">
-        <v>-6.55</v>
+        <v>-4.84</v>
       </c>
       <c r="M11" s="22" t="n">
         <v>0.17</v>
@@ -1566,10 +1586,10 @@
         <v>1.05</v>
       </c>
       <c r="O11" s="22" t="n">
-        <v>19.42</v>
+        <v>20.22</v>
       </c>
       <c r="P11" s="22" t="n">
-        <v>-17.4</v>
+        <v>-18.2</v>
       </c>
       <c r="Q11" s="22" t="n">
         <v>17.73</v>
@@ -1611,23 +1631,23 @@
       <c r="F12" s="19" t="n">
         <v>46262</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="33" t="n">
         <v>56.32</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="33" t="n">
         <v>64.81</v>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="33" t="n">
         <v>1685.08</v>
       </c>
       <c r="K12" s="22" t="n">
         <v>15.08</v>
       </c>
       <c r="L12" s="22" t="n">
-        <v>9.51</v>
+        <v>14.85</v>
       </c>
       <c r="M12" s="22" t="n">
         <v>15.08</v>
@@ -1636,10 +1656,10 @@
         <v>1.85</v>
       </c>
       <c r="O12" s="22" t="n">
-        <v>1.07</v>
+        <v>1.75</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>14.01</v>
+        <v>13.33</v>
       </c>
       <c r="Q12" s="22" t="n">
         <v>-0.68</v>
@@ -1681,23 +1701,23 @@
       <c r="F13" s="19" t="n">
         <v>46267</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="33" t="n">
         <v>145.79</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="33" t="n">
         <v>184.4</v>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="33" t="n">
         <v>1843.99</v>
       </c>
       <c r="K13" s="22" t="n">
         <v>26.48</v>
       </c>
       <c r="L13" s="22" t="n">
-        <v>-12.18</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M13" s="22" t="n">
         <v>26.48</v>
@@ -1706,10 +1726,10 @@
         <v>2.02</v>
       </c>
       <c r="O13" s="22" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="P13" s="22" t="n">
-        <v>24.83</v>
+        <v>24.15</v>
       </c>
       <c r="Q13" s="22" t="n">
         <v>1.03</v>
@@ -1753,23 +1773,23 @@
       <c r="F14" s="19" t="n">
         <v>45922</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="33" t="n">
         <v>3.58</v>
       </c>
       <c r="H14" s="21" t="n">
         <v>145</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="33" t="n">
         <v>7.77</v>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="J14" s="33" t="n">
         <v>1126.33</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>116.89</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>1.26</v>
+        <v>-1.45</v>
       </c>
       <c r="M14" s="22" t="n">
         <v>9.74</v>
@@ -1778,10 +1798,10 @@
         <v>1.24</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>19.42</v>
+        <v>20.22</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>97.47</v>
+        <v>96.67</v>
       </c>
       <c r="Q14" s="22" t="n">
         <v>15.16</v>
@@ -1821,23 +1841,23 @@
       <c r="F15" s="19" t="n">
         <v>46140</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="33" t="n">
         <v>91.79000000000001</v>
       </c>
       <c r="H15" s="21" t="n">
         <v>22.46</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="33" t="n">
         <v>95</v>
       </c>
-      <c r="J15" s="20" t="n">
+      <c r="J15" s="33" t="n">
         <v>2133.59</v>
       </c>
       <c r="K15" s="22" t="n">
         <v>3.49</v>
       </c>
       <c r="L15" s="22" t="n">
-        <v>-4.03</v>
+        <v>-5.72</v>
       </c>
       <c r="M15" s="22" t="n">
         <v>0.87</v>
@@ -1846,10 +1866,10 @@
         <v>2.34</v>
       </c>
       <c r="O15" s="22" t="n">
-        <v>11.16</v>
+        <v>11.91</v>
       </c>
       <c r="P15" s="22" t="n">
-        <v>-7.67</v>
+        <v>-8.42</v>
       </c>
       <c r="Q15" s="22" t="n">
         <v>10.97</v>
@@ -1893,23 +1913,23 @@
       <c r="F16" s="19" t="n">
         <v>45621</v>
       </c>
-      <c r="G16" s="20" t="n">
+      <c r="G16" s="33" t="n">
         <v>23.74</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>204.17081927</v>
       </c>
-      <c r="I16" s="20" t="n">
+      <c r="I16" s="33" t="n">
         <v>14.94</v>
       </c>
-      <c r="J16" s="20" t="n">
+      <c r="J16" s="33" t="n">
         <v>3050.05</v>
       </c>
       <c r="K16" s="22" t="n">
         <v>-37.07</v>
       </c>
       <c r="L16" s="22" t="n">
-        <v>-11.69</v>
+        <v>-5.45</v>
       </c>
       <c r="M16" s="22" t="n">
         <v>-1.69</v>
@@ -1918,10 +1938,10 @@
         <v>3.35</v>
       </c>
       <c r="O16" s="22" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="P16" s="22" t="n">
-        <v>-56.87</v>
+        <v>-57.67</v>
       </c>
       <c r="Q16" s="22" t="n">
         <v>-4.07</v>
@@ -1963,23 +1983,23 @@
       <c r="F17" s="19" t="n">
         <v>45629</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="33" t="n">
         <v>27.11</v>
       </c>
       <c r="H17" s="21" t="n">
         <v>13.996531</v>
       </c>
-      <c r="I17" s="20" t="n">
+      <c r="I17" s="33" t="n">
         <v>24.57</v>
       </c>
-      <c r="J17" s="20" t="n">
+      <c r="J17" s="33" t="n">
         <v>343.86</v>
       </c>
       <c r="K17" s="22" t="n">
         <v>-9.369999999999999</v>
       </c>
       <c r="L17" s="22" t="n">
-        <v>-15.16</v>
+        <v>-15.13</v>
       </c>
       <c r="M17" s="22" t="n">
         <v>-0.45</v>
@@ -1988,10 +2008,10 @@
         <v>0.38</v>
       </c>
       <c r="O17" s="22" t="n">
-        <v>18.97</v>
+        <v>19.78</v>
       </c>
       <c r="P17" s="22" t="n">
-        <v>-28.34</v>
+        <v>-29.15</v>
       </c>
       <c r="Q17" s="22" t="n">
         <v>4.57</v>
@@ -2035,23 +2055,23 @@
       <c r="F18" s="19" t="n">
         <v>46273</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="33" t="n">
         <v>120.26</v>
       </c>
       <c r="H18" s="21" t="n">
         <v>3.3</v>
       </c>
-      <c r="I18" s="20" t="n">
+      <c r="I18" s="33" t="n">
         <v>121.56</v>
       </c>
-      <c r="J18" s="20" t="n">
+      <c r="J18" s="33" t="n">
         <v>401.16</v>
       </c>
       <c r="K18" s="22" t="n">
         <v>1.08</v>
       </c>
       <c r="L18" s="22" t="n">
-        <v>-13.1</v>
+        <v>-12.11</v>
       </c>
       <c r="M18" s="22" t="n">
         <v>1.08</v>
@@ -2060,10 +2080,10 @@
         <v>0.44</v>
       </c>
       <c r="O18" s="22" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>-0.62</v>
+        <v>-1.3</v>
       </c>
       <c r="Q18" s="22" t="n">
         <v>5.72</v>
@@ -2107,23 +2127,23 @@
       <c r="F19" s="19" t="n">
         <v>45775</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="33" t="n">
         <v>49.93</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="I19" s="20" t="n">
+      <c r="I19" s="33" t="n">
         <v>55</v>
       </c>
-      <c r="J19" s="20" t="n">
+      <c r="J19" s="33" t="n">
         <v>989.96</v>
       </c>
       <c r="K19" s="22" t="n">
         <v>10.16</v>
       </c>
       <c r="L19" s="22" t="n">
-        <v>-8.380000000000001</v>
+        <v>-9.4</v>
       </c>
       <c r="M19" s="22" t="n">
         <v>0.64</v>
@@ -2132,10 +2152,10 @@
         <v>1.09</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>40.82</v>
+        <v>41.77</v>
       </c>
       <c r="P19" s="22" t="n">
-        <v>-30.66</v>
+        <v>-31.61</v>
       </c>
       <c r="Q19" s="22" t="n">
         <v>6.98</v>
@@ -2175,23 +2195,23 @@
       <c r="F20" s="19" t="n">
         <v>46141</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="33" t="n">
         <v>237.04</v>
       </c>
       <c r="H20" s="21" t="n">
         <v>11.7</v>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="I20" s="33" t="n">
         <v>239.09</v>
       </c>
-      <c r="J20" s="20" t="n">
+      <c r="J20" s="33" t="n">
         <v>2797.35</v>
       </c>
       <c r="K20" s="22" t="n">
         <v>0.87</v>
       </c>
       <c r="L20" s="22" t="n">
-        <v>-2.04</v>
+        <v>-2.46</v>
       </c>
       <c r="M20" s="22" t="n">
         <v>0.22</v>
@@ -2200,10 +2220,10 @@
         <v>3.07</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>10.93</v>
+        <v>11.68</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>-10.06</v>
+        <v>-10.81</v>
       </c>
       <c r="Q20" s="22" t="n">
         <v>11.67</v>
@@ -2247,23 +2267,23 @@
       <c r="F21" s="19" t="n">
         <v>45775</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="33" t="n">
         <v>134.3</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>8.6406803</v>
       </c>
-      <c r="I21" s="20" t="n">
+      <c r="I21" s="33" t="n">
         <v>179.3</v>
       </c>
-      <c r="J21" s="20" t="n">
+      <c r="J21" s="33" t="n">
         <v>1549.27</v>
       </c>
       <c r="K21" s="22" t="n">
         <v>33.51</v>
       </c>
       <c r="L21" s="22" t="n">
-        <v>2.34</v>
+        <v>1.28</v>
       </c>
       <c r="M21" s="22" t="n">
         <v>2.09</v>
@@ -2272,10 +2292,10 @@
         <v>1.7</v>
       </c>
       <c r="O21" s="22" t="n">
-        <v>40.82</v>
+        <v>41.77</v>
       </c>
       <c r="P21" s="22" t="n">
-        <v>-7.31</v>
+        <v>-8.26</v>
       </c>
       <c r="Q21" s="22" t="n">
         <v>4.14</v>
@@ -2319,23 +2339,23 @@
       <c r="F22" s="19" t="n">
         <v>45775</v>
       </c>
-      <c r="G22" s="20" t="n">
+      <c r="G22" s="33" t="n">
         <v>37.05</v>
       </c>
       <c r="H22" s="21" t="n">
         <v>17.45</v>
       </c>
-      <c r="I22" s="20" t="n">
+      <c r="I22" s="33" t="n">
         <v>49.8</v>
       </c>
-      <c r="J22" s="20" t="n">
+      <c r="J22" s="33" t="n">
         <v>869.04</v>
       </c>
       <c r="K22" s="22" t="n">
         <v>34.42</v>
       </c>
       <c r="L22" s="22" t="n">
-        <v>-7.31</v>
+        <v>-9.02</v>
       </c>
       <c r="M22" s="22" t="n">
         <v>2.15</v>
@@ -2344,10 +2364,10 @@
         <v>0.95</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>40.82</v>
+        <v>41.77</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>-6.4</v>
+        <v>-7.35</v>
       </c>
       <c r="Q22" s="22" t="n">
         <v>3.18</v>
@@ -2385,23 +2405,23 @@
       <c r="F23" s="19" t="n">
         <v>46254</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="33" t="n">
         <v>125.22</v>
       </c>
       <c r="H23" s="21" t="n">
         <v>12.9</v>
       </c>
-      <c r="I23" s="20" t="n">
+      <c r="I23" s="33" t="n">
         <v>119.58</v>
       </c>
-      <c r="J23" s="20" t="n">
+      <c r="J23" s="33" t="n">
         <v>1542.58</v>
       </c>
       <c r="K23" s="22" t="n">
         <v>-4.51</v>
       </c>
       <c r="L23" s="22" t="n">
-        <v>-5.08</v>
+        <v>-6.2</v>
       </c>
       <c r="M23" s="22" t="n">
         <v>-4.51</v>
@@ -2410,10 +2430,10 @@
         <v>1.69</v>
       </c>
       <c r="O23" s="22" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="P23" s="22" t="n">
-        <v>-6.82</v>
+        <v>-7.51</v>
       </c>
       <c r="Q23" s="22" t="n">
         <v>3.71</v>
@@ -2457,23 +2477,23 @@
       <c r="F24" s="19" t="n">
         <v>46261</v>
       </c>
-      <c r="G24" s="20" t="n">
+      <c r="G24" s="33" t="n">
         <v>38.87</v>
       </c>
       <c r="H24" s="21" t="n">
         <v>45</v>
       </c>
-      <c r="I24" s="20" t="n">
+      <c r="I24" s="33" t="n">
         <v>34.3</v>
       </c>
-      <c r="J24" s="20" t="n">
+      <c r="J24" s="33" t="n">
         <v>1543.55</v>
       </c>
       <c r="K24" s="22" t="n">
         <v>-11.76</v>
       </c>
       <c r="L24" s="22" t="n">
-        <v>-11.87</v>
+        <v>-13.43</v>
       </c>
       <c r="M24" s="22" t="n">
         <v>-11.76</v>
@@ -2482,10 +2502,10 @@
         <v>1.69</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>1.59</v>
+        <v>2.28</v>
       </c>
       <c r="P24" s="22" t="n">
-        <v>-13.35</v>
+        <v>-14.04</v>
       </c>
       <c r="Q24" s="22" t="n">
         <v>7.05</v>
@@ -2529,23 +2549,23 @@
       <c r="F25" s="19" t="n">
         <v>45621</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="33" t="n">
         <v>17.92</v>
       </c>
       <c r="H25" s="21" t="n">
         <v>28.702979</v>
       </c>
-      <c r="I25" s="20" t="n">
+      <c r="I25" s="33" t="n">
         <v>20.96</v>
       </c>
-      <c r="J25" s="20" t="n">
+      <c r="J25" s="33" t="n">
         <v>601.61</v>
       </c>
       <c r="K25" s="22" t="n">
         <v>16.99</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>-1.24</v>
+        <v>-0.91</v>
       </c>
       <c r="M25" s="22" t="n">
         <v>0.77</v>
@@ -2554,10 +2574,10 @@
         <v>0.66</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="P25" s="22" t="n">
-        <v>-2.81</v>
+        <v>-3.61</v>
       </c>
       <c r="Q25" s="22" t="n">
         <v>11.45</v>
@@ -2601,23 +2621,23 @@
       <c r="F26" s="19" t="n">
         <v>46273</v>
       </c>
-      <c r="G26" s="20" t="n">
+      <c r="G26" s="33" t="n">
         <v>108.3</v>
       </c>
       <c r="H26" s="21" t="n">
         <v>10.5</v>
       </c>
-      <c r="I26" s="20" t="n">
+      <c r="I26" s="33" t="n">
         <v>97.11</v>
       </c>
-      <c r="J26" s="20" t="n">
+      <c r="J26" s="33" t="n">
         <v>1019.66</v>
       </c>
       <c r="K26" s="22" t="n">
         <v>-10.33</v>
       </c>
       <c r="L26" s="22" t="n">
-        <v>-19.18</v>
+        <v>-20.12</v>
       </c>
       <c r="M26" s="22" t="n">
         <v>-10.33</v>
@@ -2626,10 +2646,10 @@
         <v>1.12</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="P26" s="22" t="n">
-        <v>-12.03</v>
+        <v>-12.71</v>
       </c>
       <c r="Q26" s="22" t="n">
         <v>5.35</v>
@@ -2661,23 +2681,23 @@
       <c r="F27" s="19" t="n">
         <v>45621</v>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="33" t="n">
         <v>58.55</v>
       </c>
       <c r="H27" s="21" t="n">
         <v>5.678723</v>
       </c>
-      <c r="I27" s="20" t="n">
+      <c r="I27" s="33" t="n">
         <v>64.91</v>
       </c>
-      <c r="J27" s="20" t="n">
+      <c r="J27" s="33" t="n">
         <v>368.59</v>
       </c>
       <c r="K27" s="22" t="n">
         <v>10.85</v>
       </c>
       <c r="L27" s="22" t="n">
-        <v>-5.77</v>
+        <v>-4.16</v>
       </c>
       <c r="M27" s="22" t="n">
         <v>0.49</v>
@@ -2686,10 +2706,10 @@
         <v>0.4</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="P27" s="22" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.75</v>
       </c>
       <c r="Q27" s="22" t="n"/>
       <c r="R27" s="22" t="n"/>
@@ -2717,35 +2737,35 @@
       <c r="F28" s="19" t="n">
         <v>45623</v>
       </c>
-      <c r="G28" s="20" t="n">
+      <c r="G28" s="33" t="n">
         <v>490.01</v>
       </c>
       <c r="H28" s="21" t="n">
         <v>1.234883</v>
       </c>
-      <c r="I28" s="20" t="n">
+      <c r="I28" s="33" t="n">
         <v>551</v>
       </c>
-      <c r="J28" s="20" t="n">
+      <c r="J28" s="33" t="n">
         <v>680.42</v>
       </c>
       <c r="K28" s="22" t="n">
         <v>12.45</v>
       </c>
       <c r="L28" s="22" t="n">
-        <v>-2.12</v>
+        <v>-2.25</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="N28" s="22" t="n">
         <v>0.75</v>
       </c>
       <c r="O28" s="22" t="n">
-        <v>19.74</v>
+        <v>20.54</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>-7.29</v>
+        <v>-8.09</v>
       </c>
       <c r="Q28" s="22" t="n"/>
       <c r="R28" s="22" t="n"/>
@@ -2781,23 +2801,23 @@
       <c r="F29" s="19" t="n">
         <v>46033</v>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="33" t="n">
         <v>977.3</v>
       </c>
       <c r="H29" s="21" t="n">
         <v>3.09</v>
       </c>
-      <c r="I29" s="20" t="n">
+      <c r="I29" s="33" t="n">
         <v>977.8099999999999</v>
       </c>
-      <c r="J29" s="20" t="n">
+      <c r="J29" s="33" t="n">
         <v>3021.42</v>
       </c>
       <c r="K29" s="22" t="n">
         <v>5.47</v>
       </c>
       <c r="L29" s="22" t="n">
-        <v>-16.26</v>
+        <v>-14.91</v>
       </c>
       <c r="M29" s="22" t="n">
         <v>0.68</v>
@@ -2806,10 +2826,10 @@
         <v>3.31</v>
       </c>
       <c r="O29" s="22" t="n">
-        <v>12.9</v>
+        <v>13.66</v>
       </c>
       <c r="P29" s="22" t="n">
-        <v>-7.43</v>
+        <v>-8.19</v>
       </c>
       <c r="Q29" s="22" t="n">
         <v>3.09</v>
@@ -2853,23 +2873,23 @@
       <c r="F30" s="19" t="n">
         <v>45720</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="33" t="n">
         <v>259.8</v>
       </c>
       <c r="H30" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="I30" s="20" t="n">
+      <c r="I30" s="33" t="n">
         <v>326.33</v>
       </c>
-      <c r="J30" s="20" t="n">
+      <c r="J30" s="33" t="n">
         <v>130.54</v>
       </c>
       <c r="K30" s="22" t="n">
         <v>25.62</v>
       </c>
       <c r="L30" s="22" t="n">
-        <v>4.88</v>
+        <v>6.7</v>
       </c>
       <c r="M30" s="22" t="n">
         <v>1.42</v>
@@ -2878,10 +2898,10 @@
         <v>0.14</v>
       </c>
       <c r="O30" s="22" t="n">
-        <v>24.63</v>
+        <v>25.47</v>
       </c>
       <c r="P30" s="22" t="n">
-        <v>0.99</v>
+        <v>0.15</v>
       </c>
       <c r="Q30" s="22" t="n">
         <v>0.42</v>
@@ -2917,23 +2937,23 @@
       <c r="F31" s="19" t="n">
         <v>45622</v>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="33" t="n">
         <v>232.04</v>
       </c>
       <c r="H31" s="21" t="n">
         <v>3.1</v>
       </c>
-      <c r="I31" s="20" t="n">
+      <c r="I31" s="33" t="n">
         <v>344.29</v>
       </c>
-      <c r="J31" s="20" t="n">
+      <c r="J31" s="33" t="n">
         <v>1067.29</v>
       </c>
       <c r="K31" s="22" t="n">
         <v>48.37</v>
       </c>
       <c r="L31" s="22" t="n">
-        <v>-6.91</v>
+        <v>-3.79</v>
       </c>
       <c r="M31" s="22" t="n">
         <v>2.2</v>
@@ -2942,10 +2962,10 @@
         <v>1.17</v>
       </c>
       <c r="O31" s="22" t="n">
-        <v>19.01</v>
+        <v>19.82</v>
       </c>
       <c r="P31" s="22" t="n">
-        <v>29.36</v>
+        <v>28.55</v>
       </c>
       <c r="Q31" s="22" t="n"/>
       <c r="R31" s="22" t="n"/>
@@ -2981,23 +3001,23 @@
       <c r="F32" s="19" t="n">
         <v>45757</v>
       </c>
-      <c r="G32" s="20" t="n">
+      <c r="G32" s="33" t="n">
         <v>46.77</v>
       </c>
       <c r="H32" s="21" t="n">
         <v>25.9</v>
       </c>
-      <c r="I32" s="20" t="n">
+      <c r="I32" s="33" t="n">
         <v>53.26</v>
       </c>
-      <c r="J32" s="20" t="n">
+      <c r="J32" s="33" t="n">
         <v>1379.43</v>
       </c>
       <c r="K32" s="22" t="n">
         <v>13.88</v>
       </c>
       <c r="L32" s="22" t="n">
-        <v>-7.69</v>
+        <v>-8.68</v>
       </c>
       <c r="M32" s="22" t="n">
         <v>0.82</v>
@@ -3006,10 +3026,10 @@
         <v>1.51</v>
       </c>
       <c r="O32" s="22" t="n">
-        <v>42.18</v>
+        <v>43.14</v>
       </c>
       <c r="P32" s="22" t="n">
-        <v>-28.3</v>
+        <v>-29.26</v>
       </c>
       <c r="Q32" s="22" t="n">
         <v>3.93</v>
@@ -3053,35 +3073,35 @@
       <c r="F33" s="19" t="n">
         <v>46139</v>
       </c>
-      <c r="G33" s="20" t="n">
+      <c r="G33" s="33" t="n">
         <v>72.2</v>
       </c>
       <c r="H33" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="I33" s="20" t="n">
+      <c r="I33" s="33" t="n">
         <v>78.55</v>
       </c>
-      <c r="J33" s="20" t="n">
+      <c r="J33" s="33" t="n">
         <v>1885.2</v>
       </c>
       <c r="K33" s="22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>-2.65</v>
+        <v>-2.31</v>
       </c>
       <c r="M33" s="22" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="N33" s="22" t="n">
         <v>2.07</v>
       </c>
       <c r="O33" s="22" t="n">
-        <v>10.48</v>
+        <v>11.23</v>
       </c>
       <c r="P33" s="22" t="n">
-        <v>-1.68</v>
+        <v>-2.43</v>
       </c>
       <c r="Q33" s="22" t="n">
         <v>1.88</v>
@@ -3125,23 +3145,23 @@
       <c r="F34" s="19" t="n">
         <v>45682</v>
       </c>
-      <c r="G34" s="20" t="n">
+      <c r="G34" s="33" t="n">
         <v>37.28</v>
       </c>
       <c r="H34" s="21" t="n">
         <v>35</v>
       </c>
-      <c r="I34" s="20" t="n">
+      <c r="I34" s="33" t="n">
         <v>49.01</v>
       </c>
-      <c r="J34" s="20" t="n">
+      <c r="J34" s="33" t="n">
         <v>1715.35</v>
       </c>
       <c r="K34" s="22" t="n">
         <v>40.76</v>
       </c>
       <c r="L34" s="22" t="n">
-        <v>-11.04</v>
+        <v>-7.37</v>
       </c>
       <c r="M34" s="22" t="n">
         <v>2.04</v>
@@ -3150,10 +3170,10 @@
         <v>1.88</v>
       </c>
       <c r="O34" s="22" t="n">
-        <v>19.51</v>
+        <v>20.31</v>
       </c>
       <c r="P34" s="22" t="n">
-        <v>21.25</v>
+        <v>20.45</v>
       </c>
       <c r="Q34" s="22" t="n">
         <v>2.6</v>
@@ -3197,23 +3217,23 @@
       <c r="F35" s="19" t="n">
         <v>45663</v>
       </c>
-      <c r="G35" s="20" t="n">
+      <c r="G35" s="33" t="n">
         <v>30.41</v>
       </c>
       <c r="H35" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="I35" s="20" t="n">
+      <c r="I35" s="33" t="n">
         <v>59.24</v>
       </c>
-      <c r="J35" s="20" t="n">
+      <c r="J35" s="33" t="n">
         <v>829.36</v>
       </c>
       <c r="K35" s="22" t="n">
         <v>94.84</v>
       </c>
       <c r="L35" s="22" t="n">
-        <v>2.84</v>
+        <v>0.51</v>
       </c>
       <c r="M35" s="22" t="n">
         <v>4.74</v>
@@ -3222,10 +3242,10 @@
         <v>0.91</v>
       </c>
       <c r="O35" s="22" t="n">
-        <v>17.14</v>
+        <v>17.93</v>
       </c>
       <c r="P35" s="22" t="n">
-        <v>77.7</v>
+        <v>76.91</v>
       </c>
       <c r="Q35" s="22" t="n">
         <v>-10.92</v>
@@ -3267,23 +3287,23 @@
       <c r="F36" s="19" t="n">
         <v>46197</v>
       </c>
-      <c r="G36" s="20" t="n">
+      <c r="G36" s="33" t="n">
         <v>135.15</v>
       </c>
       <c r="H36" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="I36" s="20" t="n">
+      <c r="I36" s="33" t="n">
         <v>205.36</v>
       </c>
-      <c r="J36" s="20" t="n">
+      <c r="J36" s="33" t="n">
         <v>1642.84</v>
       </c>
       <c r="K36" s="22" t="n">
         <v>51.95</v>
       </c>
       <c r="L36" s="22" t="n">
-        <v>-7.15</v>
+        <v>-8.59</v>
       </c>
       <c r="M36" s="22" t="n">
         <v>17.32</v>
@@ -3292,10 +3312,10 @@
         <v>1.8</v>
       </c>
       <c r="O36" s="22" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="P36" s="22" t="n">
-        <v>48.6</v>
+        <v>47.9</v>
       </c>
       <c r="Q36" s="22" t="n">
         <v>7.48</v>
@@ -3339,23 +3359,23 @@
       <c r="F37" s="19" t="n">
         <v>45632</v>
       </c>
-      <c r="G37" s="20" t="n">
+      <c r="G37" s="33" t="n">
         <v>156</v>
       </c>
       <c r="H37" s="21" t="n">
         <v>1.04</v>
       </c>
-      <c r="I37" s="20" t="n">
+      <c r="I37" s="33" t="n">
         <v>192.14</v>
       </c>
-      <c r="J37" s="20" t="n">
+      <c r="J37" s="33" t="n">
         <v>199.83</v>
       </c>
       <c r="K37" s="22" t="n">
         <v>23.17</v>
       </c>
       <c r="L37" s="22" t="n">
-        <v>-5.41</v>
+        <v>-5.25</v>
       </c>
       <c r="M37" s="22" t="n">
         <v>1.1</v>
@@ -3364,10 +3384,10 @@
         <v>0.22</v>
       </c>
       <c r="O37" s="22" t="n">
-        <v>18.96</v>
+        <v>19.76</v>
       </c>
       <c r="P37" s="22" t="n">
-        <v>4.21</v>
+        <v>3.41</v>
       </c>
       <c r="Q37" s="22" t="n">
         <v>2.65</v>
@@ -3411,23 +3431,23 @@
       <c r="F38" s="19" t="n">
         <v>46273</v>
       </c>
-      <c r="G38" s="20" t="n">
+      <c r="G38" s="33" t="n">
         <v>5.63</v>
       </c>
       <c r="H38" s="21" t="n">
         <v>250</v>
       </c>
-      <c r="I38" s="20" t="n">
+      <c r="I38" s="33" t="n">
         <v>5.91</v>
       </c>
-      <c r="J38" s="20" t="n">
+      <c r="J38" s="33" t="n">
         <v>1477.5</v>
       </c>
       <c r="K38" s="22" t="n">
         <v>4.97</v>
       </c>
       <c r="L38" s="22" t="n">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="M38" s="22" t="n">
         <v>4.97</v>
@@ -3436,10 +3456,10 @@
         <v>1.62</v>
       </c>
       <c r="O38" s="22" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="P38" s="22" t="n">
-        <v>3.27</v>
+        <v>2.59</v>
       </c>
       <c r="Q38" s="22" t="n">
         <v>18.4</v>
@@ -3483,23 +3503,23 @@
       <c r="F39" s="19" t="n">
         <v>45721</v>
       </c>
-      <c r="G39" s="20" t="n">
+      <c r="G39" s="33" t="n">
         <v>33.18</v>
       </c>
       <c r="H39" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="I39" s="20" t="n">
+      <c r="I39" s="33" t="n">
         <v>54.61</v>
       </c>
-      <c r="J39" s="20" t="n">
+      <c r="J39" s="33" t="n">
         <v>1310.64</v>
       </c>
       <c r="K39" s="22" t="n">
         <v>64.58</v>
       </c>
       <c r="L39" s="22" t="n">
-        <v>-2.89</v>
+        <v>-2.64</v>
       </c>
       <c r="M39" s="22" t="n">
         <v>3.59</v>
@@ -3508,10 +3528,10 @@
         <v>1.44</v>
       </c>
       <c r="O39" s="22" t="n">
-        <v>26.27</v>
+        <v>27.12</v>
       </c>
       <c r="P39" s="22" t="n">
-        <v>38.31</v>
+        <v>37.46</v>
       </c>
       <c r="Q39" s="22" t="n">
         <v>1.46</v>
@@ -3555,23 +3575,23 @@
       <c r="F40" s="19" t="n">
         <v>46258</v>
       </c>
-      <c r="G40" s="20" t="n">
+      <c r="G40" s="33" t="n">
         <v>99.09</v>
       </c>
       <c r="H40" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="20" t="n">
+      <c r="I40" s="33" t="n">
         <v>284.16</v>
       </c>
-      <c r="J40" s="20" t="n">
+      <c r="J40" s="33" t="n">
         <v>568.33</v>
       </c>
       <c r="K40" s="22" t="n">
         <v>186.78</v>
       </c>
       <c r="L40" s="22" t="n">
-        <v>-2.86</v>
+        <v>4.63</v>
       </c>
       <c r="M40" s="22" t="n">
         <v>186.78</v>
@@ -3580,10 +3600,10 @@
         <v>0.62</v>
       </c>
       <c r="O40" s="22" t="n">
-        <v>2.72</v>
+        <v>3.41</v>
       </c>
       <c r="P40" s="22" t="n">
-        <v>184.06</v>
+        <v>183.37</v>
       </c>
       <c r="Q40" s="22" t="n">
         <v>1.69</v>
@@ -3627,23 +3647,23 @@
       <c r="F41" s="19" t="n">
         <v>46127</v>
       </c>
-      <c r="G41" s="20" t="n">
+      <c r="G41" s="33" t="n">
         <v>48.81</v>
       </c>
       <c r="H41" s="21" t="n">
         <v>48.4</v>
       </c>
-      <c r="I41" s="20" t="n">
+      <c r="I41" s="33" t="n">
         <v>54.26</v>
       </c>
-      <c r="J41" s="20" t="n">
+      <c r="J41" s="33" t="n">
         <v>2625.95</v>
       </c>
       <c r="K41" s="22" t="n">
         <v>11.15</v>
       </c>
       <c r="L41" s="22" t="n">
-        <v>-1.84</v>
+        <v>-2.33</v>
       </c>
       <c r="M41" s="22" t="n">
         <v>2.23</v>
@@ -3652,10 +3672,10 @@
         <v>2.88</v>
       </c>
       <c r="O41" s="22" t="n">
-        <v>13.94</v>
+        <v>14.71</v>
       </c>
       <c r="P41" s="22" t="n">
-        <v>-2.79</v>
+        <v>-3.56</v>
       </c>
       <c r="Q41" s="22" t="n">
         <v>5.79</v>
@@ -3699,23 +3719,23 @@
       <c r="F42" s="19" t="n">
         <v>45757</v>
       </c>
-      <c r="G42" s="20" t="n">
+      <c r="G42" s="33" t="n">
         <v>147.77</v>
       </c>
       <c r="H42" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="I42" s="20" t="n">
+      <c r="I42" s="33" t="n">
         <v>394.91</v>
       </c>
-      <c r="J42" s="20" t="n">
+      <c r="J42" s="33" t="n">
         <v>3159.31</v>
       </c>
       <c r="K42" s="22" t="n">
         <v>167.25</v>
       </c>
       <c r="L42" s="22" t="n">
-        <v>5.46</v>
+        <v>7.93</v>
       </c>
       <c r="M42" s="22" t="n">
         <v>9.84</v>
@@ -3724,10 +3744,10 @@
         <v>3.47</v>
       </c>
       <c r="O42" s="22" t="n">
-        <v>42.18</v>
+        <v>43.14</v>
       </c>
       <c r="P42" s="22" t="n">
-        <v>125.07</v>
+        <v>124.11</v>
       </c>
       <c r="Q42" s="22" t="n">
         <v>1.34</v>
@@ -3771,23 +3791,23 @@
       <c r="F43" s="19" t="n">
         <v>46041</v>
       </c>
-      <c r="G43" s="20" t="n">
+      <c r="G43" s="33" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="H43" s="21" t="n">
         <v>15.2</v>
       </c>
-      <c r="I43" s="20" t="n">
+      <c r="I43" s="33" t="n">
         <v>73.7</v>
       </c>
-      <c r="J43" s="20" t="n">
+      <c r="J43" s="33" t="n">
         <v>1120.24</v>
       </c>
       <c r="K43" s="22" t="n">
         <v>1.8</v>
       </c>
       <c r="L43" s="22" t="n">
-        <v>-2.59</v>
+        <v>-2.74</v>
       </c>
       <c r="M43" s="22" t="n">
         <v>0.23</v>
@@ -3796,10 +3816,10 @@
         <v>1.23</v>
       </c>
       <c r="O43" s="22" t="n">
-        <v>14.57</v>
+        <v>15.34</v>
       </c>
       <c r="P43" s="22" t="n">
-        <v>-12.77</v>
+        <v>-13.54</v>
       </c>
       <c r="Q43" s="22" t="n">
         <v>6.17</v>
@@ -3843,23 +3863,23 @@
       <c r="F44" s="19" t="n">
         <v>45642</v>
       </c>
-      <c r="G44" s="20" t="n">
+      <c r="G44" s="33" t="n">
         <v>186.62</v>
       </c>
       <c r="H44" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="20" t="n">
+      <c r="I44" s="33" t="n">
         <v>290.82</v>
       </c>
-      <c r="J44" s="20" t="n">
+      <c r="J44" s="33" t="n">
         <v>581.64</v>
       </c>
       <c r="K44" s="22" t="n">
         <v>55.83</v>
       </c>
       <c r="L44" s="22" t="n">
-        <v>-0.13</v>
+        <v>-0.28</v>
       </c>
       <c r="M44" s="22" t="n">
         <v>2.66</v>
@@ -3868,10 +3888,10 @@
         <v>0.64</v>
       </c>
       <c r="O44" s="22" t="n">
-        <v>18.41</v>
+        <v>19.21</v>
       </c>
       <c r="P44" s="22" t="n">
-        <v>37.42</v>
+        <v>36.62</v>
       </c>
       <c r="Q44" s="22" t="n">
         <v>5.5</v>
@@ -3915,35 +3935,35 @@
       <c r="F45" s="19" t="n">
         <v>45790</v>
       </c>
-      <c r="G45" s="20" t="n">
+      <c r="G45" s="33" t="n">
         <v>96.78</v>
       </c>
       <c r="H45" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="I45" s="20" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="J45" s="20" t="n">
+      <c r="I45" s="33" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="J45" s="33" t="n">
         <v>523.01</v>
       </c>
       <c r="K45" s="22" t="n">
-        <v>-44.26</v>
+        <v>-45.2</v>
       </c>
       <c r="L45" s="22" t="n">
-        <v>-8.08</v>
+        <v>-11.97</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>-2.77</v>
+        <v>-2.83</v>
       </c>
       <c r="N45" s="22" t="n">
         <v>0.57</v>
       </c>
       <c r="O45" s="22" t="n">
-        <v>28.28</v>
+        <v>29.14</v>
       </c>
       <c r="P45" s="22" t="n">
-        <v>-72.54000000000001</v>
+        <v>-74.34</v>
       </c>
       <c r="Q45" s="22" t="n">
         <v>8.74</v>
@@ -3987,35 +4007,35 @@
       <c r="F46" s="19" t="n">
         <v>46166</v>
       </c>
-      <c r="G46" s="20" t="n">
+      <c r="G46" s="33" t="n">
         <v>12.3</v>
       </c>
       <c r="H46" s="21" t="n">
         <v>181</v>
       </c>
-      <c r="I46" s="20" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="J46" s="20" t="n">
+      <c r="I46" s="33" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="J46" s="33" t="n">
         <v>2025.39</v>
       </c>
       <c r="K46" s="22" t="n">
-        <v>-7.07</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>-8.48</v>
+        <v>-8.18</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>-1.77</v>
+        <v>-2.19</v>
       </c>
       <c r="N46" s="22" t="n">
         <v>2.22</v>
       </c>
       <c r="O46" s="22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P46" s="22" t="n">
-        <v>-11.57</v>
+        <v>-13.98</v>
       </c>
       <c r="Q46" s="22" t="n">
         <v>7.07</v>
@@ -4059,35 +4079,35 @@
       <c r="F47" s="19" t="n">
         <v>46230</v>
       </c>
-      <c r="G47" s="20" t="n">
+      <c r="G47" s="33" t="n">
         <v>4.1</v>
       </c>
       <c r="H47" s="21" t="n">
         <v>478</v>
       </c>
-      <c r="I47" s="20" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="J47" s="20" t="n">
+      <c r="I47" s="33" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="J47" s="33" t="n">
         <v>2194.5</v>
       </c>
       <c r="K47" s="22" t="n">
-        <v>13.87</v>
+        <v>12.02</v>
       </c>
       <c r="L47" s="22" t="n">
-        <v>1.35</v>
+        <v>0.42</v>
       </c>
       <c r="M47" s="22" t="n">
-        <v>13.87</v>
+        <v>6.01</v>
       </c>
       <c r="N47" s="22" t="n">
         <v>2.41</v>
       </c>
       <c r="O47" s="22" t="n">
-        <v>3.78</v>
+        <v>4.48</v>
       </c>
       <c r="P47" s="22" t="n">
-        <v>10.09</v>
+        <v>7.54</v>
       </c>
       <c r="Q47" s="22" t="n">
         <v>6.5</v>
@@ -4125,35 +4145,35 @@
       <c r="F48" s="19" t="n">
         <v>45848</v>
       </c>
-      <c r="G48" s="20" t="n">
+      <c r="G48" s="33" t="n">
         <v>682.3</v>
       </c>
       <c r="H48" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="20" t="n">
-        <v>1527.2</v>
-      </c>
-      <c r="J48" s="20" t="n">
+      <c r="I48" s="33" t="n">
+        <v>1522.6</v>
+      </c>
+      <c r="J48" s="33" t="n">
         <v>1522.2</v>
       </c>
       <c r="K48" s="22" t="n">
-        <v>123.83</v>
+        <v>123.16</v>
       </c>
       <c r="L48" s="22" t="n">
-        <v>0.51</v>
+        <v>2.82</v>
       </c>
       <c r="M48" s="22" t="n">
-        <v>8.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N48" s="22" t="n">
         <v>1.67</v>
       </c>
       <c r="O48" s="22" t="n">
-        <v>27.11</v>
+        <v>27.97</v>
       </c>
       <c r="P48" s="22" t="n">
-        <v>96.72</v>
+        <v>95.19</v>
       </c>
       <c r="Q48" s="22" t="n">
         <v>1.88</v>
@@ -4197,35 +4217,35 @@
       <c r="F49" s="19" t="n">
         <v>46111</v>
       </c>
-      <c r="G49" s="20" t="n">
+      <c r="G49" s="33" t="n">
         <v>22.5</v>
       </c>
       <c r="H49" s="21" t="n">
         <v>90</v>
       </c>
-      <c r="I49" s="20" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="J49" s="20" t="n">
+      <c r="I49" s="33" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="J49" s="33" t="n">
         <v>2208.6</v>
       </c>
       <c r="K49" s="22" t="n">
-        <v>10.58</v>
+        <v>9.07</v>
       </c>
       <c r="L49" s="22" t="n">
-        <v>-5.03</v>
+        <v>-6.41</v>
       </c>
       <c r="M49" s="22" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="N49" s="22" t="n">
         <v>2.42</v>
       </c>
       <c r="O49" s="22" t="n">
-        <v>21.25</v>
+        <v>22.06</v>
       </c>
       <c r="P49" s="22" t="n">
-        <v>-10.67</v>
+        <v>-12.99</v>
       </c>
       <c r="Q49" s="22" t="n">
         <v>7.84</v>
@@ -4269,35 +4289,35 @@
       <c r="F50" s="19" t="n">
         <v>45848</v>
       </c>
-      <c r="G50" s="20" t="n">
+      <c r="G50" s="33" t="n">
         <v>146.72</v>
       </c>
       <c r="H50" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="I50" s="20" t="n">
-        <v>104.53</v>
-      </c>
-      <c r="J50" s="20" t="n">
+      <c r="I50" s="33" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="J50" s="33" t="n">
         <v>1045</v>
       </c>
       <c r="K50" s="22" t="n">
-        <v>-28.76</v>
+        <v>-28.78</v>
       </c>
       <c r="L50" s="22" t="n">
-        <v>-4.57</v>
+        <v>-4.52</v>
       </c>
       <c r="M50" s="22" t="n">
-        <v>-2.05</v>
+        <v>-2.06</v>
       </c>
       <c r="N50" s="22" t="n">
         <v>1.15</v>
       </c>
       <c r="O50" s="22" t="n">
-        <v>27.11</v>
+        <v>27.97</v>
       </c>
       <c r="P50" s="22" t="n">
-        <v>-55.87</v>
+        <v>-56.75</v>
       </c>
       <c r="Q50" s="22" t="n">
         <v>12.65</v>
@@ -4341,35 +4361,35 @@
       <c r="F51" s="19" t="n">
         <v>46092</v>
       </c>
-      <c r="G51" s="20" t="n">
+      <c r="G51" s="33" t="n">
         <v>104.01</v>
       </c>
       <c r="H51" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="I51" s="20" t="n">
-        <v>112.04</v>
-      </c>
-      <c r="J51" s="20" t="n">
+      <c r="I51" s="33" t="n">
+        <v>112</v>
+      </c>
+      <c r="J51" s="33" t="n">
         <v>2351.81</v>
       </c>
       <c r="K51" s="22" t="n">
-        <v>7.72</v>
+        <v>7.68</v>
       </c>
       <c r="L51" s="22" t="n">
-        <v>-1.71</v>
+        <v>-2.34</v>
       </c>
       <c r="M51" s="22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="N51" s="22" t="n">
         <v>2.58</v>
       </c>
       <c r="O51" s="22" t="n">
-        <v>15.96</v>
+        <v>16.74</v>
       </c>
       <c r="P51" s="22" t="n">
-        <v>-8.24</v>
+        <v>-9.06</v>
       </c>
       <c r="Q51" s="22" t="n">
         <v>4.74</v>
@@ -4413,35 +4433,35 @@
       <c r="F52" s="19" t="n">
         <v>45660</v>
       </c>
-      <c r="G52" s="20" t="n">
+      <c r="G52" s="33" t="n">
         <v>30.96</v>
       </c>
       <c r="H52" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="I52" s="20" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J52" s="20" t="n">
+      <c r="I52" s="33" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="J52" s="33" t="n">
         <v>334.65</v>
       </c>
       <c r="K52" s="22" t="n">
-        <v>-6.32</v>
+        <v>-5.92</v>
       </c>
       <c r="L52" s="22" t="n">
-        <v>-16.48</v>
+        <v>-14.19</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="N52" s="22" t="n">
         <v>0.37</v>
       </c>
       <c r="O52" s="22" t="n">
-        <v>18.56</v>
+        <v>19.36</v>
       </c>
       <c r="P52" s="22" t="n">
-        <v>-24.88</v>
+        <v>-25.28</v>
       </c>
       <c r="Q52" s="22" t="n">
         <v>7.95</v>
@@ -4485,35 +4505,35 @@
       <c r="F53" s="19" t="n">
         <v>46254</v>
       </c>
-      <c r="G53" s="20" t="n">
+      <c r="G53" s="33" t="n">
         <v>3.68</v>
       </c>
       <c r="H53" s="21" t="n">
         <v>426</v>
       </c>
-      <c r="I53" s="20" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="J53" s="20" t="n">
+      <c r="I53" s="33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J53" s="33" t="n">
         <v>1557.03</v>
       </c>
       <c r="K53" s="22" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="L53" s="22" t="n">
-        <v>-2.79</v>
+        <v>-2.53</v>
       </c>
       <c r="M53" s="22" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="N53" s="22" t="n">
         <v>1.71</v>
       </c>
       <c r="O53" s="22" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="P53" s="22" t="n">
-        <v>-2.31</v>
+        <v>-3.68</v>
       </c>
       <c r="Q53" s="22" t="n">
         <v>4.86</v>
@@ -4557,35 +4577,35 @@
       <c r="F54" s="19" t="n">
         <v>46165</v>
       </c>
-      <c r="G54" s="20" t="n">
+      <c r="G54" s="33" t="n">
         <v>14.43</v>
       </c>
       <c r="H54" s="21" t="n">
         <v>155</v>
       </c>
-      <c r="I54" s="20" t="n">
-        <v>17.55</v>
-      </c>
-      <c r="J54" s="20" t="n">
+      <c r="I54" s="33" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="J54" s="33" t="n">
         <v>2702.43</v>
       </c>
       <c r="K54" s="22" t="n">
-        <v>21.64</v>
+        <v>20.84</v>
       </c>
       <c r="L54" s="22" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="M54" s="22" t="n">
-        <v>5.41</v>
+        <v>5.21</v>
       </c>
       <c r="N54" s="22" t="n">
         <v>2.96</v>
       </c>
       <c r="O54" s="22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P54" s="22" t="n">
-        <v>17.14</v>
+        <v>15.64</v>
       </c>
       <c r="Q54" s="22" t="n">
         <v>20.28</v>
@@ -4623,35 +4643,35 @@
       <c r="F55" s="19" t="n">
         <v>46165</v>
       </c>
-      <c r="G55" s="20" t="n">
+      <c r="G55" s="33" t="n">
         <v>3.47</v>
       </c>
       <c r="H55" s="21" t="n">
         <v>239</v>
       </c>
-      <c r="I55" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J55" s="20" t="n">
+      <c r="I55" s="33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J55" s="33" t="n">
         <v>1123.78</v>
       </c>
       <c r="K55" s="22" t="n">
-        <v>29.86</v>
+        <v>35.53</v>
       </c>
       <c r="L55" s="22" t="n">
-        <v>2.48</v>
+        <v>1.12</v>
       </c>
       <c r="M55" s="22" t="n">
-        <v>7.46</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="N55" s="22" t="n">
         <v>1.23</v>
       </c>
       <c r="O55" s="22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P55" s="22" t="n">
-        <v>25.36</v>
+        <v>30.33</v>
       </c>
       <c r="Q55" s="22" t="n">
         <v>15.65</v>
@@ -4691,35 +4711,35 @@
       <c r="F56" s="19" t="n">
         <v>46146</v>
       </c>
-      <c r="G56" s="20" t="n">
+      <c r="G56" s="33" t="n">
         <v>54.5</v>
       </c>
       <c r="H56" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="I56" s="20" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="J56" s="20" t="n">
+      <c r="I56" s="33" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="J56" s="33" t="n">
         <v>549.5</v>
       </c>
       <c r="K56" s="22" t="n">
-        <v>0.55</v>
+        <v>0.83</v>
       </c>
       <c r="L56" s="22" t="n">
-        <v>-8.869999999999999</v>
+        <v>-7.72</v>
       </c>
       <c r="M56" s="22" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="N56" s="22" t="n">
         <v>0.6</v>
       </c>
       <c r="O56" s="22" t="n">
-        <v>9.140000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P56" s="22" t="n">
-        <v>-8.59</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="Q56" s="22" t="n">
         <v>1.63</v>
@@ -4761,35 +4781,35 @@
       <c r="F57" s="19" t="n">
         <v>45849</v>
       </c>
-      <c r="G57" s="20" t="n">
+      <c r="G57" s="33" t="n">
         <v>39.46</v>
       </c>
       <c r="H57" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="I57" s="20" t="n">
-        <v>63.46</v>
-      </c>
-      <c r="J57" s="20" t="n">
+      <c r="I57" s="33" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="J57" s="33" t="n">
         <v>1526.73</v>
       </c>
       <c r="K57" s="22" t="n">
-        <v>60.82</v>
+        <v>61.45</v>
       </c>
       <c r="L57" s="22" t="n">
-        <v>-7.79</v>
+        <v>-5.42</v>
       </c>
       <c r="M57" s="22" t="n">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="N57" s="22" t="n">
         <v>1.67</v>
       </c>
       <c r="O57" s="22" t="n">
-        <v>27.2</v>
+        <v>28.06</v>
       </c>
       <c r="P57" s="22" t="n">
-        <v>33.62</v>
+        <v>33.39</v>
       </c>
       <c r="Q57" s="22" t="n">
         <v>1.07</v>
@@ -4831,35 +4851,35 @@
       <c r="F58" s="19" t="n">
         <v>46265</v>
       </c>
-      <c r="G58" s="20" t="n">
+      <c r="G58" s="33" t="n">
         <v>4.15</v>
       </c>
       <c r="H58" s="21" t="n">
         <v>300</v>
       </c>
-      <c r="I58" s="20" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="J58" s="20" t="n">
+      <c r="I58" s="33" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="J58" s="33" t="n">
         <v>1188</v>
       </c>
       <c r="K58" s="22" t="n">
-        <v>-4.34</v>
+        <v>-4.58</v>
       </c>
       <c r="L58" s="22" t="n">
-        <v>-7.04</v>
+        <v>-5.6</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>-4.34</v>
+        <v>-4.58</v>
       </c>
       <c r="N58" s="22" t="n">
         <v>1.3</v>
       </c>
       <c r="O58" s="22" t="n">
-        <v>1.94</v>
+        <v>2.62</v>
       </c>
       <c r="P58" s="22" t="n">
-        <v>-6.28</v>
+        <v>-7.2</v>
       </c>
       <c r="Q58" s="22" t="n">
         <v>2.71</v>
@@ -4903,35 +4923,35 @@
       <c r="F59" s="19" t="n">
         <v>46257</v>
       </c>
-      <c r="G59" s="20" t="n">
+      <c r="G59" s="33" t="n">
         <v>6.48</v>
       </c>
       <c r="H59" s="21" t="n">
         <v>198</v>
       </c>
-      <c r="I59" s="20" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="J59" s="20" t="n">
+      <c r="I59" s="33" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J59" s="33" t="n">
         <v>1227.6</v>
       </c>
       <c r="K59" s="22" t="n">
-        <v>-3.44</v>
+        <v>-4.21</v>
       </c>
       <c r="L59" s="22" t="n">
-        <v>-3.72</v>
+        <v>-3.27</v>
       </c>
       <c r="M59" s="22" t="n">
-        <v>-3.44</v>
+        <v>-4.21</v>
       </c>
       <c r="N59" s="22" t="n">
         <v>1.35</v>
       </c>
       <c r="O59" s="22" t="n">
-        <v>2.72</v>
+        <v>3.41</v>
       </c>
       <c r="P59" s="22" t="n">
-        <v>-6.16</v>
+        <v>-7.62</v>
       </c>
       <c r="Q59" s="22" t="n">
         <v>-8.130000000000001</v>
@@ -4971,35 +4991,35 @@
       <c r="F60" s="19" t="n">
         <v>46122</v>
       </c>
-      <c r="G60" s="20" t="n">
+      <c r="G60" s="33" t="n">
         <v>225.75</v>
       </c>
       <c r="H60" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="I60" s="20" t="n">
-        <v>236.93</v>
-      </c>
-      <c r="J60" s="20" t="n">
+      <c r="I60" s="33" t="n">
+        <v>236.37</v>
+      </c>
+      <c r="J60" s="33" t="n">
         <v>2114.01</v>
       </c>
       <c r="K60" s="22" t="n">
-        <v>4.95</v>
+        <v>4.71</v>
       </c>
       <c r="L60" s="22" t="n">
-        <v>-4.37</v>
+        <v>-4.88</v>
       </c>
       <c r="M60" s="22" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N60" s="22" t="n">
         <v>2.32</v>
       </c>
       <c r="O60" s="22" t="n">
-        <v>15.55</v>
+        <v>16.33</v>
       </c>
       <c r="P60" s="22" t="n">
-        <v>-10.6</v>
+        <v>-11.62</v>
       </c>
       <c r="Q60" s="22" t="n">
         <v>4.44</v>
@@ -5043,35 +5063,35 @@
       <c r="F61" s="19" t="n">
         <v>45649</v>
       </c>
-      <c r="G61" s="20" t="n">
+      <c r="G61" s="33" t="n">
         <v>20.44</v>
       </c>
       <c r="H61" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="I61" s="20" t="n">
-        <v>65.84999999999999</v>
-      </c>
-      <c r="J61" s="20" t="n">
+      <c r="I61" s="33" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="J61" s="33" t="n">
         <v>999</v>
       </c>
       <c r="K61" s="22" t="n">
-        <v>222.16</v>
+        <v>226.08</v>
       </c>
       <c r="L61" s="22" t="n">
-        <v>9.08</v>
+        <v>10.9</v>
       </c>
       <c r="M61" s="22" t="n">
-        <v>10.58</v>
+        <v>10.77</v>
       </c>
       <c r="N61" s="22" t="n">
         <v>1.1</v>
       </c>
       <c r="O61" s="22" t="n">
-        <v>20.32</v>
+        <v>21.13</v>
       </c>
       <c r="P61" s="22" t="n">
-        <v>201.84</v>
+        <v>204.95</v>
       </c>
       <c r="Q61" s="22" t="n">
         <v>3.04</v>
@@ -5115,35 +5135,35 @@
       <c r="F62" s="19" t="n">
         <v>45883</v>
       </c>
-      <c r="G62" s="20" t="n">
+      <c r="G62" s="33" t="n">
         <v>40.49</v>
       </c>
       <c r="H62" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="I62" s="20" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="J62" s="20" t="n">
+      <c r="I62" s="33" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="J62" s="33" t="n">
         <v>3091.2</v>
       </c>
       <c r="K62" s="22" t="n">
-        <v>19.84</v>
+        <v>19.3</v>
       </c>
       <c r="L62" s="22" t="n">
-        <v>-2.83</v>
+        <v>-2.71</v>
       </c>
       <c r="M62" s="22" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="N62" s="22" t="n">
         <v>3.39</v>
       </c>
       <c r="O62" s="22" t="n">
-        <v>23.42</v>
+        <v>24.25</v>
       </c>
       <c r="P62" s="22" t="n">
-        <v>-3.58</v>
+        <v>-4.95</v>
       </c>
       <c r="Q62" s="22" t="n">
         <v>-3.53</v>
@@ -5185,35 +5205,35 @@
       <c r="F63" s="19" t="n">
         <v>46167</v>
       </c>
-      <c r="G63" s="20" t="n">
+      <c r="G63" s="33" t="n">
         <v>10.89</v>
       </c>
       <c r="H63" s="21" t="n">
         <v>193</v>
       </c>
-      <c r="I63" s="20" t="n">
-        <v>10.76</v>
-      </c>
-      <c r="J63" s="20" t="n">
+      <c r="I63" s="33" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="J63" s="33" t="n">
         <v>2072.82</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>-1.23</v>
+        <v>-0.31</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>-4.9</v>
+        <v>-6.86</v>
       </c>
       <c r="M63" s="22" t="n">
-        <v>-0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="N63" s="22" t="n">
         <v>2.27</v>
       </c>
       <c r="O63" s="22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P63" s="22" t="n">
-        <v>-5.73</v>
+        <v>-5.51</v>
       </c>
       <c r="Q63" s="22" t="n">
         <v>-5.5</v>
@@ -5255,35 +5275,35 @@
       <c r="F64" s="19" t="n">
         <v>46043</v>
       </c>
-      <c r="G64" s="20" t="n">
+      <c r="G64" s="33" t="n">
         <v>17.61</v>
       </c>
       <c r="H64" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="I64" s="20" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J64" s="20" t="n">
+      <c r="I64" s="33" t="n">
+        <v>22.96</v>
+      </c>
+      <c r="J64" s="33" t="n">
         <v>1836.8</v>
       </c>
       <c r="K64" s="22" t="n">
-        <v>32.86</v>
+        <v>30.36</v>
       </c>
       <c r="L64" s="22" t="n">
-        <v>-2.71</v>
+        <v>-3.77</v>
       </c>
       <c r="M64" s="22" t="n">
-        <v>4.11</v>
+        <v>3.79</v>
       </c>
       <c r="N64" s="22" t="n">
         <v>2.02</v>
       </c>
       <c r="O64" s="22" t="n">
-        <v>15.76</v>
+        <v>16.54</v>
       </c>
       <c r="P64" s="22" t="n">
-        <v>17.1</v>
+        <v>13.82</v>
       </c>
       <c r="Q64" s="22" t="n">
         <v>-3.85</v>
@@ -5325,35 +5345,35 @@
       <c r="F65" s="19" t="n">
         <v>45790</v>
       </c>
-      <c r="G65" s="20" t="n">
+      <c r="G65" s="33" t="n">
         <v>59.15</v>
       </c>
       <c r="H65" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="I65" s="20" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="J65" s="20" t="n">
+      <c r="I65" s="33" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="J65" s="33" t="n">
         <v>329.9</v>
       </c>
       <c r="K65" s="22" t="n">
-        <v>-36.12</v>
+        <v>-35.91</v>
       </c>
       <c r="L65" s="22" t="n">
-        <v>-12.6</v>
+        <v>-12.1</v>
       </c>
       <c r="M65" s="22" t="n">
-        <v>-2.26</v>
+        <v>-2.24</v>
       </c>
       <c r="N65" s="22" t="n">
         <v>0.36</v>
       </c>
       <c r="O65" s="22" t="n">
-        <v>28.28</v>
+        <v>29.14</v>
       </c>
       <c r="P65" s="22" t="n">
-        <v>-64.40000000000001</v>
+        <v>-65.05</v>
       </c>
       <c r="Q65" s="22" t="n">
         <v>8.92</v>
@@ -5397,35 +5417,35 @@
       <c r="F66" s="19" t="n">
         <v>46146</v>
       </c>
-      <c r="G66" s="20" t="n">
+      <c r="G66" s="33" t="n">
         <v>1396.6</v>
       </c>
       <c r="H66" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="20" t="n">
-        <v>975.9</v>
-      </c>
-      <c r="J66" s="20" t="n">
+      <c r="I66" s="33" t="n">
+        <v>983.3</v>
+      </c>
+      <c r="J66" s="33" t="n">
         <v>981.4</v>
       </c>
       <c r="K66" s="22" t="n">
-        <v>-30.12</v>
+        <v>-29.59</v>
       </c>
       <c r="L66" s="22" t="n">
-        <v>-16.26</v>
+        <v>-14.91</v>
       </c>
       <c r="M66" s="22" t="n">
-        <v>-7.53</v>
+        <v>-7.4</v>
       </c>
       <c r="N66" s="22" t="n">
         <v>1.08</v>
       </c>
       <c r="O66" s="22" t="n">
-        <v>9.140000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P66" s="22" t="n">
-        <v>-39.26</v>
+        <v>-39.46</v>
       </c>
       <c r="Q66" s="22" t="n">
         <v>3.09</v>
@@ -5469,23 +5489,23 @@
       <c r="F67" s="19" t="n">
         <v>46146</v>
       </c>
-      <c r="G67" s="20" t="n">
+      <c r="G67" s="33" t="n">
         <v>58.5</v>
       </c>
       <c r="H67" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="I67" s="20" t="n">
+      <c r="I67" s="33" t="n">
         <v>56.1</v>
       </c>
-      <c r="J67" s="20" t="n">
+      <c r="J67" s="33" t="n">
         <v>335.4</v>
       </c>
       <c r="K67" s="22" t="n">
         <v>-4.1</v>
       </c>
       <c r="L67" s="22" t="n">
-        <v>-5.08</v>
+        <v>-5.66</v>
       </c>
       <c r="M67" s="22" t="n">
         <v>-1.02</v>
@@ -5494,10 +5514,10 @@
         <v>0.37</v>
       </c>
       <c r="O67" s="22" t="n">
-        <v>9.140000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P67" s="22" t="n">
-        <v>-13.24</v>
+        <v>-13.97</v>
       </c>
       <c r="Q67" s="22" t="n">
         <v>-5.35</v>
@@ -5539,35 +5559,35 @@
       <c r="F68" s="19" t="n">
         <v>46019</v>
       </c>
-      <c r="G68" s="20" t="n">
+      <c r="G68" s="33" t="n">
         <v>31.33</v>
       </c>
       <c r="H68" s="21" t="n">
         <v>44</v>
       </c>
-      <c r="I68" s="20" t="n">
-        <v>30.62</v>
-      </c>
-      <c r="J68" s="20" t="n">
+      <c r="I68" s="33" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J68" s="33" t="n">
         <v>1333.2</v>
       </c>
       <c r="K68" s="22" t="n">
-        <v>-2.26</v>
+        <v>-3.28</v>
       </c>
       <c r="L68" s="22" t="n">
-        <v>-10.88</v>
+        <v>-9.01</v>
       </c>
       <c r="M68" s="22" t="n">
-        <v>-0.28</v>
+        <v>-0.41</v>
       </c>
       <c r="N68" s="22" t="n">
         <v>1.46</v>
       </c>
       <c r="O68" s="22" t="n">
-        <v>15.64</v>
+        <v>16.42</v>
       </c>
       <c r="P68" s="22" t="n">
-        <v>-17.9</v>
+        <v>-19.7</v>
       </c>
       <c r="Q68" s="22" t="n">
         <v>-1.57</v>
@@ -5601,23 +5621,23 @@
       <c r="F69" s="19" t="n">
         <v>46272</v>
       </c>
-      <c r="G69" s="20" t="n">
+      <c r="G69" s="33" t="n">
         <v>128.29</v>
       </c>
       <c r="H69" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I69" s="20" t="n">
+      <c r="I69" s="33" t="n">
         <v>131.36</v>
       </c>
-      <c r="J69" s="20" t="n">
+      <c r="J69" s="33" t="n">
         <v>393.88</v>
       </c>
       <c r="K69" s="22" t="n">
         <v>2.39</v>
       </c>
       <c r="L69" s="22" t="n">
-        <v>-0.62</v>
+        <v>-0.48</v>
       </c>
       <c r="M69" s="22" t="n">
         <v>2.39</v>
@@ -5626,10 +5646,10 @@
         <v>0.43</v>
       </c>
       <c r="O69" s="22" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="P69" s="22" t="n">
-        <v>0.89</v>
+        <v>0.21</v>
       </c>
       <c r="Q69" s="22" t="n"/>
       <c r="R69" s="22" t="n"/>
@@ -5663,7 +5683,7 @@
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
-      <c r="B76" s="29">
+      <c r="B76" s="34">
         <f>IFERROR(SUMPRODUCT(SUBTOTAL(109,OFFSET(INDEX(StockSummary[current_price],1),ROW(StockSummary[current_price])-MIN(ROW(StockSummary[current_price])),0,1)),StockSummary[quantity]),0)</f>
         <v/>
       </c>
@@ -5685,9 +5705,9 @@
     <row r="77" ht="15" customHeight="1" thickBot="1"/>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="I75:J75"/>
     <mergeCell ref="E75:F75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="E76:F76"/>
     <mergeCell ref="I76:J76"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:T69">
@@ -5876,16 +5896,16 @@
       <c r="F2" s="19" t="n">
         <v>46273</v>
       </c>
-      <c r="G2" s="20" t="n">
+      <c r="G2" s="33" t="n">
         <v>5.63</v>
       </c>
       <c r="H2" s="21" t="n">
         <v>250</v>
       </c>
-      <c r="I2" s="20" t="n">
+      <c r="I2" s="33" t="n">
         <v>5.91</v>
       </c>
-      <c r="J2" s="20" t="n">
+      <c r="J2" s="33" t="n">
         <v>1477.5</v>
       </c>
       <c r="K2" s="22" t="n">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Φύλλο1" sheetId="1" state="visible" r:id="rId1"/>
@@ -75,10 +75,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="009C5700"/>
+      <color rgb="00000000"/>
     </font>
     <font>
-      <color rgb="00000000"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -158,22 +158,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="005B9BD5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005B9BD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -453,31 +453,37 @@
     </xf>
     <xf numFmtId="166" fontId="6" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -492,25 +498,19 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -604,54 +604,54 @@
     <xf numFmtId="2" fontId="8" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="11" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="12" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="12" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -664,28 +664,28 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -693,22 +693,22 @@
     <xf numFmtId="168" fontId="8" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="9" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="21" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="11" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="12" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="12" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -855,8 +855,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StockSummary" displayName="StockSummary" ref="A1:V70" headerRowCount="1">
-  <autoFilter ref="A1:V70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StockSummary" displayName="StockSummary" ref="A1:V69" headerRowCount="1">
+  <autoFilter ref="A1:V69"/>
   <tableColumns count="22">
     <tableColumn id="1" name="symbol"/>
     <tableColumn id="2" name="name"/>
@@ -886,8 +886,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SoldSummary" displayName="SoldSummary" ref="A1:J14" headerRowCount="1">
-  <autoFilter ref="A1:J14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SoldSummary" displayName="SoldSummary" ref="A1:J16" headerRowCount="1">
+  <autoFilter ref="A1:J16"/>
   <tableColumns count="10">
     <tableColumn id="1" name="symbol"/>
     <tableColumn id="2" name="sector"/>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1290,353 +1290,353 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="86" t="inlineStr">
+      <c r="A2" s="79" t="inlineStr">
         <is>
           <t>VUAA.L</t>
         </is>
       </c>
-      <c r="B2" s="87" t="inlineStr">
+      <c r="B2" s="80" t="inlineStr">
         <is>
           <t>Vanguard S&amp;P 500 (Acc)</t>
         </is>
       </c>
-      <c r="C2" s="86" t="n"/>
-      <c r="D2" s="86" t="n"/>
-      <c r="E2" s="86" t="inlineStr">
+      <c r="C2" s="79" t="n"/>
+      <c r="D2" s="79" t="n"/>
+      <c r="E2" s="79" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F2" s="88" t="n">
+      <c r="F2" s="81" t="n">
         <v>46224</v>
       </c>
-      <c r="G2" s="145" t="n">
+      <c r="G2" s="144" t="n">
         <v>126.56</v>
       </c>
-      <c r="H2" s="90" t="n">
+      <c r="H2" s="83" t="n">
         <v>16.14269911</v>
       </c>
-      <c r="I2" s="145" t="n">
-        <v>134.63</v>
-      </c>
-      <c r="J2" s="145" t="n">
-        <v>2173.29</v>
-      </c>
-      <c r="K2" s="91" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="L2" s="91" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="M2" s="91" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N2" s="91" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O2" s="91" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="P2" s="91" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="Q2" s="91" t="n"/>
-      <c r="R2" s="91" t="n"/>
-      <c r="S2" s="91" t="n"/>
-      <c r="T2" s="91" t="n"/>
-      <c r="U2" s="91" t="n"/>
-      <c r="V2" s="92" t="n"/>
+      <c r="I2" s="144" t="n">
+        <v>134.74</v>
+      </c>
+      <c r="J2" s="144" t="n">
+        <v>2175.07</v>
+      </c>
+      <c r="K2" s="84" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="L2" s="84" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M2" s="84" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N2" s="84" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O2" s="84" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="P2" s="84" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q2" s="84" t="n"/>
+      <c r="R2" s="84" t="n"/>
+      <c r="S2" s="84" t="n"/>
+      <c r="T2" s="84" t="n"/>
+      <c r="U2" s="84" t="n"/>
+      <c r="V2" s="85" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="79" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>BSX</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="87" t="inlineStr">
         <is>
           <t>Boston Scientific</t>
         </is>
       </c>
-      <c r="C3" s="79" t="inlineStr">
+      <c r="C3" s="86" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="D3" s="79" t="inlineStr">
+      <c r="D3" s="86" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E3" s="79" t="inlineStr">
+      <c r="E3" s="86" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F3" s="81" t="n">
+      <c r="F3" s="88" t="n">
         <v>46261</v>
       </c>
-      <c r="G3" s="144" t="n">
+      <c r="G3" s="145" t="n">
         <v>40.46</v>
       </c>
-      <c r="H3" s="83" t="n">
+      <c r="H3" s="90" t="n">
         <v>47</v>
       </c>
-      <c r="I3" s="144" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="J3" s="144" t="n">
-        <v>1771.9</v>
-      </c>
-      <c r="K3" s="84" t="n">
-        <v>-6.82</v>
-      </c>
-      <c r="L3" s="84" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="M3" s="84" t="n">
-        <v>-6.82</v>
-      </c>
-      <c r="N3" s="84" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="O3" s="84" t="n">
+      <c r="I3" s="145" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="J3" s="145" t="n">
+        <v>1789.76</v>
+      </c>
+      <c r="K3" s="91" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="L3" s="91" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M3" s="91" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="N3" s="91" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O3" s="91" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="P3" s="91" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="Q3" s="91" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" s="91" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="S3" s="91" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="T3" s="91" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="U3" s="91" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="V3" s="92" t="n">
+        <v>53.03</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="86" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="C4" s="86" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D4" s="86" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E4" s="86" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F4" s="88" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G4" s="145" t="n">
+        <v>213.63</v>
+      </c>
+      <c r="H4" s="90" t="n">
+        <v>8.67721214</v>
+      </c>
+      <c r="I4" s="145" t="n">
+        <v>204.66</v>
+      </c>
+      <c r="J4" s="145" t="n">
+        <v>1775.88</v>
+      </c>
+      <c r="K4" s="91" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L4" s="91" t="n">
         <v>5.03</v>
       </c>
-      <c r="P3" s="84" t="n">
-        <v>-11.85</v>
-      </c>
-      <c r="Q3" s="84" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="R3" s="84" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="S3" s="84" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="T3" s="84" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="U3" s="84" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="V3" s="85" t="n">
-        <v>53.29</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="79" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B4" s="80" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="C4" s="79" t="inlineStr">
+      <c r="M4" s="91" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="N4" s="91" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O4" s="91" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="P4" s="91" t="n">
+        <v>-3.76</v>
+      </c>
+      <c r="Q4" s="91" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R4" s="91" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="S4" s="91" t="n">
+        <v>66.77</v>
+      </c>
+      <c r="T4" s="91" t="n">
+        <v>68.15000000000001</v>
+      </c>
+      <c r="U4" s="91" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="V4" s="92" t="n">
+        <v>75.31999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="86" t="inlineStr">
+        <is>
+          <t>EGLN.L</t>
+        </is>
+      </c>
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>iShares Physical Gold</t>
+        </is>
+      </c>
+      <c r="C5" s="86" t="n"/>
+      <c r="D5" s="86" t="n"/>
+      <c r="E5" s="86" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F5" s="88" t="n">
+        <v>45621</v>
+      </c>
+      <c r="G5" s="145" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="H5" s="90" t="n">
+        <v>17.014908</v>
+      </c>
+      <c r="I5" s="145" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="J5" s="145" t="n">
+        <v>1235.45</v>
+      </c>
+      <c r="K5" s="91" t="n">
+        <v>-10.55</v>
+      </c>
+      <c r="L5" s="91" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="M5" s="91" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="N5" s="91" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O5" s="91" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="P5" s="91" t="n">
+        <v>-34.54</v>
+      </c>
+      <c r="Q5" s="91" t="n"/>
+      <c r="R5" s="91" t="n"/>
+      <c r="S5" s="91" t="n"/>
+      <c r="T5" s="91" t="n"/>
+      <c r="U5" s="91" t="n"/>
+      <c r="V5" s="92" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="93" t="inlineStr">
+        <is>
+          <t>ROP</t>
+        </is>
+      </c>
+      <c r="B6" s="94" t="inlineStr">
+        <is>
+          <t>Roper Technologies</t>
+        </is>
+      </c>
+      <c r="C6" s="93" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D4" s="79" t="inlineStr">
+      <c r="D6" s="93" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E4" s="79" t="inlineStr">
+      <c r="E6" s="93" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F4" s="81" t="n">
-        <v>46301</v>
-      </c>
-      <c r="G4" s="144" t="n">
-        <v>215.24</v>
-      </c>
-      <c r="H4" s="83" t="n">
-        <v>5.87721214</v>
-      </c>
-      <c r="I4" s="144" t="n">
-        <v>215.19</v>
-      </c>
-      <c r="J4" s="144" t="n">
-        <v>1264.72</v>
-      </c>
-      <c r="K4" s="84" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L4" s="84" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="M4" s="84" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="N4" s="84" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O4" s="84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="84" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="Q4" s="84" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R4" s="84" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="S4" s="84" t="n">
-        <v>66.77</v>
-      </c>
-      <c r="T4" s="84" t="n">
-        <v>67</v>
-      </c>
-      <c r="U4" s="84" t="n">
-        <v>69.66</v>
-      </c>
-      <c r="V4" s="85" t="n">
-        <v>75.19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="79" t="inlineStr">
-        <is>
-          <t>EGLN.L</t>
-        </is>
-      </c>
-      <c r="B5" s="80" t="inlineStr">
-        <is>
-          <t>iShares Physical Gold</t>
-        </is>
-      </c>
-      <c r="C5" s="79" t="n"/>
-      <c r="D5" s="79" t="n"/>
-      <c r="E5" s="79" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F5" s="81" t="n">
-        <v>45621</v>
-      </c>
-      <c r="G5" s="144" t="n">
-        <v>81.17</v>
-      </c>
-      <c r="H5" s="83" t="n">
-        <v>17.014908</v>
-      </c>
-      <c r="I5" s="144" t="n">
-        <v>71.70999999999999</v>
-      </c>
-      <c r="J5" s="144" t="n">
-        <v>1220.14</v>
-      </c>
-      <c r="K5" s="84" t="n">
-        <v>-11.65</v>
-      </c>
-      <c r="L5" s="84" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="M5" s="84" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="N5" s="84" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O5" s="84" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="P5" s="84" t="n">
-        <v>-35.5</v>
-      </c>
-      <c r="Q5" s="84" t="n"/>
-      <c r="R5" s="84" t="n"/>
-      <c r="S5" s="84" t="n"/>
-      <c r="T5" s="84" t="n"/>
-      <c r="U5" s="84" t="n"/>
-      <c r="V5" s="85" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="86" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
-      <c r="B6" s="87" t="inlineStr">
-        <is>
-          <t>Roper Technologies</t>
-        </is>
-      </c>
-      <c r="C6" s="86" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D6" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E6" s="86" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F6" s="88" t="n">
+      <c r="F6" s="95" t="n">
         <v>46293</v>
       </c>
-      <c r="G6" s="145" t="n">
+      <c r="G6" s="146" t="n">
         <v>309.27</v>
       </c>
-      <c r="H6" s="90" t="n">
+      <c r="H6" s="97" t="n">
         <v>4.47586725</v>
       </c>
-      <c r="I6" s="145" t="n">
-        <v>322.96</v>
-      </c>
-      <c r="J6" s="145" t="n">
-        <v>1445.53</v>
-      </c>
-      <c r="K6" s="91" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="L6" s="91" t="n">
-        <v>-8.06</v>
-      </c>
-      <c r="M6" s="91" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="N6" s="91" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="O6" s="91" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" s="91" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q6" s="91" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="R6" s="91" t="n">
+      <c r="I6" s="146" t="n">
+        <v>324.96</v>
+      </c>
+      <c r="J6" s="146" t="n">
+        <v>1454.48</v>
+      </c>
+      <c r="K6" s="98" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="L6" s="98" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="M6" s="98" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="N6" s="98" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O6" s="98" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P6" s="98" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" s="98" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="R6" s="98" t="n">
         <v>6.72</v>
       </c>
-      <c r="S6" s="91" t="n">
+      <c r="S6" s="98" t="n">
         <v>6.08</v>
       </c>
-      <c r="T6" s="91" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="U6" s="91" t="n">
+      <c r="T6" s="98" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="U6" s="98" t="n">
         <v>9.73</v>
       </c>
-      <c r="V6" s="92" t="n">
-        <v>39.02</v>
+      <c r="V6" s="99" t="n">
+        <v>38.99</v>
       </c>
     </row>
     <row r="7">
@@ -1675,31 +1675,31 @@
         <v>190</v>
       </c>
       <c r="I7" s="144" t="n">
-        <v>7.12</v>
+        <v>7.63</v>
       </c>
       <c r="J7" s="144" t="n">
-        <v>1352.8</v>
+        <v>1449.7</v>
       </c>
       <c r="K7" s="84" t="n">
-        <v>-3.26</v>
+        <v>3.67</v>
       </c>
       <c r="L7" s="84" t="n">
-        <v>-11.69</v>
+        <v>5.3</v>
       </c>
       <c r="M7" s="84" t="n">
-        <v>-3.26</v>
+        <v>3.67</v>
       </c>
       <c r="N7" s="84" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="O7" s="84" t="n">
-        <v>-0.04</v>
+        <v>0.96</v>
       </c>
       <c r="P7" s="84" t="n">
-        <v>-3.22</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" s="84" t="n">
-        <v>16.85</v>
+        <v>15.79</v>
       </c>
       <c r="R7" s="84" t="n"/>
       <c r="S7" s="84" t="n">
@@ -1716,155 +1716,175 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="86" t="inlineStr">
-        <is>
-          <t>SXR8.DE</t>
-        </is>
-      </c>
-      <c r="B8" s="87" t="inlineStr">
-        <is>
-          <t>iShares Core S&amp;P 500 (Acc)</t>
-        </is>
-      </c>
-      <c r="C8" s="86" t="n"/>
-      <c r="D8" s="86" t="n"/>
-      <c r="E8" s="86" t="inlineStr">
+      <c r="A8" s="93" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B8" s="94" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C8" s="93" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D8" s="93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E8" s="93" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F8" s="88" t="n">
-        <v>45621</v>
-      </c>
-      <c r="G8" s="145" t="n">
-        <v>596.48</v>
-      </c>
-      <c r="H8" s="90" t="n">
-        <v>0.828825</v>
-      </c>
-      <c r="I8" s="145" t="n">
-        <v>750.91</v>
-      </c>
-      <c r="J8" s="145" t="n">
-        <v>622.37</v>
-      </c>
-      <c r="K8" s="91" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="L8" s="91" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="M8" s="91" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N8" s="91" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O8" s="91" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="P8" s="91" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q8" s="91" t="n"/>
-      <c r="R8" s="91" t="n"/>
-      <c r="S8" s="91" t="n"/>
-      <c r="T8" s="91" t="n"/>
-      <c r="U8" s="91" t="n"/>
-      <c r="V8" s="92" t="n"/>
+      <c r="F8" s="95" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G8" s="146" t="n">
+        <v>132.54</v>
+      </c>
+      <c r="H8" s="97" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" s="146" t="n">
+        <v>142.51</v>
+      </c>
+      <c r="J8" s="146" t="n">
+        <v>1710.12</v>
+      </c>
+      <c r="K8" s="98" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="L8" s="98" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M8" s="98" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="N8" s="98" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O8" s="98" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="P8" s="98" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="Q8" s="98" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R8" s="98" t="n">
+        <v>217.01</v>
+      </c>
+      <c r="S8" s="98" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="T8" s="98" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="U8" s="98" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="V8" s="99" t="n">
+        <v>67.26000000000001</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="86" t="inlineStr">
-        <is>
-          <t>RDDT</t>
-        </is>
-      </c>
-      <c r="B9" s="87" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C9" s="86" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D9" s="86" t="inlineStr">
+      <c r="A9" s="79" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B9" s="80" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C9" s="79" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D9" s="79" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E9" s="86" t="inlineStr">
+      <c r="E9" s="79" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F9" s="88" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G9" s="145" t="n">
-        <v>132.54</v>
-      </c>
-      <c r="H9" s="90" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="145" t="n">
-        <v>133.39</v>
-      </c>
-      <c r="J9" s="145" t="n">
-        <v>1600.68</v>
-      </c>
-      <c r="K9" s="91" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L9" s="91" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M9" s="91" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N9" s="91" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O9" s="91" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="P9" s="91" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="Q9" s="91" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="R9" s="91" t="n">
-        <v>217.01</v>
-      </c>
-      <c r="S9" s="91" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="T9" s="91" t="n">
-        <v>31.81</v>
-      </c>
-      <c r="U9" s="91" t="n">
-        <v>31.42</v>
-      </c>
-      <c r="V9" s="92" t="n">
-        <v>67.41</v>
+      <c r="F9" s="81" t="n">
+        <v>46170</v>
+      </c>
+      <c r="G9" s="144" t="n">
+        <v>206.93</v>
+      </c>
+      <c r="H9" s="83" t="n">
+        <v>5.95313343</v>
+      </c>
+      <c r="I9" s="144" t="n">
+        <v>216.21</v>
+      </c>
+      <c r="J9" s="144" t="n">
+        <v>1287.13</v>
+      </c>
+      <c r="K9" s="84" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="L9" s="84" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="M9" s="84" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N9" s="84" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O9" s="84" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="P9" s="84" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="Q9" s="84" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="R9" s="84" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="S9" s="84" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="T9" s="84" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="U9" s="84" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="V9" s="85" t="n">
+        <v>82.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="86" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B10" s="87" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Deckers Outdoor</t>
         </is>
       </c>
       <c r="C10" s="86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D10" s="86" t="inlineStr">
@@ -1878,71 +1898,71 @@
         </is>
       </c>
       <c r="F10" s="88" t="n">
-        <v>46170</v>
+        <v>46260</v>
       </c>
       <c r="G10" s="145" t="n">
-        <v>206.93</v>
+        <v>76.27</v>
       </c>
       <c r="H10" s="90" t="n">
-        <v>5.95313343</v>
+        <v>23</v>
       </c>
       <c r="I10" s="145" t="n">
-        <v>211.83</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="J10" s="145" t="n">
-        <v>1261.05</v>
+        <v>1703.61</v>
       </c>
       <c r="K10" s="91" t="n">
-        <v>2.37</v>
+        <v>-2.88</v>
       </c>
       <c r="L10" s="91" t="n">
-        <v>-7.26</v>
+        <v>1.99</v>
       </c>
       <c r="M10" s="91" t="n">
-        <v>0.59</v>
+        <v>-2.88</v>
       </c>
       <c r="N10" s="91" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="O10" s="91" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="P10" s="91" t="n">
+        <v>-8.92</v>
+      </c>
+      <c r="Q10" s="91" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="R10" s="91" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S10" s="91" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="T10" s="91" t="n">
         <v>7.23</v>
       </c>
-      <c r="P10" s="91" t="n">
-        <v>-4.86</v>
-      </c>
-      <c r="Q10" s="91" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="R10" s="91" t="n">
-        <v>25.14</v>
-      </c>
-      <c r="S10" s="91" t="n">
-        <v>39.85</v>
-      </c>
-      <c r="T10" s="91" t="n">
-        <v>9.18</v>
-      </c>
       <c r="U10" s="91" t="n">
-        <v>13.04</v>
+        <v>11.16</v>
       </c>
       <c r="V10" s="92" t="n">
-        <v>82.39</v>
+        <v>81.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="79" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>IMMR</t>
         </is>
       </c>
       <c r="B11" s="80" t="inlineStr">
         <is>
-          <t>Deckers Outdoor</t>
+          <t>Immersion</t>
         </is>
       </c>
       <c r="C11" s="79" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" s="79" t="inlineStr">
@@ -1956,371 +1976,371 @@
         </is>
       </c>
       <c r="F11" s="81" t="n">
-        <v>46260</v>
+        <v>45922</v>
       </c>
       <c r="G11" s="144" t="n">
-        <v>76.27</v>
+        <v>6.26</v>
       </c>
       <c r="H11" s="83" t="n">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="I11" s="144" t="n">
-        <v>72.31999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J11" s="144" t="n">
-        <v>1663.36</v>
+        <v>990</v>
       </c>
       <c r="K11" s="84" t="n">
-        <v>-5.18</v>
+        <v>5.43</v>
       </c>
       <c r="L11" s="84" t="n">
-        <v>-1.44</v>
+        <v>0.41</v>
       </c>
       <c r="M11" s="84" t="n">
-        <v>-5.18</v>
+        <v>0.45</v>
       </c>
       <c r="N11" s="84" t="n">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="O11" s="84" t="n">
-        <v>5.92</v>
+        <v>23.6</v>
       </c>
       <c r="P11" s="84" t="n">
-        <v>-11.1</v>
+        <v>-18.17</v>
       </c>
       <c r="Q11" s="84" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="R11" s="84" t="n">
-        <v>14.5</v>
-      </c>
+        <v>17.38</v>
+      </c>
+      <c r="R11" s="84" t="n"/>
       <c r="S11" s="84" t="n">
-        <v>39.01</v>
-      </c>
-      <c r="T11" s="84" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="U11" s="84" t="n">
-        <v>11.16</v>
-      </c>
+        <v>2.71</v>
+      </c>
+      <c r="T11" s="84" t="n"/>
+      <c r="U11" s="84" t="n"/>
       <c r="V11" s="85" t="n">
-        <v>81.92</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="86" t="inlineStr">
-        <is>
-          <t>IMMR</t>
-        </is>
-      </c>
-      <c r="B12" s="87" t="inlineStr">
-        <is>
-          <t>Immersion</t>
-        </is>
-      </c>
-      <c r="C12" s="86" t="inlineStr">
+      <c r="A12" s="93" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B12" s="94" t="inlineStr">
+        <is>
+          <t>Rocket Lab</t>
+        </is>
+      </c>
+      <c r="C12" s="93" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D12" s="93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E12" s="93" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F12" s="95" t="n">
+        <v>46262</v>
+      </c>
+      <c r="G12" s="146" t="n">
+        <v>56.32</v>
+      </c>
+      <c r="H12" s="97" t="n">
+        <v>26</v>
+      </c>
+      <c r="I12" s="146" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="J12" s="146" t="n">
+        <v>1582.1</v>
+      </c>
+      <c r="K12" s="98" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="L12" s="98" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="M12" s="98" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="N12" s="98" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O12" s="98" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P12" s="98" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Q12" s="98" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="R12" s="98" t="n"/>
+      <c r="S12" s="98" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="T12" s="98" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="U12" s="98" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="V12" s="99" t="n">
+        <v>35.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="100" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B13" s="101" t="inlineStr">
+        <is>
+          <t>Credo Technology</t>
+        </is>
+      </c>
+      <c r="C13" s="100" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D12" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E12" s="86" t="inlineStr">
+      <c r="D13" s="100" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="E13" s="100" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F12" s="88" t="n">
-        <v>45922</v>
-      </c>
-      <c r="G12" s="145" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="H12" s="90" t="n">
-        <v>150</v>
-      </c>
-      <c r="I12" s="145" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="J12" s="145" t="n">
-        <v>969</v>
-      </c>
-      <c r="K12" s="91" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="L12" s="91" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="M12" s="91" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="N12" s="91" t="n">
+      <c r="F13" s="102" t="n">
+        <v>46267</v>
+      </c>
+      <c r="G13" s="147" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="H13" s="104" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I13" s="147" t="n">
+        <v>192.87</v>
+      </c>
+      <c r="J13" s="147" t="n">
+        <v>115.72</v>
+      </c>
+      <c r="K13" s="105" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="L13" s="105" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="M13" s="105" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="N13" s="105" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O13" s="105" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="P13" s="105" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="Q13" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="91" t="n">
-        <v>23.45</v>
-      </c>
-      <c r="P12" s="91" t="n">
-        <v>-20.26</v>
-      </c>
-      <c r="Q12" s="91" t="n">
-        <v>17.74</v>
-      </c>
-      <c r="R12" s="91" t="n"/>
-      <c r="S12" s="91" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T12" s="91" t="n"/>
-      <c r="U12" s="91" t="n"/>
-      <c r="V12" s="92" t="n">
-        <v>52.17</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="93" t="inlineStr">
-        <is>
-          <t>RKLB</t>
-        </is>
-      </c>
-      <c r="B13" s="94" t="inlineStr">
-        <is>
-          <t>Rocket Lab</t>
-        </is>
-      </c>
-      <c r="C13" s="93" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D13" s="93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E13" s="93" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F13" s="95" t="n">
-        <v>46262</v>
-      </c>
-      <c r="G13" s="146" t="n">
-        <v>56.32</v>
-      </c>
-      <c r="H13" s="97" t="n">
-        <v>26</v>
-      </c>
-      <c r="I13" s="146" t="n">
-        <v>67.28</v>
-      </c>
-      <c r="J13" s="146" t="n">
-        <v>1749.28</v>
-      </c>
-      <c r="K13" s="98" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="L13" s="98" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="M13" s="98" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="N13" s="98" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O13" s="98" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="P13" s="98" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="Q13" s="98" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="R13" s="98" t="n"/>
-      <c r="S13" s="98" t="n">
-        <v>-12.2</v>
-      </c>
-      <c r="T13" s="98" t="n">
-        <v>41.62</v>
-      </c>
-      <c r="U13" s="98" t="n">
-        <v>68.11</v>
-      </c>
-      <c r="V13" s="99" t="n">
-        <v>35.45</v>
+      <c r="R13" s="105" t="n">
+        <v>1302.37</v>
+      </c>
+      <c r="S13" s="105" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="T13" s="105" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="U13" s="105" t="n">
+        <v>53.66</v>
+      </c>
+      <c r="V13" s="106" t="n">
+        <v>68.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="93" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>OPHC</t>
         </is>
       </c>
       <c r="B14" s="94" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>OptimumBank</t>
         </is>
       </c>
       <c r="C14" s="93" t="inlineStr">
         <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D14" s="93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E14" s="93" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F14" s="95" t="n">
+        <v>45922</v>
+      </c>
+      <c r="G14" s="146" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H14" s="97" t="n">
+        <v>145</v>
+      </c>
+      <c r="I14" s="146" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="J14" s="146" t="n">
+        <v>1125.2</v>
+      </c>
+      <c r="K14" s="98" t="n">
+        <v>116.76</v>
+      </c>
+      <c r="L14" s="98" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="M14" s="98" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="N14" s="98" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O14" s="98" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="P14" s="98" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="Q14" s="98" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="R14" s="98" t="n">
+        <v>15.93</v>
+      </c>
+      <c r="S14" s="98" t="n"/>
+      <c r="T14" s="98" t="n"/>
+      <c r="U14" s="98" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V14" s="99" t="n">
+        <v>62.86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="79" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C15" s="79" t="inlineStr">
+        <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D14" s="93" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="E14" s="93" t="inlineStr">
+      <c r="D15" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E15" s="79" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F14" s="95" t="n">
-        <v>46267</v>
-      </c>
-      <c r="G14" s="146" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="H14" s="97" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I14" s="146" t="n">
-        <v>198.35</v>
-      </c>
-      <c r="J14" s="146" t="n">
-        <v>119.01</v>
-      </c>
-      <c r="K14" s="98" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="L14" s="98" t="n">
-        <v>33</v>
-      </c>
-      <c r="M14" s="98" t="n">
-        <v>36.04</v>
-      </c>
-      <c r="N14" s="98" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O14" s="98" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="P14" s="98" t="n">
-        <v>30.95</v>
-      </c>
-      <c r="Q14" s="98" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="R14" s="98" t="n">
-        <v>1302.37</v>
-      </c>
-      <c r="S14" s="98" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="T14" s="98" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U14" s="98" t="n">
-        <v>53.66</v>
-      </c>
-      <c r="V14" s="99" t="n">
-        <v>68.48</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="100" t="inlineStr">
-        <is>
-          <t>OPHC</t>
-        </is>
-      </c>
-      <c r="B15" s="101" t="inlineStr">
-        <is>
-          <t>OptimumBank</t>
-        </is>
-      </c>
-      <c r="C15" s="100" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D15" s="100" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E15" s="100" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F15" s="102" t="n">
-        <v>45922</v>
-      </c>
-      <c r="G15" s="147" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="H15" s="104" t="n">
-        <v>145</v>
-      </c>
-      <c r="I15" s="147" t="n">
-        <v>7.71</v>
-      </c>
-      <c r="J15" s="147" t="n">
-        <v>1117.95</v>
-      </c>
-      <c r="K15" s="105" t="n">
-        <v>115.36</v>
-      </c>
-      <c r="L15" s="105" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="M15" s="105" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="N15" s="105" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="O15" s="105" t="n">
-        <v>23.45</v>
-      </c>
-      <c r="P15" s="105" t="n">
-        <v>91.91</v>
-      </c>
-      <c r="Q15" s="105" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="R15" s="105" t="n">
-        <v>15.93</v>
-      </c>
-      <c r="S15" s="105" t="n"/>
-      <c r="T15" s="105" t="n"/>
-      <c r="U15" s="105" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="V15" s="106" t="n">
-        <v>65.26000000000001</v>
+      <c r="F15" s="81" t="n">
+        <v>46140</v>
+      </c>
+      <c r="G15" s="144" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="H15" s="83" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="I15" s="144" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="J15" s="144" t="n">
+        <v>2270.03</v>
+      </c>
+      <c r="K15" s="84" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="L15" s="84" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="M15" s="84" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N15" s="84" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O15" s="84" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="P15" s="84" t="n">
+        <v>-4.94</v>
+      </c>
+      <c r="Q15" s="84" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="R15" s="84" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="S15" s="84" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="T15" s="84" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="U15" s="84" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="V15" s="85" t="n">
+        <v>57.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="86" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>NNE</t>
         </is>
       </c>
       <c r="B16" s="87" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>NANO Nuclear Energy</t>
         </is>
       </c>
       <c r="C16" s="86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D16" s="86" t="inlineStr">
@@ -2334,71 +2354,69 @@
         </is>
       </c>
       <c r="F16" s="88" t="n">
-        <v>46140</v>
+        <v>45621</v>
       </c>
       <c r="G16" s="145" t="n">
-        <v>91.79000000000001</v>
+        <v>23.74</v>
       </c>
       <c r="H16" s="90" t="n">
-        <v>22.46</v>
+        <v>204.17081927</v>
       </c>
       <c r="I16" s="145" t="n">
-        <v>97.02</v>
+        <v>13.69</v>
       </c>
       <c r="J16" s="145" t="n">
-        <v>2179.07</v>
+        <v>2795.1</v>
       </c>
       <c r="K16" s="91" t="n">
-        <v>5.7</v>
+        <v>-42.33</v>
       </c>
       <c r="L16" s="91" t="n">
-        <v>-5.28</v>
+        <v>-6.52</v>
       </c>
       <c r="M16" s="91" t="n">
-        <v>1.14</v>
+        <v>-1.92</v>
       </c>
       <c r="N16" s="91" t="n">
-        <v>2.24</v>
+        <v>2.92</v>
       </c>
       <c r="O16" s="91" t="n">
-        <v>14.92</v>
+        <v>23.99</v>
       </c>
       <c r="P16" s="91" t="n">
-        <v>-9.220000000000001</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="Q16" s="91" t="n">
-        <v>10.89</v>
-      </c>
-      <c r="R16" s="91" t="n">
-        <v>16.26</v>
-      </c>
+        <v>-4.51</v>
+      </c>
+      <c r="R16" s="91" t="n"/>
       <c r="S16" s="91" t="n">
-        <v>10.49</v>
+        <v>-20.22</v>
       </c>
       <c r="T16" s="91" t="n">
-        <v>3.57</v>
+        <v>459.93</v>
       </c>
       <c r="U16" s="91" t="n">
-        <v>6.91</v>
+        <v>-55.06</v>
       </c>
       <c r="V16" s="92" t="n">
-        <v>57.66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="79" t="inlineStr">
         <is>
-          <t>NNE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B17" s="80" t="inlineStr">
         <is>
-          <t>NANO Nuclear Energy</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="C17" s="79" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D17" s="79" t="inlineStr">
@@ -2412,457 +2430,455 @@
         </is>
       </c>
       <c r="F17" s="81" t="n">
-        <v>45621</v>
+        <v>46300</v>
       </c>
       <c r="G17" s="144" t="n">
-        <v>23.74</v>
+        <v>241.84</v>
       </c>
       <c r="H17" s="83" t="n">
-        <v>204.17081927</v>
+        <v>6</v>
       </c>
       <c r="I17" s="144" t="n">
-        <v>14.98</v>
+        <v>246.88</v>
       </c>
       <c r="J17" s="144" t="n">
-        <v>3058.48</v>
+        <v>1481.28</v>
       </c>
       <c r="K17" s="84" t="n">
-        <v>-36.9</v>
+        <v>2.08</v>
       </c>
       <c r="L17" s="84" t="n">
-        <v>-13.02</v>
+        <v>-14.48</v>
       </c>
       <c r="M17" s="84" t="n">
-        <v>-1.68</v>
+        <v>2.08</v>
       </c>
       <c r="N17" s="84" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="O17" s="84" t="n">
-        <v>23.85</v>
+        <v>0.96</v>
       </c>
       <c r="P17" s="84" t="n">
-        <v>-60.75</v>
+        <v>1.12</v>
       </c>
       <c r="Q17" s="84" t="n">
-        <v>-4.13</v>
-      </c>
-      <c r="R17" s="84" t="n"/>
+        <v>4.25</v>
+      </c>
+      <c r="R17" s="84" t="n">
+        <v>90.15000000000001</v>
+      </c>
       <c r="S17" s="84" t="n">
-        <v>-20.22</v>
+        <v>63.85</v>
       </c>
       <c r="T17" s="84" t="n">
-        <v>459.93</v>
+        <v>26.4</v>
       </c>
       <c r="U17" s="84" t="n">
-        <v>-55.06</v>
+        <v>27.53</v>
       </c>
       <c r="V17" s="85" t="n">
-        <v>15</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="86" t="inlineStr">
-        <is>
-          <t>APP</t>
-        </is>
-      </c>
-      <c r="B18" s="87" t="inlineStr">
-        <is>
-          <t>AppLovin</t>
-        </is>
-      </c>
-      <c r="C18" s="86" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D18" s="86" t="inlineStr">
+      <c r="A18" s="100" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="B18" s="101" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="C18" s="100" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D18" s="100" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E18" s="86" t="inlineStr">
+      <c r="E18" s="100" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F18" s="88" t="n">
-        <v>46300</v>
-      </c>
-      <c r="G18" s="145" t="n">
-        <v>241.84</v>
-      </c>
-      <c r="H18" s="90" t="n">
+      <c r="F18" s="102" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G18" s="147" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="H18" s="104" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I18" s="147" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="J18" s="147" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="K18" s="105" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="L18" s="105" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="M18" s="105" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="N18" s="105" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O18" s="105" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P18" s="105" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="Q18" s="105" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="R18" s="105" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="S18" s="105" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="T18" s="105" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="U18" s="105" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="V18" s="106" t="n">
+        <v>52.61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="86" t="inlineStr">
+        <is>
+          <t>CCS</t>
+        </is>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>Century Communities</t>
+        </is>
+      </c>
+      <c r="C19" s="86" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D19" s="86" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E19" s="86" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F19" s="88" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G19" s="145" t="n">
+        <v>49.93</v>
+      </c>
+      <c r="H19" s="90" t="n">
+        <v>18</v>
+      </c>
+      <c r="I19" s="145" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J19" s="145" t="n">
+        <v>886.86</v>
+      </c>
+      <c r="K19" s="91" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="L19" s="91" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="M19" s="91" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="N19" s="91" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O19" s="91" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="P19" s="91" t="n">
+        <v>-47.07</v>
+      </c>
+      <c r="Q19" s="91" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="R19" s="91" t="n"/>
+      <c r="S19" s="91" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="T19" s="91" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="U19" s="91" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="V19" s="92" t="n">
+        <v>68.79000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="79" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B20" s="80" t="inlineStr">
+        <is>
+          <t>Cigna Group</t>
+        </is>
+      </c>
+      <c r="C20" s="79" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D20" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E20" s="79" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F20" s="81" t="n">
+        <v>46141</v>
+      </c>
+      <c r="G20" s="144" t="n">
+        <v>237.04</v>
+      </c>
+      <c r="H20" s="83" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I20" s="144" t="n">
+        <v>252.58</v>
+      </c>
+      <c r="J20" s="144" t="n">
+        <v>2955.19</v>
+      </c>
+      <c r="K20" s="84" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="L20" s="84" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M20" s="84" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N20" s="84" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O20" s="84" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="P20" s="84" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="Q20" s="84" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="R20" s="84" t="n">
+        <v>-6.34</v>
+      </c>
+      <c r="S20" s="84" t="n">
         <v>9</v>
       </c>
-      <c r="I18" s="145" t="n">
-        <v>249.86</v>
-      </c>
-      <c r="J18" s="145" t="n">
-        <v>2248.74</v>
-      </c>
-      <c r="K18" s="91" t="n">
+      <c r="T20" s="84" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="U20" s="84" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="V20" s="85" t="n">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="79" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B21" s="80" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C21" s="79" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D21" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E21" s="79" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F21" s="81" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G21" s="144" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="H21" s="83" t="n">
+        <v>8.6406803</v>
+      </c>
+      <c r="I21" s="144" t="n">
+        <v>189.09</v>
+      </c>
+      <c r="J21" s="144" t="n">
+        <v>1633.87</v>
+      </c>
+      <c r="K21" s="84" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="L21" s="84" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="M21" s="84" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N21" s="84" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O21" s="84" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="P21" s="84" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="Q21" s="84" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="R21" s="84" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="S21" s="84" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="T21" s="84" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="U21" s="84" t="n">
+        <v>-13.22</v>
+      </c>
+      <c r="V21" s="85" t="n">
+        <v>29.12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="79" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="B22" s="80" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C22" s="79" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D22" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E22" s="79" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F22" s="81" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G22" s="144" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="H22" s="83" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="I22" s="144" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="J22" s="144" t="n">
+        <v>847.72</v>
+      </c>
+      <c r="K22" s="84" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="L22" s="84" t="n">
+        <v>-13.35</v>
+      </c>
+      <c r="M22" s="84" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N22" s="84" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O22" s="84" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="P22" s="84" t="n">
+        <v>-14.63</v>
+      </c>
+      <c r="Q22" s="84" t="n">
         <v>3.32</v>
       </c>
-      <c r="L18" s="91" t="n">
-        <v>-9.92</v>
-      </c>
-      <c r="M18" s="91" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N18" s="91" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O18" s="91" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="P18" s="91" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Q18" s="91" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R18" s="91" t="n">
-        <v>90.15000000000001</v>
-      </c>
-      <c r="S18" s="91" t="n">
-        <v>63.85</v>
-      </c>
-      <c r="T18" s="91" t="n">
-        <v>26.56</v>
-      </c>
-      <c r="U18" s="91" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="V18" s="92" t="n">
-        <v>79.43000000000001</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="93" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="B19" s="94" t="inlineStr">
-        <is>
-          <t>PTC</t>
-        </is>
-      </c>
-      <c r="C19" s="93" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D19" s="93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E19" s="93" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F19" s="95" t="n">
-        <v>46273</v>
-      </c>
-      <c r="G19" s="146" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="H19" s="97" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" s="146" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="J19" s="146" t="n">
-        <v>17.15</v>
-      </c>
-      <c r="K19" s="98" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="L19" s="98" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="M19" s="98" t="n">
-        <v>42.56</v>
-      </c>
-      <c r="N19" s="98" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O19" s="98" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="P19" s="98" t="n">
-        <v>37.42</v>
-      </c>
-      <c r="Q19" s="98" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="R19" s="98" t="n">
-        <v>16.46</v>
-      </c>
-      <c r="S19" s="98" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="T19" s="98" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="U19" s="98" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="V19" s="99" t="n">
-        <v>52.75</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="86" t="inlineStr">
-        <is>
-          <t>CCS</t>
-        </is>
-      </c>
-      <c r="B20" s="87" t="inlineStr">
-        <is>
-          <t>Century Communities</t>
-        </is>
-      </c>
-      <c r="C20" s="86" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="D20" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E20" s="86" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F20" s="88" t="n">
-        <v>45775</v>
-      </c>
-      <c r="G20" s="145" t="n">
-        <v>49.93</v>
-      </c>
-      <c r="H20" s="90" t="n">
-        <v>18</v>
-      </c>
-      <c r="I20" s="145" t="n">
-        <v>52.32</v>
-      </c>
-      <c r="J20" s="145" t="n">
-        <v>941.76</v>
-      </c>
-      <c r="K20" s="91" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="L20" s="91" t="n">
-        <v>-5.11</v>
-      </c>
-      <c r="M20" s="91" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="N20" s="91" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="O20" s="91" t="n">
-        <v>45.59</v>
-      </c>
-      <c r="P20" s="91" t="n">
-        <v>-40.8</v>
-      </c>
-      <c r="Q20" s="91" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="R20" s="91" t="n"/>
-      <c r="S20" s="91" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="T20" s="91" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="U20" s="91" t="n">
-        <v>-5.56</v>
-      </c>
-      <c r="V20" s="92" t="n">
-        <v>68.26000000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="86" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="B21" s="87" t="inlineStr">
-        <is>
-          <t>Cigna Group</t>
-        </is>
-      </c>
-      <c r="C21" s="86" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D21" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E21" s="86" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F21" s="88" t="n">
-        <v>46141</v>
-      </c>
-      <c r="G21" s="145" t="n">
-        <v>237.04</v>
-      </c>
-      <c r="H21" s="90" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="I21" s="145" t="n">
-        <v>241.75</v>
-      </c>
-      <c r="J21" s="145" t="n">
-        <v>2828.47</v>
-      </c>
-      <c r="K21" s="91" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="L21" s="91" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="M21" s="91" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N21" s="91" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O21" s="91" t="n">
-        <v>14.68</v>
-      </c>
-      <c r="P21" s="91" t="n">
-        <v>-12.69</v>
-      </c>
-      <c r="Q21" s="91" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="R21" s="91" t="n">
-        <v>-6.34</v>
-      </c>
-      <c r="S21" s="91" t="n">
-        <v>9</v>
-      </c>
-      <c r="T21" s="91" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="U21" s="91" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="V21" s="92" t="n">
-        <v>36.76</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="86" t="inlineStr">
-        <is>
-          <t>CVX</t>
-        </is>
-      </c>
-      <c r="B22" s="87" t="inlineStr">
-        <is>
-          <t>Chevron</t>
-        </is>
-      </c>
-      <c r="C22" s="86" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D22" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E22" s="86" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F22" s="88" t="n">
-        <v>45775</v>
-      </c>
-      <c r="G22" s="145" t="n">
-        <v>134.3</v>
-      </c>
-      <c r="H22" s="90" t="n">
-        <v>8.6406803</v>
-      </c>
-      <c r="I22" s="145" t="n">
-        <v>183.69</v>
-      </c>
-      <c r="J22" s="145" t="n">
-        <v>1587.21</v>
-      </c>
-      <c r="K22" s="91" t="n">
-        <v>36.78</v>
-      </c>
-      <c r="L22" s="91" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="M22" s="91" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="N22" s="91" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O22" s="91" t="n">
-        <v>45.59</v>
-      </c>
-      <c r="P22" s="91" t="n">
-        <v>-8.81</v>
-      </c>
-      <c r="Q22" s="91" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="R22" s="91" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="S22" s="91" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="T22" s="91" t="n">
-        <v>-5.08</v>
-      </c>
-      <c r="U22" s="91" t="n">
-        <v>-13.59</v>
-      </c>
-      <c r="V22" s="92" t="n">
-        <v>29.15</v>
+      <c r="R22" s="84" t="n"/>
+      <c r="S22" s="84" t="n"/>
+      <c r="T22" s="84" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U22" s="84" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="V22" s="85" t="n">
+        <v>57.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="86" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B23" s="87" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Insulet</t>
         </is>
       </c>
       <c r="C23" s="86" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D23" s="86" t="inlineStr">
@@ -2876,1661 +2892,1665 @@
         </is>
       </c>
       <c r="F23" s="88" t="n">
-        <v>45775</v>
+        <v>46254</v>
       </c>
       <c r="G23" s="145" t="n">
-        <v>37.05</v>
+        <v>125.22</v>
       </c>
       <c r="H23" s="90" t="n">
-        <v>17.45</v>
+        <v>12.9</v>
       </c>
       <c r="I23" s="145" t="n">
-        <v>48.09</v>
+        <v>120.74</v>
       </c>
       <c r="J23" s="145" t="n">
-        <v>839.17</v>
+        <v>1557.55</v>
       </c>
       <c r="K23" s="91" t="n">
-        <v>29.8</v>
+        <v>-3.58</v>
       </c>
       <c r="L23" s="91" t="n">
-        <v>-13.25</v>
+        <v>2.52</v>
       </c>
       <c r="M23" s="91" t="n">
-        <v>1.75</v>
+        <v>-3.58</v>
       </c>
       <c r="N23" s="91" t="n">
-        <v>0.86</v>
+        <v>1.63</v>
       </c>
       <c r="O23" s="91" t="n">
-        <v>45.59</v>
+        <v>5.89</v>
       </c>
       <c r="P23" s="91" t="n">
-        <v>-15.79</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="Q23" s="91" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R23" s="91" t="n"/>
-      <c r="S23" s="91" t="n"/>
+        <v>3.73</v>
+      </c>
+      <c r="R23" s="91" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="S23" s="91" t="n">
+        <v>13.99</v>
+      </c>
       <c r="T23" s="91" t="n">
-        <v>5.33</v>
+        <v>13.68</v>
       </c>
       <c r="U23" s="91" t="n">
-        <v>13.93</v>
+        <v>18.8</v>
       </c>
       <c r="V23" s="92" t="n">
-        <v>57.06</v>
+        <v>56.13</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="79" t="inlineStr">
-        <is>
-          <t>PODD</t>
-        </is>
-      </c>
-      <c r="B24" s="80" t="inlineStr">
-        <is>
-          <t>Insulet</t>
-        </is>
-      </c>
-      <c r="C24" s="79" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D24" s="79" t="inlineStr">
+      <c r="A24" s="107" t="inlineStr">
+        <is>
+          <t>LVS</t>
+        </is>
+      </c>
+      <c r="B24" s="108" t="inlineStr">
+        <is>
+          <t>Las Vegas Sands</t>
+        </is>
+      </c>
+      <c r="C24" s="107" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D24" s="107" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E24" s="79" t="inlineStr">
+      <c r="E24" s="107" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F24" s="81" t="n">
-        <v>46254</v>
-      </c>
-      <c r="G24" s="144" t="n">
-        <v>125.22</v>
-      </c>
-      <c r="H24" s="83" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="I24" s="144" t="n">
-        <v>119.87</v>
-      </c>
-      <c r="J24" s="144" t="n">
-        <v>1546.32</v>
-      </c>
-      <c r="K24" s="84" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="L24" s="84" t="n">
-        <v>-4.97</v>
-      </c>
-      <c r="M24" s="84" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="N24" s="84" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O24" s="84" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="P24" s="84" t="n">
-        <v>-10.04</v>
-      </c>
-      <c r="Q24" s="84" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="R24" s="84" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="S24" s="84" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="T24" s="84" t="n">
+      <c r="F24" s="109" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G24" s="148" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="H24" s="111" t="n">
+        <v>45</v>
+      </c>
+      <c r="I24" s="148" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="J24" s="148" t="n">
+        <v>1456.2</v>
+      </c>
+      <c r="K24" s="112" t="n">
+        <v>-16.75</v>
+      </c>
+      <c r="L24" s="112" t="n">
+        <v>-15.55</v>
+      </c>
+      <c r="M24" s="112" t="n">
+        <v>-16.75</v>
+      </c>
+      <c r="N24" s="112" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O24" s="112" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="P24" s="112" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="Q24" s="112" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="R24" s="112" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="S24" s="112" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="T24" s="112" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="U24" s="112" t="n">
         <v>13.68</v>
       </c>
-      <c r="U24" s="84" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="V24" s="85" t="n">
-        <v>56.09</v>
+      <c r="V24" s="113" t="n">
+        <v>56.16</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="107" t="inlineStr">
-        <is>
-          <t>LVS</t>
-        </is>
-      </c>
-      <c r="B25" s="108" t="inlineStr">
-        <is>
-          <t>Las Vegas Sands</t>
-        </is>
-      </c>
-      <c r="C25" s="107" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D25" s="107" t="inlineStr">
+      <c r="A25" s="79" t="inlineStr">
+        <is>
+          <t>CAAP</t>
+        </is>
+      </c>
+      <c r="B25" s="80" t="inlineStr">
+        <is>
+          <t>Corp America Airports</t>
+        </is>
+      </c>
+      <c r="C25" s="79" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D25" s="79" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E25" s="79" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="F25" s="81" t="n">
+        <v>45621</v>
+      </c>
+      <c r="G25" s="144" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="H25" s="83" t="n">
+        <v>28.702979</v>
+      </c>
+      <c r="I25" s="144" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="J25" s="144" t="n">
+        <v>628.6</v>
+      </c>
+      <c r="K25" s="84" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="L25" s="84" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M25" s="84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" s="84" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O25" s="84" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="P25" s="84" t="n">
+        <v>-1.78</v>
+      </c>
+      <c r="Q25" s="84" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="R25" s="84" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="S25" s="84" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T25" s="84" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="U25" s="84" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="V25" s="85" t="n">
+        <v>67.04000000000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="107" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="B26" s="108" t="inlineStr">
+        <is>
+          <t>Albemarle</t>
+        </is>
+      </c>
+      <c r="C26" s="107" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D26" s="107" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E25" s="107" t="inlineStr">
+      <c r="E26" s="107" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
-      <c r="F25" s="109" t="n">
-        <v>46261</v>
-      </c>
-      <c r="G25" s="148" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="H25" s="111" t="n">
-        <v>45</v>
-      </c>
-      <c r="I25" s="148" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="J25" s="148" t="n">
-        <v>1459.8</v>
-      </c>
-      <c r="K25" s="112" t="n">
-        <v>-16.54</v>
-      </c>
-      <c r="L25" s="112" t="n">
-        <v>-17.01</v>
-      </c>
-      <c r="M25" s="112" t="n">
-        <v>-16.54</v>
-      </c>
-      <c r="N25" s="112" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O25" s="112" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="P25" s="112" t="n">
-        <v>-21.57</v>
-      </c>
-      <c r="Q25" s="112" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="R25" s="112" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="S25" s="112" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="T25" s="112" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="U25" s="112" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="V25" s="113" t="n">
-        <v>56.08</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="86" t="inlineStr">
-        <is>
-          <t>CAAP</t>
-        </is>
-      </c>
-      <c r="B26" s="87" t="inlineStr">
-        <is>
-          <t>Corp America Airports</t>
-        </is>
-      </c>
-      <c r="C26" s="86" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D26" s="86" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="E26" s="86" t="inlineStr">
-        <is>
-          <t>Trading212</t>
-        </is>
-      </c>
-      <c r="F26" s="88" t="n">
-        <v>45621</v>
-      </c>
-      <c r="G26" s="145" t="n">
-        <v>17.92</v>
-      </c>
-      <c r="H26" s="90" t="n">
-        <v>28.702979</v>
-      </c>
-      <c r="I26" s="145" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="J26" s="145" t="n">
-        <v>651.84</v>
-      </c>
-      <c r="K26" s="91" t="n">
-        <v>26.73</v>
-      </c>
-      <c r="L26" s="91" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="M26" s="91" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="N26" s="91" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O26" s="91" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="P26" s="91" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q26" s="91" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="R26" s="91" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="S26" s="91" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="T26" s="91" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="U26" s="91" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="V26" s="92" t="n">
-        <v>66.34999999999999</v>
+      <c r="F26" s="109" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G26" s="148" t="n">
+        <v>103.64</v>
+      </c>
+      <c r="H26" s="111" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I26" s="148" t="n">
+        <v>90.45999999999999</v>
+      </c>
+      <c r="J26" s="148" t="n">
+        <v>1365.95</v>
+      </c>
+      <c r="K26" s="112" t="n">
+        <v>-12.72</v>
+      </c>
+      <c r="L26" s="112" t="n">
+        <v>-13.83</v>
+      </c>
+      <c r="M26" s="112" t="n">
+        <v>-12.72</v>
+      </c>
+      <c r="N26" s="112" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O26" s="112" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P26" s="112" t="n">
+        <v>-17.98</v>
+      </c>
+      <c r="Q26" s="112" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="R26" s="112" t="n"/>
+      <c r="S26" s="112" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="T26" s="112" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U26" s="112" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="V26" s="113" t="n">
+        <v>34.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="79" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>SXRU.DE</t>
         </is>
       </c>
       <c r="B27" s="80" t="inlineStr">
         <is>
-          <t>Albemarle</t>
-        </is>
-      </c>
-      <c r="C27" s="79" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D27" s="79" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>iShares Dow Jones Industrial Average (Acc)</t>
+        </is>
+      </c>
+      <c r="C27" s="79" t="n"/>
+      <c r="D27" s="79" t="n"/>
       <c r="E27" s="79" t="inlineStr">
         <is>
           <t>Trading212</t>
         </is>
       </c>
       <c r="F27" s="81" t="n">
-        <v>46273</v>
+        <v>45623</v>
       </c>
       <c r="G27" s="144" t="n">
-        <v>103.64</v>
+        <v>490.01</v>
       </c>
       <c r="H27" s="83" t="n">
-        <v>15.1</v>
+        <v>1.234883</v>
       </c>
       <c r="I27" s="144" t="n">
-        <v>94.34</v>
+        <v>560.3</v>
       </c>
       <c r="J27" s="144" t="n">
-        <v>1424.53</v>
+        <v>691.9</v>
       </c>
       <c r="K27" s="84" t="n">
-        <v>-8.970000000000001</v>
+        <v>14.34</v>
       </c>
       <c r="L27" s="84" t="n">
-        <v>-18.02</v>
+        <v>1.52</v>
       </c>
       <c r="M27" s="84" t="n">
-        <v>-8.970000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="N27" s="84" t="n">
-        <v>1.47</v>
+        <v>0.72</v>
       </c>
       <c r="O27" s="84" t="n">
-        <v>5.14</v>
+        <v>23.93</v>
       </c>
       <c r="P27" s="84" t="n">
-        <v>-14.11</v>
-      </c>
-      <c r="Q27" s="84" t="n">
-        <v>5.53</v>
-      </c>
+        <v>-9.59</v>
+      </c>
+      <c r="Q27" s="84" t="n"/>
       <c r="R27" s="84" t="n"/>
-      <c r="S27" s="84" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="T27" s="84" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U27" s="84" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="V27" s="85" t="n">
-        <v>33.63</v>
-      </c>
+      <c r="S27" s="84" t="n"/>
+      <c r="T27" s="84" t="n"/>
+      <c r="U27" s="84" t="n"/>
+      <c r="V27" s="85" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="86" t="inlineStr">
         <is>
-          <t>SXRU.DE</t>
+          <t>RHM.DE</t>
         </is>
       </c>
       <c r="B28" s="87" t="inlineStr">
         <is>
-          <t>iShares Dow Jones Industrial Average (Acc)</t>
-        </is>
-      </c>
-      <c r="C28" s="86" t="n"/>
-      <c r="D28" s="86" t="n"/>
+          <t>Rheinmetall</t>
+        </is>
+      </c>
+      <c r="C28" s="86" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D28" s="86" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="E28" s="86" t="inlineStr">
         <is>
-          <t>Trading212</t>
+          <t>Capital</t>
         </is>
       </c>
       <c r="F28" s="88" t="n">
-        <v>45623</v>
+        <v>46033</v>
       </c>
       <c r="G28" s="145" t="n">
-        <v>490.01</v>
+        <v>977.3</v>
       </c>
       <c r="H28" s="90" t="n">
-        <v>1.234883</v>
+        <v>3.09</v>
       </c>
       <c r="I28" s="145" t="n">
-        <v>559.1</v>
+        <v>936.55</v>
       </c>
       <c r="J28" s="145" t="n">
-        <v>690.42</v>
+        <v>2893.94</v>
       </c>
       <c r="K28" s="91" t="n">
-        <v>14.1</v>
+        <v>-4.17</v>
       </c>
       <c r="L28" s="91" t="n">
-        <v>0.58</v>
+        <v>-5.2</v>
       </c>
       <c r="M28" s="91" t="n">
-        <v>0.64</v>
+        <v>-0.46</v>
       </c>
       <c r="N28" s="91" t="n">
-        <v>0.71</v>
+        <v>3.03</v>
       </c>
       <c r="O28" s="91" t="n">
-        <v>23.79</v>
+        <v>14.15</v>
       </c>
       <c r="P28" s="91" t="n">
-        <v>-9.69</v>
-      </c>
-      <c r="Q28" s="91" t="n"/>
-      <c r="R28" s="91" t="n"/>
-      <c r="S28" s="91" t="n"/>
-      <c r="T28" s="91" t="n"/>
-      <c r="U28" s="91" t="n"/>
-      <c r="V28" s="92" t="n"/>
+        <v>-18.32</v>
+      </c>
+      <c r="Q28" s="91" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R28" s="91" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="S28" s="91" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="T28" s="91" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="U28" s="91" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="V28" s="92" t="n">
+        <v>78.58</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="79" t="inlineStr">
         <is>
-          <t>RHM.DE</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B29" s="80" t="inlineStr">
         <is>
-          <t>Rheinmetall</t>
+          <t>Roper Technologies Inc</t>
         </is>
       </c>
       <c r="C29" s="79" t="inlineStr">
         <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D29" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E29" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F29" s="81" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G29" s="144" t="n">
+        <v>312.8</v>
+      </c>
+      <c r="H29" s="83" t="n">
+        <v>1.6824</v>
+      </c>
+      <c r="I29" s="144" t="n">
+        <v>324.21</v>
+      </c>
+      <c r="J29" s="144" t="n">
+        <v>545.45</v>
+      </c>
+      <c r="K29" s="84" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L29" s="84" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="M29" s="84" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N29" s="84" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O29" s="84" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P29" s="84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q29" s="84" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="R29" s="84" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="S29" s="84" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="T29" s="84" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="U29" s="84" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="V29" s="85" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="79" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B30" s="80" t="inlineStr">
+        <is>
+          <t>Tesla Inc</t>
+        </is>
+      </c>
+      <c r="C30" s="79" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D30" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E30" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F30" s="81" t="n">
+        <v>45721</v>
+      </c>
+      <c r="G30" s="144" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="H30" s="83" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I30" s="144" t="n">
+        <v>341.03</v>
+      </c>
+      <c r="J30" s="144" t="n">
+        <v>136.41</v>
+      </c>
+      <c r="K30" s="84" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="L30" s="84" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="M30" s="84" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="N30" s="84" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O30" s="84" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="P30" s="84" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q30" s="84" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="R30" s="84" t="n">
+        <v>73.69</v>
+      </c>
+      <c r="S30" s="84" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="T30" s="84" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="U30" s="84" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="V30" s="85" t="n">
+        <v>53.64</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="79" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="B31" s="80" t="inlineStr">
+        <is>
+          <t>SPDR Gold Shares</t>
+        </is>
+      </c>
+      <c r="C31" s="79" t="n"/>
+      <c r="D31" s="79" t="n"/>
+      <c r="E31" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F31" s="81" t="n">
+        <v>45622</v>
+      </c>
+      <c r="G31" s="144" t="n">
+        <v>232.04</v>
+      </c>
+      <c r="H31" s="83" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I31" s="144" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="J31" s="144" t="n">
+        <v>1062.77</v>
+      </c>
+      <c r="K31" s="84" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="L31" s="84" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="M31" s="84" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N31" s="84" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O31" s="84" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="P31" s="84" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="Q31" s="84" t="n"/>
+      <c r="R31" s="84" t="n"/>
+      <c r="S31" s="84" t="n"/>
+      <c r="T31" s="84" t="n"/>
+      <c r="U31" s="84" t="n"/>
+      <c r="V31" s="85" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="79" t="inlineStr">
+        <is>
+          <t>ITX.MC</t>
+        </is>
+      </c>
+      <c r="B32" s="80" t="inlineStr">
+        <is>
+          <t>Inditex</t>
+        </is>
+      </c>
+      <c r="C32" s="79" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D32" s="79" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E32" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F32" s="81" t="n">
+        <v>45757</v>
+      </c>
+      <c r="G32" s="144" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="H32" s="83" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I32" s="144" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="J32" s="144" t="n">
+        <v>1392.9</v>
+      </c>
+      <c r="K32" s="84" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="L32" s="84" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M32" s="84" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N32" s="84" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O32" s="84" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="P32" s="84" t="n">
+        <v>-32.17</v>
+      </c>
+      <c r="Q32" s="84" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="R32" s="84" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="S32" s="84" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="T32" s="84" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="U32" s="84" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="V32" s="85" t="n">
+        <v>53.86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="79" t="inlineStr">
+        <is>
+          <t>BEI.DE</t>
+        </is>
+      </c>
+      <c r="B33" s="80" t="inlineStr">
+        <is>
+          <t>Beiersdorf</t>
+        </is>
+      </c>
+      <c r="C33" s="79" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D33" s="79" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E33" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F33" s="81" t="n">
+        <v>46139</v>
+      </c>
+      <c r="G33" s="144" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="H33" s="83" t="n">
+        <v>24</v>
+      </c>
+      <c r="I33" s="144" t="n">
+        <v>78</v>
+      </c>
+      <c r="J33" s="144" t="n">
+        <v>1872</v>
+      </c>
+      <c r="K33" s="84" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="L33" s="84" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="M33" s="84" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N33" s="84" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O33" s="84" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="P33" s="84" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="Q33" s="84" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R33" s="84" t="n">
+        <v>-59.45</v>
+      </c>
+      <c r="S33" s="84" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="T33" s="84" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U33" s="84" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="V33" s="85" t="n">
+        <v>19.46</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="79" t="inlineStr">
+        <is>
+          <t>LDO.MI</t>
+        </is>
+      </c>
+      <c r="B34" s="80" t="inlineStr">
+        <is>
+          <t>Leonardo</t>
+        </is>
+      </c>
+      <c r="C34" s="79" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D29" s="79" t="inlineStr">
+      <c r="D34" s="79" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E34" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F34" s="81" t="n">
+        <v>45682</v>
+      </c>
+      <c r="G34" s="144" t="n">
+        <v>37.28</v>
+      </c>
+      <c r="H34" s="83" t="n">
+        <v>35</v>
+      </c>
+      <c r="I34" s="144" t="n">
+        <v>46.74</v>
+      </c>
+      <c r="J34" s="144" t="n">
+        <v>1635.9</v>
+      </c>
+      <c r="K34" s="84" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="L34" s="84" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="M34" s="84" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N34" s="84" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O34" s="84" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="P34" s="84" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="Q34" s="84" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R34" s="84" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="S34" s="84" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="T34" s="84" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="U34" s="84" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="V34" s="85" t="n">
+        <v>47.41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="79" t="inlineStr">
+        <is>
+          <t>RWE.DE</t>
+        </is>
+      </c>
+      <c r="B35" s="80" t="inlineStr">
+        <is>
+          <t>RWE</t>
+        </is>
+      </c>
+      <c r="C35" s="79" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D35" s="79" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E29" s="79" t="inlineStr">
+      <c r="E35" s="79" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="F29" s="81" t="n">
-        <v>46033</v>
-      </c>
-      <c r="G29" s="144" t="n">
-        <v>977.3</v>
-      </c>
-      <c r="H29" s="83" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I29" s="144" t="n">
-        <v>947.74</v>
-      </c>
-      <c r="J29" s="144" t="n">
-        <v>2928.52</v>
-      </c>
-      <c r="K29" s="84" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="L29" s="84" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="M29" s="84" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="N29" s="84" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="O29" s="84" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="P29" s="84" t="n">
-        <v>-17</v>
-      </c>
-      <c r="Q29" s="84" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R29" s="84" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="S29" s="84" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="T29" s="84" t="n">
-        <v>33.22</v>
-      </c>
-      <c r="U29" s="84" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="V29" s="85" t="n">
-        <v>78.55</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="86" t="inlineStr">
-        <is>
-          <t>ROP</t>
-        </is>
-      </c>
-      <c r="B30" s="87" t="inlineStr">
-        <is>
-          <t>Roper Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C30" s="86" t="inlineStr">
+      <c r="F35" s="81" t="n">
+        <v>45663</v>
+      </c>
+      <c r="G35" s="144" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="H35" s="83" t="n">
+        <v>14</v>
+      </c>
+      <c r="I35" s="144" t="n">
+        <v>57.98</v>
+      </c>
+      <c r="J35" s="144" t="n">
+        <v>811.72</v>
+      </c>
+      <c r="K35" s="84" t="n">
+        <v>90.66</v>
+      </c>
+      <c r="L35" s="84" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="M35" s="84" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="N35" s="84" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="O35" s="84" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="P35" s="84" t="n">
+        <v>69.42</v>
+      </c>
+      <c r="Q35" s="84" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="R35" s="84" t="n"/>
+      <c r="S35" s="84" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T35" s="84" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="U35" s="84" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="V35" s="85" t="n">
+        <v>15.26</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="100" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B36" s="101" t="inlineStr">
+        <is>
+          <t>Salesforce Inc</t>
+        </is>
+      </c>
+      <c r="C36" s="100" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D30" s="86" t="inlineStr">
+      <c r="D36" s="100" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E30" s="86" t="inlineStr">
+      <c r="E36" s="100" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="F30" s="88" t="n">
-        <v>46293</v>
-      </c>
-      <c r="G30" s="145" t="n">
-        <v>312.8</v>
-      </c>
-      <c r="H30" s="90" t="n">
-        <v>1.6824</v>
-      </c>
-      <c r="I30" s="145" t="n">
-        <v>322.54</v>
-      </c>
-      <c r="J30" s="145" t="n">
-        <v>542.64</v>
-      </c>
-      <c r="K30" s="91" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="L30" s="91" t="n">
-        <v>-8.06</v>
-      </c>
-      <c r="M30" s="91" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N30" s="91" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O30" s="91" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P30" s="91" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Q30" s="91" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="R30" s="91" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="S30" s="91" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="T30" s="91" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="U30" s="91" t="n">
-        <v>9.73</v>
-      </c>
-      <c r="V30" s="92" t="n">
-        <v>39.02</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="86" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B31" s="87" t="inlineStr">
-        <is>
-          <t>Tesla Inc</t>
-        </is>
-      </c>
-      <c r="C31" s="86" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D31" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E31" s="86" t="inlineStr">
+      <c r="F36" s="102" t="n">
+        <v>46197</v>
+      </c>
+      <c r="G36" s="147" t="n">
+        <v>135.15</v>
+      </c>
+      <c r="H36" s="104" t="n">
+        <v>8</v>
+      </c>
+      <c r="I36" s="147" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="J36" s="147" t="n">
+        <v>1633.12</v>
+      </c>
+      <c r="K36" s="105" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="L36" s="105" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="M36" s="105" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="N36" s="105" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O36" s="105" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="P36" s="105" t="n">
+        <v>44.08</v>
+      </c>
+      <c r="Q36" s="105" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="R36" s="105" t="n">
+        <v>15.83</v>
+      </c>
+      <c r="S36" s="105" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="T36" s="105" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="U36" s="105" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="V36" s="106" t="n">
+        <v>50.07</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="79" t="inlineStr">
+        <is>
+          <t>AIR.PA</t>
+        </is>
+      </c>
+      <c r="B37" s="80" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C37" s="79" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D37" s="79" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E37" s="79" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="F31" s="88" t="n">
-        <v>45721</v>
-      </c>
-      <c r="G31" s="145" t="n">
-        <v>259.8</v>
-      </c>
-      <c r="H31" s="90" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I31" s="145" t="n">
-        <v>338.11</v>
-      </c>
-      <c r="J31" s="145" t="n">
-        <v>135.24</v>
-      </c>
-      <c r="K31" s="91" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="L31" s="91" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="M31" s="91" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N31" s="91" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="O31" s="91" t="n">
-        <v>29.62</v>
-      </c>
-      <c r="P31" s="91" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="Q31" s="91" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="R31" s="91" t="n">
-        <v>73.69</v>
-      </c>
-      <c r="S31" s="91" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="T31" s="91" t="n">
-        <v>13.54</v>
-      </c>
-      <c r="U31" s="91" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="V31" s="92" t="n">
-        <v>53.56</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="86" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="B32" s="87" t="inlineStr">
-        <is>
-          <t>SPDR Gold Shares</t>
-        </is>
-      </c>
-      <c r="C32" s="86" t="n"/>
-      <c r="D32" s="86" t="n"/>
-      <c r="E32" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F32" s="88" t="n">
-        <v>45622</v>
-      </c>
-      <c r="G32" s="145" t="n">
-        <v>232.04</v>
-      </c>
-      <c r="H32" s="90" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I32" s="145" t="n">
-        <v>338.71</v>
-      </c>
-      <c r="J32" s="145" t="n">
-        <v>1050</v>
-      </c>
-      <c r="K32" s="91" t="n">
-        <v>45.97</v>
-      </c>
-      <c r="L32" s="91" t="n">
-        <v>-4.54</v>
-      </c>
-      <c r="M32" s="91" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="N32" s="91" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O32" s="91" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="P32" s="91" t="n">
-        <v>23</v>
-      </c>
-      <c r="Q32" s="91" t="n"/>
-      <c r="R32" s="91" t="n"/>
-      <c r="S32" s="91" t="n"/>
-      <c r="T32" s="91" t="n"/>
-      <c r="U32" s="91" t="n"/>
-      <c r="V32" s="92" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="86" t="inlineStr">
-        <is>
-          <t>ITX.MC</t>
-        </is>
-      </c>
-      <c r="B33" s="87" t="inlineStr">
-        <is>
-          <t>Inditex</t>
-        </is>
-      </c>
-      <c r="C33" s="86" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D33" s="86" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E33" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F33" s="88" t="n">
-        <v>45757</v>
-      </c>
-      <c r="G33" s="145" t="n">
-        <v>46.77</v>
-      </c>
-      <c r="H33" s="90" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="I33" s="145" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="J33" s="145" t="n">
-        <v>1392.9</v>
-      </c>
-      <c r="K33" s="91" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="L33" s="91" t="n">
-        <v>-6.57</v>
-      </c>
-      <c r="M33" s="91" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N33" s="91" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="O33" s="91" t="n">
-        <v>46.91</v>
-      </c>
-      <c r="P33" s="91" t="n">
-        <v>-31.92</v>
-      </c>
-      <c r="Q33" s="91" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="R33" s="91" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="S33" s="91" t="n">
-        <v>30.66</v>
-      </c>
-      <c r="T33" s="91" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="U33" s="91" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="V33" s="92" t="n">
-        <v>53.87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="86" t="inlineStr">
-        <is>
-          <t>BEI.DE</t>
-        </is>
-      </c>
-      <c r="B34" s="87" t="inlineStr">
-        <is>
-          <t>Beiersdorf</t>
-        </is>
-      </c>
-      <c r="C34" s="86" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="D34" s="86" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E34" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F34" s="88" t="n">
-        <v>46139</v>
-      </c>
-      <c r="G34" s="145" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="H34" s="90" t="n">
-        <v>24</v>
-      </c>
-      <c r="I34" s="145" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="J34" s="145" t="n">
-        <v>1828.8</v>
-      </c>
-      <c r="K34" s="91" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="L34" s="91" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="M34" s="91" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N34" s="91" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="O34" s="91" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="P34" s="91" t="n">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="Q34" s="91" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R34" s="91" t="n">
-        <v>-59.45</v>
-      </c>
-      <c r="S34" s="91" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="T34" s="91" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U34" s="91" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="V34" s="92" t="n">
-        <v>19.53</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="86" t="inlineStr">
-        <is>
-          <t>LDO.MI</t>
-        </is>
-      </c>
-      <c r="B35" s="87" t="inlineStr">
-        <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C35" s="86" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D35" s="86" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E35" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F35" s="88" t="n">
-        <v>45682</v>
-      </c>
-      <c r="G35" s="145" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="H35" s="90" t="n">
-        <v>35</v>
-      </c>
-      <c r="I35" s="145" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="J35" s="145" t="n">
-        <v>1646.4</v>
-      </c>
-      <c r="K35" s="91" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="L35" s="91" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="M35" s="91" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="N35" s="91" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="O35" s="91" t="n">
-        <v>26.27</v>
-      </c>
-      <c r="P35" s="91" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="Q35" s="91" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R35" s="91" t="n">
-        <v>13.62</v>
-      </c>
-      <c r="S35" s="91" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="T35" s="91" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="U35" s="91" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="V35" s="92" t="n">
-        <v>47.4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="86" t="inlineStr">
-        <is>
-          <t>RWE.DE</t>
-        </is>
-      </c>
-      <c r="B36" s="87" t="inlineStr">
-        <is>
-          <t>RWE</t>
-        </is>
-      </c>
-      <c r="C36" s="86" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D36" s="86" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E36" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F36" s="88" t="n">
-        <v>45663</v>
-      </c>
-      <c r="G36" s="145" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="H36" s="90" t="n">
-        <v>14</v>
-      </c>
-      <c r="I36" s="145" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="J36" s="145" t="n">
-        <v>816.2</v>
-      </c>
-      <c r="K36" s="91" t="n">
-        <v>91.70999999999999</v>
-      </c>
-      <c r="L36" s="91" t="n">
-        <v>-1.91</v>
-      </c>
-      <c r="M36" s="91" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="N36" s="91" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="O36" s="91" t="n">
-        <v>21.03</v>
-      </c>
-      <c r="P36" s="91" t="n">
-        <v>70.68000000000001</v>
-      </c>
-      <c r="Q36" s="91" t="n">
-        <v>-11.09</v>
-      </c>
-      <c r="R36" s="91" t="n"/>
-      <c r="S36" s="91" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T36" s="91" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="U36" s="91" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="V36" s="92" t="n">
-        <v>11.51</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="93" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="B37" s="94" t="inlineStr">
-        <is>
-          <t>Salesforce Inc</t>
-        </is>
-      </c>
-      <c r="C37" s="93" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D37" s="93" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E37" s="93" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F37" s="95" t="n">
-        <v>46197</v>
-      </c>
-      <c r="G37" s="146" t="n">
-        <v>135.15</v>
-      </c>
-      <c r="H37" s="97" t="n">
-        <v>8</v>
-      </c>
-      <c r="I37" s="146" t="n">
-        <v>202.77</v>
-      </c>
-      <c r="J37" s="146" t="n">
-        <v>1622.16</v>
-      </c>
-      <c r="K37" s="98" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="L37" s="98" t="n">
-        <v>-8.24</v>
-      </c>
-      <c r="M37" s="98" t="n">
-        <v>16.68</v>
-      </c>
-      <c r="N37" s="98" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O37" s="98" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="P37" s="98" t="n">
-        <v>43.25</v>
-      </c>
-      <c r="Q37" s="98" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="R37" s="98" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="S37" s="98" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="T37" s="98" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="U37" s="98" t="n">
-        <v>-4.38</v>
-      </c>
-      <c r="V37" s="99" t="n">
-        <v>50.09</v>
+      <c r="F37" s="81" t="n">
+        <v>45632</v>
+      </c>
+      <c r="G37" s="144" t="n">
+        <v>156</v>
+      </c>
+      <c r="H37" s="83" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I37" s="144" t="n">
+        <v>187.73</v>
+      </c>
+      <c r="J37" s="144" t="n">
+        <v>195.24</v>
+      </c>
+      <c r="K37" s="84" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="L37" s="84" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="M37" s="84" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N37" s="84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O37" s="84" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="P37" s="84" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="Q37" s="84" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R37" s="84" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="S37" s="84" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="T37" s="84" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="U37" s="84" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="V37" s="85" t="n">
+        <v>46.65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="86" t="inlineStr">
         <is>
-          <t>AIR.PA</t>
+          <t>FFARM.AS</t>
         </is>
       </c>
       <c r="B38" s="87" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>ForFarmers</t>
         </is>
       </c>
       <c r="C38" s="86" t="inlineStr">
         <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D38" s="86" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E38" s="86" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F38" s="88" t="n">
+        <v>46273</v>
+      </c>
+      <c r="G38" s="145" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="H38" s="90" t="n">
+        <v>250</v>
+      </c>
+      <c r="I38" s="145" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="J38" s="145" t="n">
+        <v>1405</v>
+      </c>
+      <c r="K38" s="91" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L38" s="91" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="M38" s="91" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="N38" s="91" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O38" s="91" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="P38" s="91" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="Q38" s="91" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="R38" s="91" t="n">
+        <v>130</v>
+      </c>
+      <c r="S38" s="91" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="T38" s="91" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="U38" s="91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V38" s="92" t="n">
+        <v>73.94</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="79" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B39" s="80" t="inlineStr">
+        <is>
+          <t>PayPal Holdings Inc</t>
+        </is>
+      </c>
+      <c r="C39" s="79" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D39" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E39" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F39" s="81" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G39" s="144" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="H39" s="83" t="n">
+        <v>17</v>
+      </c>
+      <c r="I39" s="144" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J39" s="144" t="n">
+        <v>840.14</v>
+      </c>
+      <c r="K39" s="84" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="L39" s="84" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M39" s="84" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="N39" s="84" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O39" s="84" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P39" s="84" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q39" s="84" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="R39" s="84" t="n">
+        <v>-17.78</v>
+      </c>
+      <c r="S39" s="84" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="T39" s="84" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="U39" s="84" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="V39" s="85" t="n">
+        <v>40.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="79" t="inlineStr">
+        <is>
+          <t>SAAB-B.ST</t>
+        </is>
+      </c>
+      <c r="B40" s="80" t="inlineStr">
+        <is>
+          <t>Saab</t>
+        </is>
+      </c>
+      <c r="C40" s="79" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D38" s="86" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E38" s="86" t="inlineStr">
+      <c r="D40" s="79" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="E40" s="79" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="F38" s="88" t="n">
-        <v>45632</v>
-      </c>
-      <c r="G38" s="145" t="n">
-        <v>156</v>
-      </c>
-      <c r="H38" s="90" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I38" s="145" t="n">
-        <v>188.13</v>
-      </c>
-      <c r="J38" s="145" t="n">
-        <v>195.66</v>
-      </c>
-      <c r="K38" s="91" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="L38" s="91" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="M38" s="91" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="N38" s="91" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O38" s="91" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="P38" s="91" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="Q38" s="91" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R38" s="91" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="S38" s="91" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="T38" s="91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="U38" s="91" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="V38" s="92" t="n">
-        <v>46.63</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="86" t="inlineStr">
-        <is>
-          <t>FFARM.AS</t>
-        </is>
-      </c>
-      <c r="B39" s="87" t="inlineStr">
-        <is>
-          <t>ForFarmers</t>
-        </is>
-      </c>
-      <c r="C39" s="86" t="inlineStr">
+      <c r="F40" s="81" t="n">
+        <v>45721</v>
+      </c>
+      <c r="G40" s="144" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="H40" s="83" t="n">
+        <v>24</v>
+      </c>
+      <c r="I40" s="144" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="J40" s="144" t="n">
+        <v>1271.52</v>
+      </c>
+      <c r="K40" s="84" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="L40" s="84" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M40" s="84" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N40" s="84" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O40" s="84" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="P40" s="84" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q40" s="84" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R40" s="84" t="n">
+        <v>157.95</v>
+      </c>
+      <c r="S40" s="84" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="T40" s="84" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="U40" s="84" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="V40" s="85" t="n">
+        <v>60.07</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="79" t="inlineStr">
+        <is>
+          <t>ULVR.L</t>
+        </is>
+      </c>
+      <c r="B41" s="80" t="inlineStr">
+        <is>
+          <t>Unilever - GBP</t>
+        </is>
+      </c>
+      <c r="C41" s="79" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="D39" s="86" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E39" s="86" t="inlineStr">
+      <c r="D41" s="79" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="E41" s="79" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="F39" s="88" t="n">
-        <v>46273</v>
-      </c>
-      <c r="G39" s="145" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="H39" s="90" t="n">
-        <v>250</v>
-      </c>
-      <c r="I39" s="145" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="J39" s="145" t="n">
-        <v>1455</v>
-      </c>
-      <c r="K39" s="91" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="L39" s="91" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="M39" s="91" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="N39" s="91" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O39" s="91" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="P39" s="91" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="Q39" s="91" t="n">
-        <v>18.78</v>
-      </c>
-      <c r="R39" s="91" t="n">
-        <v>130</v>
-      </c>
-      <c r="S39" s="91" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="T39" s="91" t="n">
+      <c r="F41" s="81" t="n">
+        <v>46127</v>
+      </c>
+      <c r="G41" s="144" t="n">
+        <v>48.81</v>
+      </c>
+      <c r="H41" s="83" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="I41" s="144" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="J41" s="144" t="n">
+        <v>2670.71</v>
+      </c>
+      <c r="K41" s="84" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="L41" s="84" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M41" s="84" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N41" s="84" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O41" s="84" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="P41" s="84" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="Q41" s="84" t="n">
         <v>5.68</v>
       </c>
-      <c r="U39" s="91" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V39" s="92" t="n">
-        <v>73.94</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="86" t="inlineStr">
-        <is>
-          <t>PYPL</t>
-        </is>
-      </c>
-      <c r="B40" s="87" t="inlineStr">
-        <is>
-          <t>PayPal Holdings Inc</t>
-        </is>
-      </c>
-      <c r="C40" s="86" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D40" s="86" t="inlineStr">
+      <c r="R41" s="84" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="S41" s="84" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="T41" s="84" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="U41" s="84" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="V41" s="85" t="n">
+        <v>59.88</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="93" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B42" s="94" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manufacturing Co Ltd - ADR</t>
+        </is>
+      </c>
+      <c r="C42" s="93" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D42" s="93" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E42" s="93" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F42" s="95" t="n">
+        <v>45757</v>
+      </c>
+      <c r="G42" s="146" t="n">
+        <v>147.77</v>
+      </c>
+      <c r="H42" s="97" t="n">
+        <v>8</v>
+      </c>
+      <c r="I42" s="146" t="n">
+        <v>404.13</v>
+      </c>
+      <c r="J42" s="146" t="n">
+        <v>3233.04</v>
+      </c>
+      <c r="K42" s="98" t="n">
+        <v>173.49</v>
+      </c>
+      <c r="L42" s="98" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="M42" s="98" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="N42" s="98" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="O42" s="98" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="P42" s="98" t="n">
+        <v>126.33</v>
+      </c>
+      <c r="Q42" s="98" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R42" s="98" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="S42" s="98" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="T42" s="98" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="U42" s="98" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="V42" s="99" t="n">
+        <v>57.07</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="79" t="inlineStr">
+        <is>
+          <t>HEN3.DE</t>
+        </is>
+      </c>
+      <c r="B43" s="80" t="inlineStr">
+        <is>
+          <t>Henkel</t>
+        </is>
+      </c>
+      <c r="C43" s="79" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D43" s="79" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E43" s="79" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="F43" s="81" t="n">
+        <v>46041</v>
+      </c>
+      <c r="G43" s="144" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="H43" s="83" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I43" s="144" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="J43" s="144" t="n">
+        <v>1130.88</v>
+      </c>
+      <c r="K43" s="84" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L43" s="84" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M43" s="84" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N43" s="84" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O43" s="84" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="P43" s="84" t="n">
+        <v>-15.82</v>
+      </c>
+      <c r="Q43" s="84" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="R43" s="84" t="n">
+        <v>-26.14</v>
+      </c>
+      <c r="S43" s="84" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="T43" s="84" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" s="84" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="V43" s="85" t="n">
+        <v>46.32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="79" t="inlineStr">
+        <is>
+          <t>IDCC</t>
+        </is>
+      </c>
+      <c r="B44" s="80" t="inlineStr">
+        <is>
+          <t>InterDigital, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" s="79" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D44" s="79" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E40" s="86" t="inlineStr">
+      <c r="E44" s="79" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="F40" s="88" t="n">
-        <v>46296</v>
-      </c>
-      <c r="G40" s="145" t="n">
-        <v>47.28</v>
-      </c>
-      <c r="H40" s="90" t="n">
-        <v>17</v>
-      </c>
-      <c r="I40" s="145" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="J40" s="145" t="n">
-        <v>824.5</v>
-      </c>
-      <c r="K40" s="91" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="L40" s="91" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M40" s="91" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="N40" s="91" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O40" s="91" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P40" s="91" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="Q40" s="91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R40" s="91" t="n">
-        <v>-17.78</v>
-      </c>
-      <c r="S40" s="91" t="n">
-        <v>17.59</v>
-      </c>
-      <c r="T40" s="91" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U40" s="91" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="V40" s="92" t="n">
-        <v>40.35</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="86" t="inlineStr">
-        <is>
-          <t>SAAB-B.ST</t>
-        </is>
-      </c>
-      <c r="B41" s="87" t="inlineStr">
-        <is>
-          <t>Saab</t>
-        </is>
-      </c>
-      <c r="C41" s="86" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D41" s="86" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="E41" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F41" s="88" t="n">
-        <v>45721</v>
-      </c>
-      <c r="G41" s="145" t="n">
-        <v>33.18</v>
-      </c>
-      <c r="H41" s="90" t="n">
-        <v>24</v>
-      </c>
-      <c r="I41" s="145" t="n">
-        <v>52.91</v>
-      </c>
-      <c r="J41" s="145" t="n">
-        <v>1269.84</v>
-      </c>
-      <c r="K41" s="91" t="n">
-        <v>59.48</v>
-      </c>
-      <c r="L41" s="91" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="M41" s="91" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N41" s="91" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="O41" s="91" t="n">
-        <v>30.51</v>
-      </c>
-      <c r="P41" s="91" t="n">
-        <v>28.97</v>
-      </c>
-      <c r="Q41" s="91" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R41" s="91" t="n">
-        <v>157.95</v>
-      </c>
-      <c r="S41" s="91" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="T41" s="91" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="U41" s="91" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="V41" s="92" t="n">
-        <v>60.06</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="86" t="inlineStr">
-        <is>
-          <t>ULVR.L</t>
-        </is>
-      </c>
-      <c r="B42" s="87" t="inlineStr">
-        <is>
-          <t>Unilever - GBP</t>
-        </is>
-      </c>
-      <c r="C42" s="86" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="D42" s="86" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="E42" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F42" s="88" t="n">
-        <v>46127</v>
-      </c>
-      <c r="G42" s="145" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="H42" s="90" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="I42" s="145" t="n">
-        <v>53.67</v>
-      </c>
-      <c r="J42" s="145" t="n">
-        <v>2597.63</v>
-      </c>
-      <c r="K42" s="91" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="L42" s="91" t="n">
-        <v>-3.04</v>
-      </c>
-      <c r="M42" s="91" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="N42" s="91" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O42" s="91" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="P42" s="91" t="n">
-        <v>-7.81</v>
-      </c>
-      <c r="Q42" s="91" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="R42" s="91" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="S42" s="91" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="T42" s="91" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="U42" s="91" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="V42" s="92" t="n">
-        <v>62.55</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="93" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="B43" s="94" t="inlineStr">
-        <is>
-          <t>Taiwan Semiconductor Manufacturing Co Ltd - ADR</t>
-        </is>
-      </c>
-      <c r="C43" s="93" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D43" s="93" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="E43" s="93" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F43" s="95" t="n">
-        <v>45757</v>
-      </c>
-      <c r="G43" s="146" t="n">
-        <v>147.77</v>
-      </c>
-      <c r="H43" s="97" t="n">
-        <v>8</v>
-      </c>
-      <c r="I43" s="146" t="n">
-        <v>429.47</v>
-      </c>
-      <c r="J43" s="146" t="n">
-        <v>3435.76</v>
-      </c>
-      <c r="K43" s="98" t="n">
-        <v>190.63</v>
-      </c>
-      <c r="L43" s="98" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="M43" s="98" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="N43" s="98" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="O43" s="98" t="n">
-        <v>46.96</v>
-      </c>
-      <c r="P43" s="98" t="n">
-        <v>143.67</v>
-      </c>
-      <c r="Q43" s="98" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R43" s="98" t="n">
-        <v>15.23</v>
-      </c>
-      <c r="S43" s="98" t="n">
-        <v>25.16</v>
-      </c>
-      <c r="T43" s="98" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="U43" s="98" t="n">
-        <v>29.98</v>
-      </c>
-      <c r="V43" s="99" t="n">
-        <v>56.97</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="86" t="inlineStr">
-        <is>
-          <t>HEN3.DE</t>
-        </is>
-      </c>
-      <c r="B44" s="87" t="inlineStr">
-        <is>
-          <t>Henkel</t>
-        </is>
-      </c>
-      <c r="C44" s="86" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-      <c r="D44" s="86" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E44" s="86" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-      <c r="F44" s="88" t="n">
-        <v>46041</v>
-      </c>
-      <c r="G44" s="145" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="H44" s="90" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I44" s="145" t="n">
-        <v>72.95</v>
-      </c>
-      <c r="J44" s="145" t="n">
-        <v>1108.84</v>
-      </c>
-      <c r="K44" s="91" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L44" s="91" t="n">
-        <v>-4.33</v>
-      </c>
-      <c r="M44" s="91" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N44" s="91" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="O44" s="91" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="P44" s="91" t="n">
-        <v>-17.65</v>
-      </c>
-      <c r="Q44" s="91" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="R44" s="91" t="n">
-        <v>-26.14</v>
-      </c>
-      <c r="S44" s="91" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="T44" s="91" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="U44" s="91" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="V44" s="92" t="n">
-        <v>43.84</v>
+      <c r="F44" s="81" t="n">
+        <v>45642</v>
+      </c>
+      <c r="G44" s="144" t="n">
+        <v>186.62</v>
+      </c>
+      <c r="H44" s="83" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="144" t="n">
+        <v>294.16</v>
+      </c>
+      <c r="J44" s="144" t="n">
+        <v>588.3200000000001</v>
+      </c>
+      <c r="K44" s="84" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="L44" s="84" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="M44" s="84" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N44" s="84" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O44" s="84" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="P44" s="84" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="Q44" s="84" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="R44" s="84" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="S44" s="84" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="T44" s="84" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="U44" s="84" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="V44" s="85" t="n">
+        <v>56.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="86" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>ACM.US</t>
         </is>
       </c>
       <c r="B45" s="87" t="inlineStr">
         <is>
-          <t>InterDigital, Inc.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C45" s="86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D45" s="86" t="inlineStr">
@@ -4540,153 +4560,153 @@
       </c>
       <c r="E45" s="86" t="inlineStr">
         <is>
-          <t>Capital</t>
+          <t>Freedom24</t>
         </is>
       </c>
       <c r="F45" s="88" t="n">
-        <v>45642</v>
+        <v>45790</v>
       </c>
       <c r="G45" s="145" t="n">
-        <v>186.62</v>
+        <v>96.78</v>
       </c>
       <c r="H45" s="90" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I45" s="145" t="n">
-        <v>299.28</v>
+        <v>53.01</v>
       </c>
       <c r="J45" s="145" t="n">
-        <v>598.5599999999999</v>
+        <v>530.1</v>
       </c>
       <c r="K45" s="91" t="n">
-        <v>60.37</v>
+        <v>-45.23</v>
       </c>
       <c r="L45" s="91" t="n">
-        <v>-1.07</v>
+        <v>-6.69</v>
       </c>
       <c r="M45" s="91" t="n">
-        <v>2.87</v>
+        <v>-2.83</v>
       </c>
       <c r="N45" s="91" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="O45" s="91" t="n">
-        <v>22.39</v>
+        <v>32.77</v>
       </c>
       <c r="P45" s="91" t="n">
-        <v>37.98</v>
+        <v>-78</v>
       </c>
       <c r="Q45" s="91" t="n">
-        <v>5.46</v>
+        <v>8.98</v>
       </c>
       <c r="R45" s="91" t="n">
-        <v>122.72</v>
+        <v>-3.24</v>
       </c>
       <c r="S45" s="91" t="n">
-        <v>25.33</v>
+        <v>15.81</v>
       </c>
       <c r="T45" s="91" t="n">
-        <v>-5.28</v>
+        <v>8.73</v>
       </c>
       <c r="U45" s="91" t="n">
-        <v>0.28</v>
+        <v>59.02</v>
       </c>
       <c r="V45" s="92" t="n">
-        <v>56.73</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="79" t="inlineStr">
-        <is>
-          <t>ACM.US</t>
-        </is>
-      </c>
-      <c r="B46" s="80" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="C46" s="79" t="inlineStr">
+      <c r="A46" s="86" t="inlineStr">
+        <is>
+          <t>AEGN.GR</t>
+        </is>
+      </c>
+      <c r="B46" s="87" t="inlineStr">
+        <is>
+          <t>AEGEAN AIRLINES (CR)</t>
+        </is>
+      </c>
+      <c r="C46" s="86" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D46" s="79" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E46" s="79" t="inlineStr">
+      <c r="D46" s="86" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E46" s="86" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F46" s="81" t="n">
-        <v>45790</v>
-      </c>
-      <c r="G46" s="144" t="n">
-        <v>96.78</v>
-      </c>
-      <c r="H46" s="83" t="n">
-        <v>10</v>
-      </c>
-      <c r="I46" s="144" t="n">
-        <v>53.43</v>
-      </c>
-      <c r="J46" s="144" t="n">
-        <v>534.3</v>
-      </c>
-      <c r="K46" s="84" t="n">
-        <v>-44.79</v>
-      </c>
-      <c r="L46" s="84" t="n">
-        <v>-7.87</v>
-      </c>
-      <c r="M46" s="84" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="N46" s="84" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O46" s="84" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="P46" s="84" t="n">
-        <v>-77.38</v>
-      </c>
-      <c r="Q46" s="84" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="R46" s="84" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="S46" s="84" t="n">
-        <v>15.81</v>
-      </c>
-      <c r="T46" s="84" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="U46" s="84" t="n">
-        <v>59.84</v>
-      </c>
-      <c r="V46" s="85" t="n">
-        <v>64.23</v>
+      <c r="F46" s="88" t="n">
+        <v>46166</v>
+      </c>
+      <c r="G46" s="145" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H46" s="90" t="n">
+        <v>181</v>
+      </c>
+      <c r="I46" s="145" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J46" s="145" t="n">
+        <v>1972.9</v>
+      </c>
+      <c r="K46" s="91" t="n">
+        <v>-11.38</v>
+      </c>
+      <c r="L46" s="91" t="n">
+        <v>-6.03</v>
+      </c>
+      <c r="M46" s="91" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="N46" s="91" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O46" s="91" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="P46" s="91" t="n">
+        <v>-19.53</v>
+      </c>
+      <c r="Q46" s="91" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="R46" s="91" t="n">
+        <v>-74.81999999999999</v>
+      </c>
+      <c r="S46" s="91" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="T46" s="91" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="U46" s="91" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="V46" s="92" t="n">
+        <v>45.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="79" t="inlineStr">
         <is>
-          <t>AEGN.GR</t>
+          <t>ALPHA.GR</t>
         </is>
       </c>
       <c r="B47" s="80" t="inlineStr">
         <is>
-          <t>AEGEAN AIRLINES (CR)</t>
+          <t>ALPHA BANK (CR)</t>
         </is>
       </c>
       <c r="C47" s="79" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D47" s="79" t="inlineStr">
@@ -4700,228 +4720,228 @@
         </is>
       </c>
       <c r="F47" s="81" t="n">
-        <v>46166</v>
+        <v>46230</v>
       </c>
       <c r="G47" s="144" t="n">
-        <v>12.3</v>
+        <v>4.1</v>
       </c>
       <c r="H47" s="83" t="n">
-        <v>181</v>
+        <v>478</v>
       </c>
       <c r="I47" s="144" t="n">
-        <v>11.09</v>
+        <v>4.18</v>
       </c>
       <c r="J47" s="144" t="n">
-        <v>2007.29</v>
+        <v>1998.04</v>
       </c>
       <c r="K47" s="84" t="n">
-        <v>-9.84</v>
+        <v>1.95</v>
       </c>
       <c r="L47" s="84" t="n">
-        <v>-9.76</v>
+        <v>-14.87</v>
       </c>
       <c r="M47" s="84" t="n">
-        <v>-2.46</v>
+        <v>0.97</v>
       </c>
       <c r="N47" s="84" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="O47" s="84" t="n">
-        <v>8</v>
+        <v>7.41</v>
       </c>
       <c r="P47" s="84" t="n">
-        <v>-17.84</v>
+        <v>-5.46</v>
       </c>
       <c r="Q47" s="84" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="R47" s="84" t="n">
-        <v>-74.81999999999999</v>
-      </c>
-      <c r="S47" s="84" t="n">
-        <v>16.01</v>
-      </c>
+        <v>7.14</v>
+      </c>
+      <c r="R47" s="84" t="n"/>
+      <c r="S47" s="84" t="n"/>
       <c r="T47" s="84" t="n">
-        <v>8.01</v>
+        <v>9.48</v>
       </c>
       <c r="U47" s="84" t="n">
-        <v>-13.12</v>
+        <v>16.26</v>
       </c>
       <c r="V47" s="85" t="n">
-        <v>43.43</v>
+        <v>78.52</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="86" t="inlineStr">
-        <is>
-          <t>ALPHA.GR</t>
-        </is>
-      </c>
-      <c r="B48" s="87" t="inlineStr">
-        <is>
-          <t>ALPHA BANK (CR)</t>
-        </is>
-      </c>
-      <c r="C48" s="86" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D48" s="86" t="inlineStr">
+      <c r="A48" s="93" t="inlineStr">
+        <is>
+          <t>ASML.EU</t>
+        </is>
+      </c>
+      <c r="B48" s="94" t="inlineStr">
+        <is>
+          <t>ASML Holding</t>
+        </is>
+      </c>
+      <c r="C48" s="93" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D48" s="93" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E48" s="93" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F48" s="95" t="n">
+        <v>45848</v>
+      </c>
+      <c r="G48" s="146" t="n">
+        <v>682.3</v>
+      </c>
+      <c r="H48" s="97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="146" t="n">
+        <v>1601.6</v>
+      </c>
+      <c r="J48" s="146" t="n">
+        <v>1601.6</v>
+      </c>
+      <c r="K48" s="98" t="n">
+        <v>134.74</v>
+      </c>
+      <c r="L48" s="98" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="M48" s="98" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="N48" s="98" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O48" s="98" t="n">
+        <v>31.56</v>
+      </c>
+      <c r="P48" s="98" t="n">
+        <v>103.18</v>
+      </c>
+      <c r="Q48" s="98" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R48" s="98" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="S48" s="98" t="n">
+        <v>38.77</v>
+      </c>
+      <c r="T48" s="98" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="U48" s="98" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="V48" s="99" t="n">
+        <v>68.29000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="79" t="inlineStr">
+        <is>
+          <t>BELA.GR</t>
+        </is>
+      </c>
+      <c r="B49" s="80" t="inlineStr">
+        <is>
+          <t>JUMBO (CR)</t>
+        </is>
+      </c>
+      <c r="C49" s="79" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D49" s="79" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="E48" s="86" t="inlineStr">
+      <c r="E49" s="79" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F48" s="88" t="n">
-        <v>46230</v>
-      </c>
-      <c r="G48" s="145" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H48" s="90" t="n">
-        <v>478</v>
-      </c>
-      <c r="I48" s="145" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="J48" s="145" t="n">
-        <v>2127.1</v>
-      </c>
-      <c r="K48" s="91" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="L48" s="91" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="M48" s="91" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="N48" s="91" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="O48" s="91" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="P48" s="91" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q48" s="91" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R48" s="91" t="n"/>
-      <c r="S48" s="91" t="n"/>
-      <c r="T48" s="91" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="U48" s="91" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="V48" s="92" t="n">
-        <v>78.38</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="93" t="inlineStr">
-        <is>
-          <t>ASML.EU</t>
-        </is>
-      </c>
-      <c r="B49" s="94" t="inlineStr">
-        <is>
-          <t>ASML Holding</t>
-        </is>
-      </c>
-      <c r="C49" s="93" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D49" s="93" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E49" s="93" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F49" s="95" t="n">
-        <v>45848</v>
-      </c>
-      <c r="G49" s="146" t="n">
-        <v>682.3</v>
-      </c>
-      <c r="H49" s="97" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="146" t="n">
-        <v>1649.6</v>
-      </c>
-      <c r="J49" s="146" t="n">
-        <v>1649.6</v>
-      </c>
-      <c r="K49" s="98" t="n">
-        <v>141.77</v>
-      </c>
-      <c r="L49" s="98" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="M49" s="98" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="N49" s="98" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O49" s="98" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="P49" s="98" t="n">
-        <v>110.39</v>
-      </c>
-      <c r="Q49" s="98" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R49" s="98" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S49" s="98" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="T49" s="98" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="U49" s="98" t="n">
-        <v>34.91</v>
-      </c>
-      <c r="V49" s="99" t="n">
-        <v>68.22</v>
+      <c r="F49" s="81" t="n">
+        <v>46111</v>
+      </c>
+      <c r="G49" s="144" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H49" s="83" t="n">
+        <v>90</v>
+      </c>
+      <c r="I49" s="144" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="J49" s="144" t="n">
+        <v>2212.2</v>
+      </c>
+      <c r="K49" s="84" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="L49" s="84" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="M49" s="84" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N49" s="84" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O49" s="84" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="P49" s="84" t="n">
+        <v>-16.25</v>
+      </c>
+      <c r="Q49" s="84" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="R49" s="84" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="S49" s="84" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="T49" s="84" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="U49" s="84" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="V49" s="85" t="n">
+        <v>61.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="86" t="inlineStr">
         <is>
-          <t>BELA.GR</t>
+          <t>CAP.EU</t>
         </is>
       </c>
       <c r="B50" s="87" t="inlineStr">
         <is>
-          <t>JUMBO (CR)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" s="86" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D50" s="86" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E50" s="86" t="inlineStr">
@@ -4930,76 +4950,76 @@
         </is>
       </c>
       <c r="F50" s="88" t="n">
-        <v>46111</v>
+        <v>45848</v>
       </c>
       <c r="G50" s="145" t="n">
-        <v>22.5</v>
+        <v>146.72</v>
       </c>
       <c r="H50" s="90" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="I50" s="145" t="n">
-        <v>24.96</v>
+        <v>115.05</v>
       </c>
       <c r="J50" s="145" t="n">
-        <v>2246.4</v>
+        <v>1150.5</v>
       </c>
       <c r="K50" s="91" t="n">
-        <v>10.93</v>
+        <v>-21.59</v>
       </c>
       <c r="L50" s="91" t="n">
-        <v>-5.87</v>
+        <v>11.81</v>
       </c>
       <c r="M50" s="91" t="n">
-        <v>1.82</v>
+        <v>-1.44</v>
       </c>
       <c r="N50" s="91" t="n">
-        <v>2.31</v>
+        <v>1.2</v>
       </c>
       <c r="O50" s="91" t="n">
-        <v>25.32</v>
+        <v>31.56</v>
       </c>
       <c r="P50" s="91" t="n">
-        <v>-14.39</v>
+        <v>-53.15</v>
       </c>
       <c r="Q50" s="91" t="n">
-        <v>7.7</v>
+        <v>11.49</v>
       </c>
       <c r="R50" s="91" t="n">
-        <v>10.32</v>
+        <v>-0.72</v>
       </c>
       <c r="S50" s="91" t="n">
-        <v>20.19</v>
+        <v>9.43</v>
       </c>
       <c r="T50" s="91" t="n">
-        <v>6.23</v>
+        <v>4.29</v>
       </c>
       <c r="U50" s="91" t="n">
-        <v>4.07</v>
+        <v>7.2</v>
       </c>
       <c r="V50" s="92" t="n">
-        <v>61.76</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="79" t="inlineStr">
         <is>
-          <t>CAP.EU</t>
+          <t>COP.US</t>
         </is>
       </c>
       <c r="B51" s="80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C51" s="79" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D51" s="79" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E51" s="79" t="inlineStr">
@@ -5008,538 +5028,538 @@
         </is>
       </c>
       <c r="F51" s="81" t="n">
-        <v>45848</v>
+        <v>46092</v>
       </c>
       <c r="G51" s="144" t="n">
-        <v>146.72</v>
+        <v>104.01</v>
       </c>
       <c r="H51" s="83" t="n">
+        <v>21</v>
+      </c>
+      <c r="I51" s="144" t="n">
+        <v>120.23</v>
+      </c>
+      <c r="J51" s="144" t="n">
+        <v>2524.83</v>
+      </c>
+      <c r="K51" s="84" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="L51" s="84" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="M51" s="84" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N51" s="84" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O51" s="84" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="P51" s="84" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="Q51" s="84" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R51" s="84" t="n">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="S51" s="84" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="T51" s="84" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="U51" s="84" t="n">
+        <v>-7.86</v>
+      </c>
+      <c r="V51" s="85" t="n">
+        <v>41.34</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="79" t="inlineStr">
+        <is>
+          <t>EE.US</t>
+        </is>
+      </c>
+      <c r="B52" s="80" t="inlineStr">
+        <is>
+          <t>Excelerate Energy Inc</t>
+        </is>
+      </c>
+      <c r="C52" s="79" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D52" s="79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E52" s="79" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F52" s="81" t="n">
+        <v>45660</v>
+      </c>
+      <c r="G52" s="144" t="n">
+        <v>30.96</v>
+      </c>
+      <c r="H52" s="83" t="n">
+        <v>12</v>
+      </c>
+      <c r="I52" s="144" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="J52" s="144" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="K52" s="84" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L52" s="84" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="M52" s="84" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N52" s="84" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="O52" s="84" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="P52" s="84" t="n">
+        <v>-22.35</v>
+      </c>
+      <c r="Q52" s="84" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="R52" s="84" t="n">
+        <v>127.34</v>
+      </c>
+      <c r="S52" s="84" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="T52" s="84" t="n">
+        <v>27.03</v>
+      </c>
+      <c r="U52" s="84" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="V52" s="85" t="n">
+        <v>87.31</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="86" t="inlineStr">
+        <is>
+          <t>ELHA.GR</t>
+        </is>
+      </c>
+      <c r="B53" s="87" t="inlineStr">
+        <is>
+          <t>ELVALHALCOR (CR)</t>
+        </is>
+      </c>
+      <c r="C53" s="86" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D53" s="86" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E53" s="86" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F53" s="88" t="n">
+        <v>46254</v>
+      </c>
+      <c r="G53" s="145" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H53" s="90" t="n">
+        <v>426</v>
+      </c>
+      <c r="I53" s="145" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J53" s="145" t="n">
+        <v>1427.1</v>
+      </c>
+      <c r="K53" s="91" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="L53" s="91" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="M53" s="91" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="N53" s="91" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O53" s="91" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="P53" s="91" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="Q53" s="91" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R53" s="91" t="n">
+        <v>-58.86</v>
+      </c>
+      <c r="S53" s="91" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="T53" s="91" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="U53" s="91" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="V53" s="92" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="79" t="inlineStr">
+        <is>
+          <t>ETE.GR</t>
+        </is>
+      </c>
+      <c r="B54" s="80" t="inlineStr">
+        <is>
+          <t>NATIONAL BANK (CR)</t>
+        </is>
+      </c>
+      <c r="C54" s="79" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D54" s="79" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E54" s="79" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F54" s="81" t="n">
+        <v>46165</v>
+      </c>
+      <c r="G54" s="144" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H54" s="83" t="n">
+        <v>155</v>
+      </c>
+      <c r="I54" s="144" t="n">
+        <v>16</v>
+      </c>
+      <c r="J54" s="144" t="n">
+        <v>2480</v>
+      </c>
+      <c r="K54" s="84" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="L54" s="84" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="M54" s="84" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N54" s="84" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O54" s="84" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="P54" s="84" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q54" s="84" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="R54" s="84" t="n"/>
+      <c r="S54" s="84" t="n"/>
+      <c r="T54" s="84" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="U54" s="84" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="V54" s="85" t="n">
+        <v>49.85</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="93" t="inlineStr">
+        <is>
+          <t>EUROB.GR</t>
+        </is>
+      </c>
+      <c r="B55" s="94" t="inlineStr">
+        <is>
+          <t>EUROBANK (CR)</t>
+        </is>
+      </c>
+      <c r="C55" s="93" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D55" s="93" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E55" s="93" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F55" s="95" t="n">
+        <v>46165</v>
+      </c>
+      <c r="G55" s="146" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="H55" s="97" t="n">
+        <v>239</v>
+      </c>
+      <c r="I55" s="146" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="J55" s="146" t="n">
+        <v>1032.48</v>
+      </c>
+      <c r="K55" s="98" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L55" s="98" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="M55" s="98" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="N55" s="98" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O55" s="98" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="P55" s="98" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="Q55" s="98" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="R55" s="98" t="n">
+        <v>2566.67</v>
+      </c>
+      <c r="S55" s="98" t="n"/>
+      <c r="T55" s="98" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="U55" s="98" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="V55" s="99" t="n">
+        <v>62.88</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="79" t="inlineStr">
+        <is>
+          <t>EVD.EU</t>
+        </is>
+      </c>
+      <c r="B56" s="80" t="inlineStr">
+        <is>
+          <t>CTS Eventim AG &amp; Co KGaA</t>
+        </is>
+      </c>
+      <c r="C56" s="79" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="D56" s="79" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E56" s="79" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F56" s="81" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G56" s="144" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="H56" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="I51" s="144" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="J51" s="144" t="n">
-        <v>1069</v>
-      </c>
-      <c r="K51" s="84" t="n">
-        <v>-27.14</v>
-      </c>
-      <c r="L51" s="84" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M51" s="84" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="N51" s="84" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O51" s="84" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="P51" s="84" t="n">
-        <v>-58.52</v>
-      </c>
-      <c r="Q51" s="84" t="n">
-        <v>12</v>
-      </c>
-      <c r="R51" s="84" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="S51" s="84" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="T51" s="84" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="U51" s="84" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="V51" s="85" t="n">
-        <v>45.05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="86" t="inlineStr">
-        <is>
-          <t>COP.US</t>
-        </is>
-      </c>
-      <c r="B52" s="87" t="inlineStr">
-        <is>
-          <t>ConocoPhillips</t>
-        </is>
-      </c>
-      <c r="C52" s="86" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D52" s="86" t="inlineStr">
+      <c r="I56" s="144" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="J56" s="144" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="K56" s="84" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="L56" s="84" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="M56" s="84" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N56" s="84" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O56" s="84" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="P56" s="84" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="Q56" s="84" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R56" s="84" t="n">
+        <v>-73.98</v>
+      </c>
+      <c r="S56" s="84" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="T56" s="84" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="U56" s="84" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="V56" s="85" t="n">
+        <v>25.28</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="79" t="inlineStr">
+        <is>
+          <t>FCX.US</t>
+        </is>
+      </c>
+      <c r="B57" s="80" t="inlineStr">
+        <is>
+          <t>Freeport-McMoran Cp &amp; Gld</t>
+        </is>
+      </c>
+      <c r="C57" s="79" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D57" s="79" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="E52" s="86" t="inlineStr">
+      <c r="E57" s="79" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F52" s="88" t="n">
-        <v>46092</v>
-      </c>
-      <c r="G52" s="145" t="n">
-        <v>104.01</v>
-      </c>
-      <c r="H52" s="90" t="n">
-        <v>21</v>
-      </c>
-      <c r="I52" s="145" t="n">
-        <v>113.82</v>
-      </c>
-      <c r="J52" s="145" t="n">
-        <v>2390.22</v>
-      </c>
-      <c r="K52" s="91" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="L52" s="91" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="M52" s="91" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N52" s="91" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O52" s="91" t="n">
-        <v>19.87</v>
-      </c>
-      <c r="P52" s="91" t="n">
-        <v>-10.44</v>
-      </c>
-      <c r="Q52" s="91" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="R52" s="91" t="n">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="S52" s="91" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="T52" s="91" t="n">
-        <v>-5.83</v>
-      </c>
-      <c r="U52" s="91" t="n">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="V52" s="92" t="n">
-        <v>39.55</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="79" t="inlineStr">
-        <is>
-          <t>EE.US</t>
-        </is>
-      </c>
-      <c r="B53" s="80" t="inlineStr">
-        <is>
-          <t>Excelerate Energy Inc</t>
-        </is>
-      </c>
-      <c r="C53" s="79" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D53" s="79" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E53" s="79" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F53" s="81" t="n">
-        <v>45660</v>
-      </c>
-      <c r="G53" s="144" t="n">
-        <v>30.96</v>
-      </c>
-      <c r="H53" s="83" t="n">
-        <v>12</v>
-      </c>
-      <c r="I53" s="144" t="n">
-        <v>30.61</v>
-      </c>
-      <c r="J53" s="144" t="n">
-        <v>367.32</v>
-      </c>
-      <c r="K53" s="84" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="L53" s="84" t="n">
-        <v>-12.6</v>
-      </c>
-      <c r="M53" s="84" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="N53" s="84" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O53" s="84" t="n">
-        <v>22.56</v>
-      </c>
-      <c r="P53" s="84" t="n">
-        <v>-23.69</v>
-      </c>
-      <c r="Q53" s="84" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="R53" s="84" t="n">
-        <v>127.34</v>
-      </c>
-      <c r="S53" s="84" t="n">
-        <v>14.48</v>
-      </c>
-      <c r="T53" s="84" t="n">
-        <v>27.03</v>
-      </c>
-      <c r="U53" s="84" t="n">
-        <v>32.95</v>
-      </c>
-      <c r="V53" s="85" t="n">
-        <v>87.40000000000001</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="86" t="inlineStr">
-        <is>
-          <t>ELHA.GR</t>
-        </is>
-      </c>
-      <c r="B54" s="87" t="inlineStr">
-        <is>
-          <t>ELVALHALCOR (CR)</t>
-        </is>
-      </c>
-      <c r="C54" s="86" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D54" s="86" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="E54" s="86" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F54" s="88" t="n">
-        <v>46254</v>
-      </c>
-      <c r="G54" s="145" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="H54" s="90" t="n">
-        <v>426</v>
-      </c>
-      <c r="I54" s="145" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="J54" s="145" t="n">
-        <v>1614.54</v>
-      </c>
-      <c r="K54" s="91" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L54" s="91" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M54" s="91" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N54" s="91" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O54" s="91" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="P54" s="91" t="n">
-        <v>-2.77</v>
-      </c>
-      <c r="Q54" s="91" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="R54" s="91" t="n">
-        <v>-58.86</v>
-      </c>
-      <c r="S54" s="91" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="T54" s="91" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="U54" s="91" t="n">
-        <v>17.53</v>
-      </c>
-      <c r="V54" s="92" t="n">
-        <v>31.82</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="86" t="inlineStr">
-        <is>
-          <t>ETE.GR</t>
-        </is>
-      </c>
-      <c r="B55" s="87" t="inlineStr">
-        <is>
-          <t>NATIONAL BANK (CR)</t>
-        </is>
-      </c>
-      <c r="C55" s="86" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D55" s="86" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="E55" s="86" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F55" s="88" t="n">
-        <v>46165</v>
-      </c>
-      <c r="G55" s="145" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="H55" s="90" t="n">
-        <v>155</v>
-      </c>
-      <c r="I55" s="145" t="n">
-        <v>17.02</v>
-      </c>
-      <c r="J55" s="145" t="n">
-        <v>2638.1</v>
-      </c>
-      <c r="K55" s="91" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="L55" s="91" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M55" s="91" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="N55" s="91" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O55" s="91" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="P55" s="91" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="Q55" s="91" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="R55" s="91" t="n"/>
-      <c r="S55" s="91" t="n"/>
-      <c r="T55" s="91" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="U55" s="91" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="V55" s="92" t="n">
-        <v>49.54</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="100" t="inlineStr">
-        <is>
-          <t>EUROB.GR</t>
-        </is>
-      </c>
-      <c r="B56" s="101" t="inlineStr">
-        <is>
-          <t>EUROBANK (CR)</t>
-        </is>
-      </c>
-      <c r="C56" s="100" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D56" s="100" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="E56" s="100" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F56" s="102" t="n">
-        <v>46165</v>
-      </c>
-      <c r="G56" s="147" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="H56" s="104" t="n">
-        <v>239</v>
-      </c>
-      <c r="I56" s="147" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J56" s="147" t="n">
-        <v>1108.96</v>
-      </c>
-      <c r="K56" s="105" t="n">
-        <v>33.72</v>
-      </c>
-      <c r="L56" s="105" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M56" s="105" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="N56" s="105" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="O56" s="105" t="n">
-        <v>8.02</v>
-      </c>
-      <c r="P56" s="105" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="Q56" s="105" t="n">
-        <v>15.27</v>
-      </c>
-      <c r="R56" s="105" t="n">
-        <v>2566.67</v>
-      </c>
-      <c r="S56" s="105" t="n"/>
-      <c r="T56" s="105" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="U56" s="105" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="V56" s="106" t="n">
-        <v>60.13</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="86" t="inlineStr">
-        <is>
-          <t>EVD.EU</t>
-        </is>
-      </c>
-      <c r="B57" s="87" t="inlineStr">
-        <is>
-          <t>CTS Eventim AG &amp; Co KGaA</t>
-        </is>
-      </c>
-      <c r="C57" s="86" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="D57" s="86" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E57" s="86" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F57" s="88" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G57" s="145" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="H57" s="90" t="n">
-        <v>10</v>
-      </c>
-      <c r="I57" s="145" t="n">
-        <v>56.65</v>
-      </c>
-      <c r="J57" s="145" t="n">
-        <v>566.5</v>
-      </c>
-      <c r="K57" s="91" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="L57" s="91" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="M57" s="91" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N57" s="91" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="O57" s="91" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="P57" s="91" t="n">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="Q57" s="91" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R57" s="91" t="n">
-        <v>-73.98</v>
-      </c>
-      <c r="S57" s="91" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="T57" s="91" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="U57" s="91" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="V57" s="92" t="n">
-        <v>25.31</v>
+      <c r="F57" s="81" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G57" s="144" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="H57" s="83" t="n">
+        <v>24</v>
+      </c>
+      <c r="I57" s="144" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="J57" s="144" t="n">
+        <v>1580.4</v>
+      </c>
+      <c r="K57" s="84" t="n">
+        <v>66.88</v>
+      </c>
+      <c r="L57" s="84" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="M57" s="84" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="N57" s="84" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O57" s="84" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="P57" s="84" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="Q57" s="84" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R57" s="84" t="n">
+        <v>-52.55</v>
+      </c>
+      <c r="S57" s="84" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="T57" s="84" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="U57" s="84" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="V57" s="85" t="n">
+        <v>57.8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="86" t="inlineStr">
         <is>
-          <t>FCX.US</t>
+          <t>FOYRK.GR</t>
         </is>
       </c>
       <c r="B58" s="87" t="inlineStr">
         <is>
-          <t>Freeport-McMoran Cp &amp; Gld</t>
+          <t>FOURLIS (CR)</t>
         </is>
       </c>
       <c r="C58" s="86" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D58" s="86" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="E58" s="86" t="inlineStr">
@@ -5548,381 +5568,379 @@
         </is>
       </c>
       <c r="F58" s="88" t="n">
-        <v>45849</v>
+        <v>46265</v>
       </c>
       <c r="G58" s="145" t="n">
-        <v>39.46</v>
+        <v>4.15</v>
       </c>
       <c r="H58" s="90" t="n">
-        <v>24</v>
+        <v>300</v>
       </c>
       <c r="I58" s="145" t="n">
-        <v>64.70999999999999</v>
+        <v>3.92</v>
       </c>
       <c r="J58" s="145" t="n">
-        <v>1553.04</v>
+        <v>1176</v>
       </c>
       <c r="K58" s="91" t="n">
-        <v>63.99</v>
+        <v>-5.54</v>
       </c>
       <c r="L58" s="91" t="n">
-        <v>-6.28</v>
+        <v>-4.39</v>
       </c>
       <c r="M58" s="91" t="n">
-        <v>4.57</v>
+        <v>-5.54</v>
       </c>
       <c r="N58" s="91" t="n">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="O58" s="91" t="n">
-        <v>31.49</v>
+        <v>5.5</v>
       </c>
       <c r="P58" s="91" t="n">
-        <v>32.5</v>
+        <v>-11.04</v>
       </c>
       <c r="Q58" s="91" t="n">
-        <v>1.08</v>
+        <v>2.74</v>
       </c>
       <c r="R58" s="91" t="n">
-        <v>-52.55</v>
+        <v>-85.84</v>
       </c>
       <c r="S58" s="91" t="n">
-        <v>14.98</v>
+        <v>3.13</v>
       </c>
       <c r="T58" s="91" t="n">
-        <v>19.76</v>
+        <v>3</v>
       </c>
       <c r="U58" s="91" t="n">
-        <v>36.38</v>
+        <v>108.33</v>
       </c>
       <c r="V58" s="92" t="n">
-        <v>57.79</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="79" t="inlineStr">
-        <is>
-          <t>FOYRK.GR</t>
-        </is>
-      </c>
-      <c r="B59" s="80" t="inlineStr">
-        <is>
-          <t>FOURLIS (CR)</t>
-        </is>
-      </c>
-      <c r="C59" s="79" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D59" s="79" t="inlineStr">
+      <c r="A59" s="86" t="inlineStr">
+        <is>
+          <t>LAMDA.GR</t>
+        </is>
+      </c>
+      <c r="B59" s="87" t="inlineStr">
+        <is>
+          <t>LAMDA DEVELOPMENT (CR)</t>
+        </is>
+      </c>
+      <c r="C59" s="86" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D59" s="86" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="E59" s="79" t="inlineStr">
+      <c r="E59" s="86" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F59" s="81" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G59" s="144" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H59" s="83" t="n">
-        <v>300</v>
-      </c>
-      <c r="I59" s="144" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="J59" s="144" t="n">
-        <v>1161</v>
-      </c>
-      <c r="K59" s="84" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="L59" s="84" t="n">
-        <v>-5.72</v>
-      </c>
-      <c r="M59" s="84" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="N59" s="84" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O59" s="84" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="P59" s="84" t="n">
-        <v>-12.13</v>
-      </c>
-      <c r="Q59" s="84" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="R59" s="84" t="n">
-        <v>-85.84</v>
-      </c>
-      <c r="S59" s="84" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="T59" s="84" t="n">
-        <v>3</v>
-      </c>
-      <c r="U59" s="84" t="n">
-        <v>108.33</v>
-      </c>
-      <c r="V59" s="85" t="n">
-        <v>25.12</v>
+      <c r="F59" s="88" t="n">
+        <v>46257</v>
+      </c>
+      <c r="G59" s="145" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="H59" s="90" t="n">
+        <v>198</v>
+      </c>
+      <c r="I59" s="145" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" s="145" t="n">
+        <v>1188</v>
+      </c>
+      <c r="K59" s="91" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="L59" s="91" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="M59" s="91" t="n">
+        <v>-7.41</v>
+      </c>
+      <c r="N59" s="91" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O59" s="91" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="P59" s="91" t="n">
+        <v>-13.73</v>
+      </c>
+      <c r="Q59" s="91" t="n">
+        <v>-8.41</v>
+      </c>
+      <c r="R59" s="91" t="n"/>
+      <c r="S59" s="91" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T59" s="91" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="U59" s="91" t="n">
+        <v>-75.29000000000001</v>
+      </c>
+      <c r="V59" s="92" t="n">
+        <v>15.87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="79" t="inlineStr">
         <is>
-          <t>LAMDA.GR</t>
+          <t>LNG.US</t>
         </is>
       </c>
       <c r="B60" s="80" t="inlineStr">
         <is>
-          <t>LAMDA DEVELOPMENT (CR)</t>
+          <t>CHENIERE ENERGY INC</t>
         </is>
       </c>
       <c r="C60" s="79" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D60" s="79" t="inlineStr">
         <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E60" s="79" t="inlineStr">
+        <is>
+          <t>Freedom24</t>
+        </is>
+      </c>
+      <c r="F60" s="81" t="n">
+        <v>46122</v>
+      </c>
+      <c r="G60" s="144" t="n">
+        <v>225.75</v>
+      </c>
+      <c r="H60" s="83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I60" s="144" t="n">
+        <v>248.66</v>
+      </c>
+      <c r="J60" s="144" t="n">
+        <v>2237.94</v>
+      </c>
+      <c r="K60" s="84" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="L60" s="84" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M60" s="84" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="N60" s="84" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O60" s="84" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P60" s="84" t="n">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="Q60" s="84" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="R60" s="84" t="n">
+        <v>-22.02</v>
+      </c>
+      <c r="S60" s="84" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="T60" s="84" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U60" s="84" t="n">
+        <v>-10.22</v>
+      </c>
+      <c r="V60" s="85" t="n">
+        <v>49.42</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="100" t="inlineStr">
+        <is>
+          <t>MOH.GR</t>
+        </is>
+      </c>
+      <c r="B61" s="101" t="inlineStr">
+        <is>
+          <t>MOTOR OIL (CR)</t>
+        </is>
+      </c>
+      <c r="C61" s="100" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D61" s="100" t="inlineStr">
+        <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="E60" s="79" t="inlineStr">
+      <c r="E61" s="100" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F60" s="81" t="n">
-        <v>46257</v>
-      </c>
-      <c r="G60" s="144" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="H60" s="83" t="n">
-        <v>198</v>
-      </c>
-      <c r="I60" s="144" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="J60" s="144" t="n">
-        <v>1223.64</v>
-      </c>
-      <c r="K60" s="84" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="L60" s="84" t="n">
-        <v>-10.82</v>
-      </c>
-      <c r="M60" s="84" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="N60" s="84" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="O60" s="84" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="P60" s="84" t="n">
-        <v>-10.83</v>
-      </c>
-      <c r="Q60" s="84" t="n">
-        <v>-8.17</v>
-      </c>
-      <c r="R60" s="84" t="n"/>
-      <c r="S60" s="84" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T60" s="84" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="U60" s="84" t="n">
-        <v>-75.29000000000001</v>
-      </c>
-      <c r="V60" s="85" t="n">
-        <v>15.87</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="86" t="inlineStr">
-        <is>
-          <t>LNG.US</t>
-        </is>
-      </c>
-      <c r="B61" s="87" t="inlineStr">
-        <is>
-          <t>CHENIERE ENERGY INC</t>
-        </is>
-      </c>
-      <c r="C61" s="86" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D61" s="86" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E61" s="86" t="inlineStr">
+      <c r="F61" s="102" t="n">
+        <v>45649</v>
+      </c>
+      <c r="G61" s="147" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="H61" s="104" t="n">
+        <v>15</v>
+      </c>
+      <c r="I61" s="147" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="J61" s="147" t="n">
+        <v>1016.25</v>
+      </c>
+      <c r="K61" s="105" t="n">
+        <v>231.46</v>
+      </c>
+      <c r="L61" s="105" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M61" s="105" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="N61" s="105" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O61" s="105" t="n">
+        <v>24.53</v>
+      </c>
+      <c r="P61" s="105" t="n">
+        <v>206.93</v>
+      </c>
+      <c r="Q61" s="105" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R61" s="105" t="n">
+        <v>1055.67</v>
+      </c>
+      <c r="S61" s="105" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="T61" s="105" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="U61" s="105" t="n">
+        <v>-41.52</v>
+      </c>
+      <c r="V61" s="106" t="n">
+        <v>33.12</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="79" t="inlineStr">
+        <is>
+          <t>MTLN.GR</t>
+        </is>
+      </c>
+      <c r="B62" s="80" t="inlineStr">
+        <is>
+          <t>METLEN PLC (CR)</t>
+        </is>
+      </c>
+      <c r="C62" s="79" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D62" s="79" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E62" s="79" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F61" s="88" t="n">
-        <v>46122</v>
-      </c>
-      <c r="G61" s="145" t="n">
-        <v>225.75</v>
-      </c>
-      <c r="H61" s="90" t="n">
-        <v>9</v>
-      </c>
-      <c r="I61" s="145" t="n">
-        <v>243.75</v>
-      </c>
-      <c r="J61" s="145" t="n">
-        <v>2193.75</v>
-      </c>
-      <c r="K61" s="91" t="n">
-        <v>7.97</v>
-      </c>
-      <c r="L61" s="91" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="M61" s="91" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="N61" s="91" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="O61" s="91" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="P61" s="91" t="n">
-        <v>-11.49</v>
-      </c>
-      <c r="Q61" s="91" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="R61" s="91" t="n">
-        <v>-22.02</v>
-      </c>
-      <c r="S61" s="91" t="n">
-        <v>24.33</v>
-      </c>
-      <c r="T61" s="91" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U61" s="91" t="n">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="V61" s="92" t="n">
-        <v>51.43</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="93" t="inlineStr">
-        <is>
-          <t>MOH.GR</t>
-        </is>
-      </c>
-      <c r="B62" s="94" t="inlineStr">
-        <is>
-          <t>MOTOR OIL (CR)</t>
-        </is>
-      </c>
-      <c r="C62" s="93" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D62" s="93" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="E62" s="93" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F62" s="95" t="n">
-        <v>45649</v>
-      </c>
-      <c r="G62" s="146" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="H62" s="97" t="n">
-        <v>15</v>
-      </c>
-      <c r="I62" s="146" t="n">
-        <v>67.55</v>
-      </c>
-      <c r="J62" s="146" t="n">
-        <v>1013.25</v>
-      </c>
-      <c r="K62" s="98" t="n">
-        <v>230.48</v>
-      </c>
-      <c r="L62" s="98" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="M62" s="98" t="n">
-        <v>10.98</v>
-      </c>
-      <c r="N62" s="98" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="O62" s="98" t="n">
-        <v>24.39</v>
-      </c>
-      <c r="P62" s="98" t="n">
-        <v>206.09</v>
-      </c>
-      <c r="Q62" s="98" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="R62" s="98" t="n">
-        <v>1055.67</v>
-      </c>
-      <c r="S62" s="98" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="T62" s="98" t="n">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="U62" s="98" t="n">
-        <v>-41.52</v>
-      </c>
-      <c r="V62" s="99" t="n">
-        <v>33.2</v>
+      <c r="F62" s="81" t="n">
+        <v>45883</v>
+      </c>
+      <c r="G62" s="144" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="H62" s="83" t="n">
+        <v>64</v>
+      </c>
+      <c r="I62" s="144" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="J62" s="144" t="n">
+        <v>3107.84</v>
+      </c>
+      <c r="K62" s="84" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="L62" s="84" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M62" s="84" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N62" s="84" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O62" s="84" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="P62" s="84" t="n">
+        <v>-7.81</v>
+      </c>
+      <c r="Q62" s="84" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="R62" s="84" t="n"/>
+      <c r="S62" s="84" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="T62" s="84" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U62" s="84" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="V62" s="85" t="n">
+        <v>44.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="86" t="inlineStr">
         <is>
-          <t>MTLN.GR</t>
+          <t>OTOEL.GR</t>
         </is>
       </c>
       <c r="B63" s="87" t="inlineStr">
         <is>
-          <t>METLEN PLC (CR)</t>
+          <t>AUTOHELLAS (CR)</t>
         </is>
       </c>
       <c r="C63" s="86" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D63" s="86" t="inlineStr">
@@ -5936,69 +5954,65 @@
         </is>
       </c>
       <c r="F63" s="88" t="n">
-        <v>45883</v>
+        <v>46167</v>
       </c>
       <c r="G63" s="145" t="n">
-        <v>40.49</v>
+        <v>10.89</v>
       </c>
       <c r="H63" s="90" t="n">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="I63" s="145" t="n">
-        <v>49.32</v>
+        <v>10.52</v>
       </c>
       <c r="J63" s="145" t="n">
-        <v>3156.48</v>
+        <v>2030.36</v>
       </c>
       <c r="K63" s="91" t="n">
-        <v>21.81</v>
+        <v>-3.4</v>
       </c>
       <c r="L63" s="91" t="n">
-        <v>4.21</v>
+        <v>-7.56</v>
       </c>
       <c r="M63" s="91" t="n">
-        <v>1.68</v>
+        <v>-0.85</v>
       </c>
       <c r="N63" s="91" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="O63" s="91" t="n">
-        <v>27.59</v>
+        <v>8.15</v>
       </c>
       <c r="P63" s="91" t="n">
-        <v>-5.78</v>
+        <v>-11.55</v>
       </c>
       <c r="Q63" s="91" t="n">
-        <v>-3.4</v>
+        <v>-5.68</v>
       </c>
       <c r="R63" s="91" t="n"/>
       <c r="S63" s="91" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="T63" s="91" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="U63" s="91" t="n">
-        <v>21.75</v>
-      </c>
+        <v>7.28</v>
+      </c>
+      <c r="T63" s="91" t="n"/>
+      <c r="U63" s="91" t="n"/>
       <c r="V63" s="92" t="n">
-        <v>48.96</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="79" t="inlineStr">
         <is>
-          <t>OTOEL.GR</t>
+          <t>PPC.GR</t>
         </is>
       </c>
       <c r="B64" s="80" t="inlineStr">
         <is>
-          <t>AUTOHELLAS (CR)</t>
+          <t>PPC (CR)</t>
         </is>
       </c>
       <c r="C64" s="79" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D64" s="79" t="inlineStr">
@@ -6012,70 +6026,76 @@
         </is>
       </c>
       <c r="F64" s="81" t="n">
-        <v>46167</v>
+        <v>46043</v>
       </c>
       <c r="G64" s="144" t="n">
-        <v>10.89</v>
+        <v>17.61</v>
       </c>
       <c r="H64" s="83" t="n">
-        <v>193</v>
+        <v>80</v>
       </c>
       <c r="I64" s="144" t="n">
-        <v>10.68</v>
+        <v>22.66</v>
       </c>
       <c r="J64" s="144" t="n">
-        <v>2061.24</v>
+        <v>1812.8</v>
       </c>
       <c r="K64" s="84" t="n">
-        <v>-1.93</v>
+        <v>28.68</v>
       </c>
       <c r="L64" s="84" t="n">
-        <v>-11.22</v>
+        <v>-5.26</v>
       </c>
       <c r="M64" s="84" t="n">
-        <v>-0.48</v>
+        <v>3.58</v>
       </c>
       <c r="N64" s="84" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="O64" s="84" t="n">
-        <v>8.029999999999999</v>
+        <v>19.81</v>
       </c>
       <c r="P64" s="84" t="n">
-        <v>-9.960000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q64" s="84" t="n">
-        <v>-5.64</v>
-      </c>
-      <c r="R64" s="84" t="n"/>
+        <v>9.68</v>
+      </c>
+      <c r="R64" s="84" t="n">
+        <v>-56.37</v>
+      </c>
       <c r="S64" s="84" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="T64" s="84" t="n"/>
-      <c r="U64" s="84" t="n"/>
+        <v>17.51</v>
+      </c>
+      <c r="T64" s="84" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U64" s="84" t="n">
+        <v>16.73</v>
+      </c>
       <c r="V64" s="85" t="n">
-        <v>16.28</v>
+        <v>65.31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="86" t="inlineStr">
         <is>
-          <t>PPC.GR</t>
+          <t>PSN.US</t>
         </is>
       </c>
       <c r="B65" s="87" t="inlineStr">
         <is>
-          <t>PPC (CR)</t>
+          <t>PARSONS CORP</t>
         </is>
       </c>
       <c r="C65" s="86" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D65" s="86" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E65" s="86" t="inlineStr">
@@ -6084,493 +6104,416 @@
         </is>
       </c>
       <c r="F65" s="88" t="n">
-        <v>46043</v>
+        <v>45790</v>
       </c>
       <c r="G65" s="145" t="n">
-        <v>17.61</v>
+        <v>59.15</v>
       </c>
       <c r="H65" s="90" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="I65" s="145" t="n">
-        <v>22.92</v>
+        <v>40.43</v>
       </c>
       <c r="J65" s="145" t="n">
-        <v>1833.6</v>
+        <v>404.3</v>
       </c>
       <c r="K65" s="91" t="n">
-        <v>30.15</v>
+        <v>-31.65</v>
       </c>
       <c r="L65" s="91" t="n">
-        <v>-5.89</v>
+        <v>-1.46</v>
       </c>
       <c r="M65" s="91" t="n">
-        <v>3.77</v>
+        <v>-1.98</v>
       </c>
       <c r="N65" s="91" t="n">
-        <v>1.89</v>
+        <v>0.42</v>
       </c>
       <c r="O65" s="91" t="n">
-        <v>19.67</v>
+        <v>32.77</v>
       </c>
       <c r="P65" s="91" t="n">
-        <v>10.48</v>
+        <v>-64.42</v>
       </c>
       <c r="Q65" s="91" t="n">
-        <v>9.83</v>
+        <v>8.52</v>
       </c>
       <c r="R65" s="91" t="n">
-        <v>-56.37</v>
+        <v>-13.49</v>
       </c>
       <c r="S65" s="91" t="n">
-        <v>17.51</v>
+        <v>8.65</v>
       </c>
       <c r="T65" s="91" t="n">
-        <v>2.28</v>
+        <v>5.78</v>
       </c>
       <c r="U65" s="91" t="n">
-        <v>16.73</v>
+        <v>41.07</v>
       </c>
       <c r="V65" s="92" t="n">
-        <v>65.42</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="79" t="inlineStr">
-        <is>
-          <t>PSN.US</t>
-        </is>
-      </c>
-      <c r="B66" s="80" t="inlineStr">
-        <is>
-          <t>PARSONS CORP</t>
-        </is>
-      </c>
-      <c r="C66" s="79" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D66" s="79" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E66" s="79" t="inlineStr">
+      <c r="A66" s="86" t="inlineStr">
+        <is>
+          <t>RHM.EU</t>
+        </is>
+      </c>
+      <c r="B66" s="87" t="inlineStr">
+        <is>
+          <t>Rheinmetall AG</t>
+        </is>
+      </c>
+      <c r="C66" s="86" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D66" s="86" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E66" s="86" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F66" s="81" t="n">
-        <v>45790</v>
-      </c>
-      <c r="G66" s="144" t="n">
-        <v>59.15</v>
-      </c>
-      <c r="H66" s="83" t="n">
-        <v>10</v>
-      </c>
-      <c r="I66" s="144" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="J66" s="144" t="n">
-        <v>373</v>
-      </c>
-      <c r="K66" s="84" t="n">
-        <v>-36.94</v>
-      </c>
-      <c r="L66" s="84" t="n">
-        <v>-11.52</v>
-      </c>
-      <c r="M66" s="84" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="N66" s="84" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="O66" s="84" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="P66" s="84" t="n">
-        <v>-69.53</v>
-      </c>
-      <c r="Q66" s="84" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="R66" s="84" t="n">
-        <v>-13.49</v>
-      </c>
-      <c r="S66" s="84" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="T66" s="84" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="U66" s="84" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="V66" s="85" t="n">
-        <v>46.58</v>
+      <c r="F66" s="88" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G66" s="145" t="n">
+        <v>1396.6</v>
+      </c>
+      <c r="H66" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="145" t="n">
+        <v>935.9</v>
+      </c>
+      <c r="J66" s="145" t="n">
+        <v>935.9</v>
+      </c>
+      <c r="K66" s="91" t="n">
+        <v>-32.99</v>
+      </c>
+      <c r="L66" s="91" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="M66" s="91" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="N66" s="91" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="O66" s="91" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="P66" s="91" t="n">
+        <v>-45.95</v>
+      </c>
+      <c r="Q66" s="91" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R66" s="91" t="n">
+        <v>43.22</v>
+      </c>
+      <c r="S66" s="91" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="T66" s="91" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="U66" s="91" t="n">
+        <v>42.29</v>
+      </c>
+      <c r="V66" s="92" t="n">
+        <v>78.58</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="79" t="inlineStr">
-        <is>
-          <t>RHM.EU</t>
-        </is>
-      </c>
-      <c r="B67" s="80" t="inlineStr">
-        <is>
-          <t>Rheinmetall AG</t>
-        </is>
-      </c>
-      <c r="C67" s="79" t="inlineStr">
+      <c r="A67" s="86" t="inlineStr">
+        <is>
+          <t>SIX3.EU</t>
+        </is>
+      </c>
+      <c r="B67" s="87" t="inlineStr">
+        <is>
+          <t>Sixt SE</t>
+        </is>
+      </c>
+      <c r="C67" s="86" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D67" s="79" t="inlineStr">
+      <c r="D67" s="86" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E67" s="79" t="inlineStr">
+      <c r="E67" s="86" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F67" s="81" t="n">
+      <c r="F67" s="88" t="n">
         <v>46146</v>
       </c>
-      <c r="G67" s="144" t="n">
-        <v>1396.6</v>
-      </c>
-      <c r="H67" s="83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="144" t="n">
-        <v>981.4</v>
-      </c>
-      <c r="J67" s="144" t="n">
-        <v>981.4</v>
-      </c>
-      <c r="K67" s="84" t="n">
-        <v>-29.73</v>
-      </c>
-      <c r="L67" s="84" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="M67" s="84" t="n">
-        <v>-5.95</v>
-      </c>
-      <c r="N67" s="84" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O67" s="84" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="P67" s="84" t="n">
-        <v>-42.55</v>
-      </c>
-      <c r="Q67" s="84" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R67" s="84" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="S67" s="84" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="T67" s="84" t="n">
-        <v>33.22</v>
-      </c>
-      <c r="U67" s="84" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="V67" s="85" t="n">
-        <v>78.55</v>
-      </c>
+      <c r="G67" s="145" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="H67" s="90" t="n">
+        <v>6</v>
+      </c>
+      <c r="I67" s="145" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="J67" s="145" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="K67" s="91" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="L67" s="91" t="n"/>
+      <c r="M67" s="91" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="N67" s="91" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O67" s="91" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="P67" s="91" t="n">
+        <v>-18.77</v>
+      </c>
+      <c r="Q67" s="91" t="n"/>
+      <c r="R67" s="91" t="n"/>
+      <c r="S67" s="91" t="n"/>
+      <c r="T67" s="91" t="n"/>
+      <c r="U67" s="91" t="n"/>
+      <c r="V67" s="92" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="79" t="inlineStr">
-        <is>
-          <t>SIX3.EU</t>
-        </is>
-      </c>
-      <c r="B68" s="80" t="inlineStr">
-        <is>
-          <t>Sixt SE</t>
-        </is>
-      </c>
-      <c r="C68" s="79" t="inlineStr">
+      <c r="A68" s="86" t="inlineStr">
+        <is>
+          <t>THEON.EU</t>
+        </is>
+      </c>
+      <c r="B68" s="87" t="inlineStr">
+        <is>
+          <t>Theon International PLC</t>
+        </is>
+      </c>
+      <c r="C68" s="86" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="D68" s="79" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E68" s="79" t="inlineStr">
+      <c r="D68" s="86" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E68" s="86" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F68" s="81" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G68" s="144" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H68" s="83" t="n">
-        <v>6</v>
-      </c>
-      <c r="I68" s="144" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="J68" s="144" t="n">
-        <v>336.3</v>
-      </c>
-      <c r="K68" s="84" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="L68" s="84" t="n"/>
-      <c r="M68" s="84" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="N68" s="84" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O68" s="84" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="P68" s="84" t="n">
-        <v>-17.01</v>
-      </c>
-      <c r="Q68" s="84" t="n"/>
-      <c r="R68" s="84" t="n"/>
-      <c r="S68" s="84" t="n"/>
-      <c r="T68" s="84" t="n"/>
-      <c r="U68" s="84" t="n"/>
-      <c r="V68" s="85" t="n"/>
+      <c r="F68" s="88" t="n">
+        <v>46019</v>
+      </c>
+      <c r="G68" s="145" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="H68" s="90" t="n">
+        <v>44</v>
+      </c>
+      <c r="I68" s="145" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="J68" s="145" t="n">
+        <v>1222.32</v>
+      </c>
+      <c r="K68" s="91" t="n">
+        <v>-11.33</v>
+      </c>
+      <c r="L68" s="91" t="n">
+        <v>-11.81</v>
+      </c>
+      <c r="M68" s="91" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="N68" s="91" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O68" s="91" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="P68" s="91" t="n">
+        <v>-31.02</v>
+      </c>
+      <c r="Q68" s="91" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="R68" s="91" t="n"/>
+      <c r="S68" s="91" t="n">
+        <v>22.48</v>
+      </c>
+      <c r="T68" s="91" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="U68" s="91" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="V68" s="92" t="n">
+        <v>57.25</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="79" t="inlineStr">
-        <is>
-          <t>THEON.EU</t>
-        </is>
-      </c>
-      <c r="B69" s="80" t="inlineStr">
-        <is>
-          <t>Theon International PLC</t>
-        </is>
-      </c>
-      <c r="C69" s="79" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D69" s="79" t="inlineStr">
-        <is>
-          <t>Cyprus</t>
-        </is>
-      </c>
-      <c r="E69" s="79" t="inlineStr">
+      <c r="A69" s="93" t="inlineStr">
+        <is>
+          <t>VUAA.EU</t>
+        </is>
+      </c>
+      <c r="B69" s="94" t="inlineStr">
+        <is>
+          <t>Vanguard S&amp;P 500 UCITS ETF</t>
+        </is>
+      </c>
+      <c r="C69" s="93" t="n"/>
+      <c r="D69" s="93" t="n"/>
+      <c r="E69" s="93" t="inlineStr">
         <is>
           <t>Freedom24</t>
         </is>
       </c>
-      <c r="F69" s="81" t="n">
-        <v>46019</v>
-      </c>
-      <c r="G69" s="144" t="n">
-        <v>31.33</v>
-      </c>
-      <c r="H69" s="83" t="n">
-        <v>44</v>
-      </c>
-      <c r="I69" s="144" t="n">
-        <v>29.24</v>
-      </c>
-      <c r="J69" s="144" t="n">
-        <v>1286.56</v>
-      </c>
-      <c r="K69" s="84" t="n">
-        <v>-6.67</v>
-      </c>
-      <c r="L69" s="84" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="M69" s="84" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="N69" s="84" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O69" s="84" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="P69" s="84" t="n">
-        <v>-26.22</v>
-      </c>
-      <c r="Q69" s="84" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="R69" s="84" t="n"/>
-      <c r="S69" s="84" t="n">
-        <v>22.48</v>
-      </c>
-      <c r="T69" s="84" t="n">
-        <v>23.39</v>
-      </c>
-      <c r="U69" s="84" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="V69" s="85" t="n">
-        <v>57.25</v>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="86" t="inlineStr">
-        <is>
-          <t>VUAA.EU</t>
-        </is>
-      </c>
-      <c r="B70" s="87" t="inlineStr">
-        <is>
-          <t>Vanguard S&amp;P 500 UCITS ETF</t>
-        </is>
-      </c>
-      <c r="C70" s="86" t="n"/>
-      <c r="D70" s="86" t="n"/>
-      <c r="E70" s="86" t="inlineStr">
-        <is>
-          <t>Freedom24</t>
-        </is>
-      </c>
-      <c r="F70" s="88" t="n">
+      <c r="F69" s="95" t="n">
         <v>46272</v>
       </c>
-      <c r="G70" s="145" t="n">
+      <c r="G69" s="146" t="n">
         <v>128.29</v>
       </c>
-      <c r="H70" s="90" t="n">
+      <c r="H69" s="97" t="n">
         <v>3</v>
       </c>
-      <c r="I70" s="145" t="n">
-        <v>132.84</v>
-      </c>
-      <c r="J70" s="145" t="n">
-        <v>398.52</v>
-      </c>
-      <c r="K70" s="91" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L70" s="91" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M70" s="91" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N70" s="91" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="O70" s="91" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="P70" s="91" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="Q70" s="91" t="n"/>
-      <c r="R70" s="91" t="n"/>
-      <c r="S70" s="91" t="n"/>
-      <c r="T70" s="91" t="n"/>
-      <c r="U70" s="91" t="n"/>
-      <c r="V70" s="92" t="n"/>
-    </row>
+      <c r="I69" s="146" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="J69" s="146" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="K69" s="98" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="L69" s="98" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M69" s="98" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="N69" s="98" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O69" s="98" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="P69" s="98" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q69" s="98" t="n"/>
+      <c r="R69" s="98" t="n"/>
+      <c r="S69" s="98" t="n"/>
+      <c r="T69" s="98" t="n"/>
+      <c r="U69" s="98" t="n"/>
+      <c r="V69" s="99" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1"/>
     <row r="72" ht="15" customHeight="1"/>
     <row r="73" ht="21" customHeight="1"/>
     <row r="74" ht="21" customHeight="1"/>
-    <row r="75" ht="21" customHeight="1"/>
+    <row r="75" ht="21" customHeight="1">
+      <c r="B75" s="114" t="inlineStr">
+        <is>
+          <t>PORTFOLIO VALUE</t>
+        </is>
+      </c>
+      <c r="E75" s="115" t="inlineStr">
+        <is>
+          <t>PORTFOLIO RETURN</t>
+        </is>
+      </c>
+      <c r="F75" s="116" t="n"/>
+      <c r="L75" s="117" t="inlineStr">
+        <is>
+          <t>EXCESS RETURN</t>
+        </is>
+      </c>
+      <c r="N75" s="118" t="inlineStr">
+        <is>
+          <t>VUAA RETURN</t>
+        </is>
+      </c>
+      <c r="O75" s="119" t="n"/>
+    </row>
     <row r="76" ht="21" customHeight="1">
-      <c r="B76" s="114" t="inlineStr">
-        <is>
-          <t>PORTFOLIO VALUE</t>
-        </is>
-      </c>
-      <c r="E76" s="115" t="inlineStr">
-        <is>
-          <t>PORTFOLIO RETURN</t>
-        </is>
-      </c>
-      <c r="F76" s="116" t="n"/>
-      <c r="L76" s="117" t="inlineStr">
-        <is>
-          <t>EXCESS RETURN</t>
-        </is>
-      </c>
-      <c r="N76" s="118" t="inlineStr">
-        <is>
-          <t>VUAA RETURN</t>
-        </is>
-      </c>
-      <c r="O76" s="119" t="n"/>
-    </row>
-    <row r="77" ht="21" customHeight="1">
-      <c r="B77" s="149">
+      <c r="B76" s="149">
         <f>IFERROR(SUMPRODUCT(SUBTOTAL(109,OFFSET(INDEX(StockSummary[current_price],1),ROW(StockSummary[current_price])-MIN(ROW(StockSummary[current_price])),0,1)),StockSummary[quantity]),0)</f>
         <v/>
       </c>
-      <c r="E77" s="121">
+      <c r="E76" s="121">
         <f>IFERROR(SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[current_price],StockSummary[quantity])/SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[purchase_price],StockSummary[quantity])-1,0)</f>
         <v/>
       </c>
-      <c r="F77" s="116" t="n"/>
-      <c r="L77" s="122">
-        <f>E77-N77</f>
+      <c r="F76" s="116" t="n"/>
+      <c r="L76" s="122">
+        <f>E76-N76</f>
         <v/>
       </c>
-      <c r="N77" s="123">
+      <c r="N76" s="123">
         <f>IFERROR(SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[portfolio_weight],StockSummary[vuaa_return])/SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[portfolio_weight])/100,0)</f>
         <v/>
       </c>
-      <c r="O77" s="119" t="n"/>
-    </row>
+      <c r="O76" s="119" t="n"/>
+    </row>
+    <row r="77" ht="21" customHeight="1"/>
     <row r="78" ht="21" customHeight="1"/>
-    <row r="79" ht="21" customHeight="1"/>
+    <row r="79" ht="21" customHeight="1">
+      <c r="B79" s="124" t="inlineStr">
+        <is>
+          <t>TOTAL VALUE</t>
+        </is>
+      </c>
+      <c r="E79" s="125" t="inlineStr">
+        <is>
+          <t>TOTAL PORTFOLIO RETURN</t>
+        </is>
+      </c>
+      <c r="F79" s="126" t="n"/>
+    </row>
     <row r="80" ht="21" customHeight="1">
-      <c r="B80" s="124" t="inlineStr">
-        <is>
-          <t>TOTAL VALUE</t>
-        </is>
-      </c>
-      <c r="E80" s="125" t="inlineStr">
-        <is>
-          <t>TOTAL PORTFOLIO RETURN</t>
-        </is>
+      <c r="B80" s="150">
+        <f>IFERROR(B76+SUM(SoldSummary[total_profit_loss]),B76)</f>
+        <v/>
+      </c>
+      <c r="E80" s="128">
+        <f>IFERROR((B80-(SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[purchase_price],StockSummary[quantity])))/(SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[purchase_price],StockSummary[quantity])),0)</f>
+        <v/>
       </c>
       <c r="F80" s="126" t="n"/>
     </row>
-    <row r="81" ht="21" customHeight="1">
-      <c r="B81" s="150">
-        <f>IFERROR(B77+SUM(SoldSummary[total_profit_loss]),B77)</f>
-        <v/>
-      </c>
-      <c r="E81" s="128">
-        <f>IFERROR((B81-(SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[purchase_price],StockSummary[quantity])))/(SUMPRODUCT(SUBTOTAL(103,OFFSET(INDEX(StockSummary[symbol],1),ROW(StockSummary[symbol])-MIN(ROW(StockSummary[symbol])),0,1)),StockSummary[purchase_price],StockSummary[quantity])),0)</f>
-        <v/>
-      </c>
-      <c r="F81" s="126" t="n"/>
-    </row>
+    <row r="81" ht="21" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="E77:F77"/>
     <mergeCell ref="N76:O76"/>
     <mergeCell ref="E76:F76"/>
-    <mergeCell ref="N77:O77"/>
     <mergeCell ref="E80:F80"/>
-    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="E79:F79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -6585,7 +6528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6615,52 +6558,52 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="93" t="inlineStr">
+      <c r="A1" s="100" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="B1" s="93" t="inlineStr">
+      <c r="B1" s="100" t="inlineStr">
         <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="C1" s="93" t="inlineStr">
+      <c r="C1" s="100" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="D1" s="93" t="inlineStr">
+      <c r="D1" s="100" t="inlineStr">
         <is>
           <t>purchase_date</t>
         </is>
       </c>
-      <c r="E1" s="93" t="inlineStr">
+      <c r="E1" s="100" t="inlineStr">
         <is>
           <t>sell_date</t>
         </is>
       </c>
-      <c r="F1" s="93" t="inlineStr">
+      <c r="F1" s="100" t="inlineStr">
         <is>
           <t>purchase_price</t>
         </is>
       </c>
-      <c r="G1" s="93" t="inlineStr">
+      <c r="G1" s="100" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" s="93" t="inlineStr">
+      <c r="H1" s="100" t="inlineStr">
         <is>
           <t>current_price</t>
         </is>
       </c>
-      <c r="I1" s="93" t="inlineStr">
+      <c r="I1" s="100" t="inlineStr">
         <is>
           <t>percent_change</t>
         </is>
       </c>
-      <c r="J1" s="93" t="inlineStr">
+      <c r="J1" s="100" t="inlineStr">
         <is>
           <t>total_profit_loss</t>
         </is>
@@ -7150,84 +7093,156 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SXR8.DE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>45621</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F15" s="151" t="n">
+        <v>596.48</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.828825</v>
+      </c>
+      <c r="H15" s="151" t="n">
+        <v>752</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="J15" s="152" t="n">
+        <v>128.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>APP</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trading212</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F16" s="151" t="n">
+        <v>241.84</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="151" t="n">
+        <v>248.44</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J16" s="152" t="n">
+        <v>19.81</v>
+      </c>
+    </row>
     <row r="18" ht="21" customHeight="1"/>
     <row r="19" ht="21" customHeight="1"/>
-    <row r="20" ht="21" customHeight="1">
-      <c r="B20" s="132" t="inlineStr">
+    <row r="20" ht="21" customHeight="1"/>
+    <row r="21" ht="21" customHeight="1"/>
+    <row r="22" ht="21" customHeight="1">
+      <c r="B22" s="132" t="inlineStr">
         <is>
           <t>SOLD VALUE</t>
         </is>
       </c>
-      <c r="C20" s="133" t="n"/>
-      <c r="E20" s="134" t="inlineStr">
+      <c r="C22" s="133" t="n"/>
+      <c r="E22" s="134" t="inlineStr">
         <is>
           <t>SOLD RETURN</t>
         </is>
       </c>
-      <c r="F20" s="135" t="n"/>
-      <c r="H20" s="136" t="inlineStr">
+      <c r="F22" s="135" t="n"/>
+      <c r="H22" s="136" t="inlineStr">
         <is>
           <t>REALIZED P/L</t>
         </is>
       </c>
-      <c r="I20" s="137" t="n"/>
-      <c r="K20" s="138" t="inlineStr">
+      <c r="I22" s="137" t="n"/>
+      <c r="K22" s="138" t="inlineStr">
         <is>
           <t>SOLD % RETURN</t>
         </is>
       </c>
-      <c r="L20" s="139" t="n"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="B21" s="154">
+      <c r="L22" s="139" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="B23" s="154">
         <f>IFERROR(SUMPRODUCT(SoldSummary[quantity],SoldSummary[purchase_price]),0)</f>
         <v/>
       </c>
-      <c r="C21" s="133" t="n"/>
-      <c r="E21" s="155">
+      <c r="C23" s="133" t="n"/>
+      <c r="E23" s="155">
         <f>IFERROR(SUMPRODUCT(SoldSummary[quantity],SoldSummary[current_price]),0)</f>
         <v/>
       </c>
-      <c r="F21" s="135" t="n"/>
-      <c r="H21" s="156">
+      <c r="F23" s="135" t="n"/>
+      <c r="H23" s="156">
         <f>IFERROR(SUM(SoldSummary[total_profit_loss]),0)</f>
         <v/>
       </c>
-      <c r="I21" s="137" t="n"/>
-      <c r="K21" s="143">
-        <f>IFERROR((E21-B21)/B21,0)</f>
+      <c r="I23" s="137" t="n"/>
+      <c r="K23" s="143">
+        <f>IFERROR((E23-B23)/B23,0)</f>
         <v/>
       </c>
-      <c r="L21" s="139" t="n"/>
+      <c r="L23" s="139" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="K22:L22"/>
   </mergeCells>
-  <conditionalFormatting sqref="H21:I21">
+  <conditionalFormatting sqref="H23:I23">
     <cfRule type="expression" priority="1" dxfId="7">
-      <formula>$H$21&gt;=0</formula>
+      <formula>$H$23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="8">
-      <formula>$H$21&lt;0</formula>
+      <formula>$H$23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K21:L21">
+  <conditionalFormatting sqref="K23:L23">
     <cfRule type="expression" priority="3" dxfId="7">
-      <formula>$K$21&gt;=0</formula>
+      <formula>$K$23&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="8">
-      <formula>$K$21&lt;0</formula>
+      <formula>$K$23&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
